--- a/ssp_modeling/transformations/templates/calibrated/mexico/model_input_variables_mexico_ip_calibrated.xlsx
+++ b/ssp_modeling/transformations/templates/calibrated/mexico/model_input_variables_mexico_ip_calibrated.xlsx
@@ -11,13 +11,14 @@
     <sheet name="strategy_id-6003" sheetId="2" r:id="rId2"/>
     <sheet name="strategy_id-6004" sheetId="3" r:id="rId3"/>
     <sheet name="strategy_id-6005" sheetId="4" r:id="rId4"/>
+    <sheet name="strategy_id-6006" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="242">
   <si>
     <t>subsector</t>
   </si>
@@ -42540,4 +42541,4893 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:BC32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:55">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:55">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2">
+        <v>1.5</v>
+      </c>
+      <c r="I2">
+        <v>0.5</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V2">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W2">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X2">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y2">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z2">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA2">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB2">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC2">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD2">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE2">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF2">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG2">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH2">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI2">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ2">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK2">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL2">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM2">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN2">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO2">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP2">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ2">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR2">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS2">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT2">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU2">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV2">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW2">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX2">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY2">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ2">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA2">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB2">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:55">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3">
+        <v>1.5</v>
+      </c>
+      <c r="I3">
+        <v>0.5</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V3">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W3">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X3">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y3">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z3">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA3">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB3">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC3">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD3">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE3">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF3">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG3">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH3">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI3">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ3">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK3">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL3">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM3">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN3">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO3">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP3">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ3">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR3">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS3">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT3">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU3">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV3">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW3">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX3">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY3">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ3">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA3">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB3">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:55">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4">
+        <v>1.5</v>
+      </c>
+      <c r="I4">
+        <v>0.5</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V4">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W4">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X4">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y4">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z4">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA4">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB4">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC4">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD4">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE4">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF4">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG4">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH4">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI4">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ4">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK4">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL4">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM4">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN4">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO4">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP4">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ4">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR4">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS4">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT4">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU4">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV4">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW4">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX4">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY4">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ4">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA4">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB4">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:55">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5">
+        <v>1.5</v>
+      </c>
+      <c r="I5">
+        <v>0.5</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V5">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W5">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X5">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y5">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z5">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA5">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB5">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC5">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD5">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE5">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF5">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG5">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH5">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI5">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ5">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK5">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL5">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM5">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN5">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO5">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP5">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ5">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR5">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS5">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT5">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU5">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV5">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW5">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX5">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY5">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ5">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA5">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB5">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC5">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:55">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6">
+        <v>1.5</v>
+      </c>
+      <c r="I6">
+        <v>0.5</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V6">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W6">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X6">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y6">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z6">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA6">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB6">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC6">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD6">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE6">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF6">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG6">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH6">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI6">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ6">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK6">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL6">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM6">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN6">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO6">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP6">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ6">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR6">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS6">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT6">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU6">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV6">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW6">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX6">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY6">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ6">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA6">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB6">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC6">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:55">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7">
+        <v>1.5</v>
+      </c>
+      <c r="I7">
+        <v>0.5</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V7">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W7">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X7">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y7">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z7">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA7">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB7">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC7">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD7">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE7">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF7">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG7">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH7">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI7">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ7">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK7">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL7">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM7">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN7">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO7">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP7">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ7">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR7">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS7">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT7">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU7">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV7">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW7">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX7">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY7">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ7">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA7">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB7">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC7">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:55">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8">
+        <v>1.5</v>
+      </c>
+      <c r="I8">
+        <v>0.5</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V8">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W8">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X8">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y8">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z8">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA8">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB8">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC8">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD8">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE8">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF8">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG8">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH8">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI8">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ8">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK8">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL8">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM8">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN8">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO8">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP8">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ8">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR8">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS8">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT8">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU8">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV8">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW8">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX8">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY8">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ8">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA8">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB8">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:55">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9">
+        <v>1.5</v>
+      </c>
+      <c r="I9">
+        <v>0.5</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V9">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W9">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X9">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y9">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z9">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA9">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB9">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC9">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD9">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE9">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF9">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG9">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH9">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI9">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ9">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK9">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL9">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM9">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN9">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO9">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP9">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ9">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR9">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS9">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT9">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU9">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV9">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW9">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX9">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY9">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ9">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA9">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB9">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC9">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:55">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10">
+        <v>1.5</v>
+      </c>
+      <c r="I10">
+        <v>0.5</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V10">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W10">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X10">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y10">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z10">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA10">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB10">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC10">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD10">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE10">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF10">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG10">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH10">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI10">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ10">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK10">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL10">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM10">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN10">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO10">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP10">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ10">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR10">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS10">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT10">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU10">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV10">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW10">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX10">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY10">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ10">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA10">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB10">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC10">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:55">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11">
+        <v>1.5</v>
+      </c>
+      <c r="I11">
+        <v>0.5</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V11">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W11">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X11">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y11">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z11">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA11">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB11">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC11">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD11">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE11">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF11">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG11">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH11">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI11">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ11">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK11">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL11">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM11">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN11">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO11">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP11">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ11">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR11">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS11">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT11">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU11">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV11">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW11">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX11">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY11">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ11">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA11">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB11">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC11">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:55">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12">
+        <v>1.5</v>
+      </c>
+      <c r="I12">
+        <v>0.5</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V12">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W12">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X12">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y12">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z12">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA12">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB12">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC12">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD12">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE12">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF12">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG12">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH12">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI12">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ12">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK12">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL12">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM12">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN12">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO12">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP12">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ12">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR12">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS12">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT12">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU12">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV12">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW12">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX12">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY12">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ12">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA12">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB12">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC12">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:55">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13">
+        <v>1.5</v>
+      </c>
+      <c r="I13">
+        <v>0.5</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V13">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W13">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X13">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y13">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z13">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA13">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB13">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC13">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD13">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE13">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF13">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG13">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH13">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI13">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ13">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK13">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL13">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM13">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN13">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO13">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP13">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ13">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR13">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS13">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT13">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU13">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV13">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW13">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX13">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY13">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ13">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA13">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB13">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC13">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:55">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14">
+        <v>1.5</v>
+      </c>
+      <c r="I14">
+        <v>0.5</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V14">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W14">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X14">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y14">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z14">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA14">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB14">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC14">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD14">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE14">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF14">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG14">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH14">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI14">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ14">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK14">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL14">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM14">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN14">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO14">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP14">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ14">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR14">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS14">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT14">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU14">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV14">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW14">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX14">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY14">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ14">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA14">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB14">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC14">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:55">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15">
+        <v>1.5</v>
+      </c>
+      <c r="I15">
+        <v>0.5</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V15">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W15">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X15">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y15">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z15">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA15">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB15">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC15">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD15">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE15">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF15">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG15">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH15">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI15">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ15">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK15">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL15">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM15">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN15">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO15">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP15">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ15">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR15">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS15">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT15">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU15">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV15">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW15">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX15">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY15">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ15">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA15">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB15">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC15">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:55">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16">
+        <v>1.5</v>
+      </c>
+      <c r="I16">
+        <v>0.5</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V16">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W16">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X16">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y16">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z16">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA16">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB16">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC16">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD16">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE16">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF16">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG16">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH16">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI16">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ16">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK16">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL16">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM16">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN16">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO16">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP16">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ16">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR16">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS16">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT16">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU16">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV16">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW16">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX16">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY16">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ16">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA16">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB16">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC16">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:55">
+      <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17">
+        <v>1.5</v>
+      </c>
+      <c r="I17">
+        <v>0.5</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V17">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W17">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X17">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y17">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z17">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA17">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB17">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC17">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD17">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE17">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF17">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG17">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH17">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI17">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ17">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK17">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL17">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM17">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN17">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO17">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP17">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ17">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR17">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS17">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT17">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU17">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV17">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW17">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX17">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY17">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ17">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA17">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB17">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC17">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:55">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18">
+        <v>1.5</v>
+      </c>
+      <c r="I18">
+        <v>0.5</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V18">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W18">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X18">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y18">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z18">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA18">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB18">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC18">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD18">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE18">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF18">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG18">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH18">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI18">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ18">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK18">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL18">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM18">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN18">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO18">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP18">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ18">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR18">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS18">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT18">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU18">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV18">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW18">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX18">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY18">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ18">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA18">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB18">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC18">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:55">
+      <c r="A19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19">
+        <v>1.5</v>
+      </c>
+      <c r="I19">
+        <v>0.5</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V19">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W19">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X19">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y19">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z19">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA19">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB19">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC19">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD19">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE19">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF19">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG19">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH19">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI19">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ19">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK19">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL19">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM19">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN19">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO19">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP19">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ19">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR19">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS19">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT19">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU19">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV19">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW19">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX19">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY19">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ19">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA19">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB19">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC19">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:55">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20">
+        <v>1.5</v>
+      </c>
+      <c r="I20">
+        <v>0.5</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V20">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W20">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X20">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y20">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z20">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA20">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB20">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC20">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD20">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE20">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF20">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG20">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH20">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI20">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ20">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK20">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL20">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM20">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN20">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO20">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP20">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ20">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR20">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS20">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT20">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU20">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV20">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW20">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX20">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY20">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ20">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA20">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB20">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:55">
+      <c r="A21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21">
+        <v>1.5</v>
+      </c>
+      <c r="I21">
+        <v>0.5</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>0.9914285714285714</v>
+      </c>
+      <c r="V21">
+        <v>0.9828571428571429</v>
+      </c>
+      <c r="W21">
+        <v>0.9742857142857142</v>
+      </c>
+      <c r="X21">
+        <v>0.9657142857142856</v>
+      </c>
+      <c r="Y21">
+        <v>0.9571428571428572</v>
+      </c>
+      <c r="Z21">
+        <v>0.9485714285714285</v>
+      </c>
+      <c r="AA21">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB21">
+        <v>0.9314285714285715</v>
+      </c>
+      <c r="AC21">
+        <v>0.9228571428571428</v>
+      </c>
+      <c r="AD21">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AE21">
+        <v>0.9057142857142857</v>
+      </c>
+      <c r="AF21">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="AG21">
+        <v>0.8885714285714286</v>
+      </c>
+      <c r="AH21">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AI21">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="AJ21">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="AK21">
+        <v>0.8542857142857142</v>
+      </c>
+      <c r="AL21">
+        <v>0.8457142857142856</v>
+      </c>
+      <c r="AM21">
+        <v>0.8371428571428572</v>
+      </c>
+      <c r="AN21">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="AO21">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AP21">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="AQ21">
+        <v>0.8028571428571428</v>
+      </c>
+      <c r="AR21">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="AS21">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AT21">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="AU21">
+        <v>0.7685714285714286</v>
+      </c>
+      <c r="AV21">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AW21">
+        <v>0.7514285714285713</v>
+      </c>
+      <c r="AX21">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AY21">
+        <v>0.7342857142857142</v>
+      </c>
+      <c r="AZ21">
+        <v>0.7257142857142856</v>
+      </c>
+      <c r="BA21">
+        <v>0.7171428571428571</v>
+      </c>
+      <c r="BB21">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="BC21">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:55">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" t="s">
+        <v>168</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>0.75</v>
+      </c>
+      <c r="K22">
+        <v>0.75</v>
+      </c>
+      <c r="L22">
+        <v>0.75</v>
+      </c>
+      <c r="M22">
+        <v>0.75</v>
+      </c>
+      <c r="N22">
+        <v>0.75</v>
+      </c>
+      <c r="O22">
+        <v>0.75</v>
+      </c>
+      <c r="P22">
+        <v>0.75</v>
+      </c>
+      <c r="Q22">
+        <v>0.75</v>
+      </c>
+      <c r="R22">
+        <v>0.75</v>
+      </c>
+      <c r="S22">
+        <v>0.75</v>
+      </c>
+      <c r="T22">
+        <v>0.75</v>
+      </c>
+      <c r="U22">
+        <v>0.7428571428571428</v>
+      </c>
+      <c r="V22">
+        <v>0.7357142857142857</v>
+      </c>
+      <c r="W22">
+        <v>0.7285714285714285</v>
+      </c>
+      <c r="X22">
+        <v>0.7214285714285714</v>
+      </c>
+      <c r="Y22">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Z22">
+        <v>0.7071428571428572</v>
+      </c>
+      <c r="AA22">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="AB22">
+        <v>0.6928571428571429</v>
+      </c>
+      <c r="AC22">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="AD22">
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="AE22">
+        <v>0.6714285714285714</v>
+      </c>
+      <c r="AF22">
+        <v>0.6642857142857144</v>
+      </c>
+      <c r="AG22">
+        <v>0.6571428571428571</v>
+      </c>
+      <c r="AH22">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="AI22">
+        <v>0.6428571428571428</v>
+      </c>
+      <c r="AJ22">
+        <v>0.6357142857142858</v>
+      </c>
+      <c r="AK22">
+        <v>0.6285714285714286</v>
+      </c>
+      <c r="AL22">
+        <v>0.6214285714285714</v>
+      </c>
+      <c r="AM22">
+        <v>0.6142857142857143</v>
+      </c>
+      <c r="AN22">
+        <v>0.6071428571428572</v>
+      </c>
+      <c r="AO22">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AP22">
+        <v>0.5928571428571429</v>
+      </c>
+      <c r="AQ22">
+        <v>0.5857142857142856</v>
+      </c>
+      <c r="AR22">
+        <v>0.5785714285714285</v>
+      </c>
+      <c r="AS22">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AT22">
+        <v>0.5642857142857143</v>
+      </c>
+      <c r="AU22">
+        <v>0.5571428571428572</v>
+      </c>
+      <c r="AV22">
+        <v>0.55</v>
+      </c>
+      <c r="AW22">
+        <v>0.5428571428571428</v>
+      </c>
+      <c r="AX22">
+        <v>0.5357142857142857</v>
+      </c>
+      <c r="AY22">
+        <v>0.5285714285714286</v>
+      </c>
+      <c r="AZ22">
+        <v>0.5214285714285715</v>
+      </c>
+      <c r="BA22">
+        <v>0.5142857142857142</v>
+      </c>
+      <c r="BB22">
+        <v>0.5071428571428571</v>
+      </c>
+      <c r="BC22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:55">
+      <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" t="s">
+        <v>169</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0.02285714285714286</v>
+      </c>
+      <c r="V23">
+        <v>0.04571428571428571</v>
+      </c>
+      <c r="W23">
+        <v>0.06857142857142857</v>
+      </c>
+      <c r="X23">
+        <v>0.09142857142857143</v>
+      </c>
+      <c r="Y23">
+        <v>0.1142857142857143</v>
+      </c>
+      <c r="Z23">
+        <v>0.1371428571428571</v>
+      </c>
+      <c r="AA23">
+        <v>0.16</v>
+      </c>
+      <c r="AB23">
+        <v>0.1828571428571429</v>
+      </c>
+      <c r="AC23">
+        <v>0.2057142857142857</v>
+      </c>
+      <c r="AD23">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AE23">
+        <v>0.2514285714285714</v>
+      </c>
+      <c r="AF23">
+        <v>0.2742857142857143</v>
+      </c>
+      <c r="AG23">
+        <v>0.2971428571428572</v>
+      </c>
+      <c r="AH23">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="AI23">
+        <v>0.3428571428571429</v>
+      </c>
+      <c r="AJ23">
+        <v>0.3657142857142857</v>
+      </c>
+      <c r="AK23">
+        <v>0.3885714285714286</v>
+      </c>
+      <c r="AL23">
+        <v>0.4114285714285714</v>
+      </c>
+      <c r="AM23">
+        <v>0.4342857142857143</v>
+      </c>
+      <c r="AN23">
+        <v>0.4571428571428571</v>
+      </c>
+      <c r="AO23">
+        <v>0.48</v>
+      </c>
+      <c r="AP23">
+        <v>0.5028571428571429</v>
+      </c>
+      <c r="AQ23">
+        <v>0.5257142857142857</v>
+      </c>
+      <c r="AR23">
+        <v>0.5485714285714286</v>
+      </c>
+      <c r="AS23">
+        <v>0.5714285714285715</v>
+      </c>
+      <c r="AT23">
+        <v>0.5942857142857143</v>
+      </c>
+      <c r="AU23">
+        <v>0.6171428571428572</v>
+      </c>
+      <c r="AV23">
+        <v>0.6400000000000001</v>
+      </c>
+      <c r="AW23">
+        <v>0.6628571428571429</v>
+      </c>
+      <c r="AX23">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="AY23">
+        <v>0.7085714285714286</v>
+      </c>
+      <c r="AZ23">
+        <v>0.7314285714285714</v>
+      </c>
+      <c r="BA23">
+        <v>0.7542857142857143</v>
+      </c>
+      <c r="BB23">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="BC23">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:55">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
+        <v>170</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0.02285714285714286</v>
+      </c>
+      <c r="V24">
+        <v>0.04571428571428571</v>
+      </c>
+      <c r="W24">
+        <v>0.06857142857142857</v>
+      </c>
+      <c r="X24">
+        <v>0.09142857142857143</v>
+      </c>
+      <c r="Y24">
+        <v>0.1142857142857143</v>
+      </c>
+      <c r="Z24">
+        <v>0.1371428571428571</v>
+      </c>
+      <c r="AA24">
+        <v>0.16</v>
+      </c>
+      <c r="AB24">
+        <v>0.1828571428571429</v>
+      </c>
+      <c r="AC24">
+        <v>0.2057142857142857</v>
+      </c>
+      <c r="AD24">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AE24">
+        <v>0.2514285714285714</v>
+      </c>
+      <c r="AF24">
+        <v>0.2742857142857143</v>
+      </c>
+      <c r="AG24">
+        <v>0.2971428571428572</v>
+      </c>
+      <c r="AH24">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="AI24">
+        <v>0.3428571428571429</v>
+      </c>
+      <c r="AJ24">
+        <v>0.3657142857142857</v>
+      </c>
+      <c r="AK24">
+        <v>0.3885714285714286</v>
+      </c>
+      <c r="AL24">
+        <v>0.4114285714285714</v>
+      </c>
+      <c r="AM24">
+        <v>0.4342857142857143</v>
+      </c>
+      <c r="AN24">
+        <v>0.4571428571428571</v>
+      </c>
+      <c r="AO24">
+        <v>0.48</v>
+      </c>
+      <c r="AP24">
+        <v>0.5028571428571429</v>
+      </c>
+      <c r="AQ24">
+        <v>0.5257142857142857</v>
+      </c>
+      <c r="AR24">
+        <v>0.5485714285714286</v>
+      </c>
+      <c r="AS24">
+        <v>0.5714285714285715</v>
+      </c>
+      <c r="AT24">
+        <v>0.5942857142857143</v>
+      </c>
+      <c r="AU24">
+        <v>0.6171428571428572</v>
+      </c>
+      <c r="AV24">
+        <v>0.6400000000000001</v>
+      </c>
+      <c r="AW24">
+        <v>0.6628571428571429</v>
+      </c>
+      <c r="AX24">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="AY24">
+        <v>0.7085714285714286</v>
+      </c>
+      <c r="AZ24">
+        <v>0.7314285714285714</v>
+      </c>
+      <c r="BA24">
+        <v>0.7542857142857143</v>
+      </c>
+      <c r="BB24">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="BC24">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:55">
+      <c r="A25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0.02285714285714286</v>
+      </c>
+      <c r="V25">
+        <v>0.04571428571428571</v>
+      </c>
+      <c r="W25">
+        <v>0.06857142857142857</v>
+      </c>
+      <c r="X25">
+        <v>0.09142857142857143</v>
+      </c>
+      <c r="Y25">
+        <v>0.1142857142857143</v>
+      </c>
+      <c r="Z25">
+        <v>0.1371428571428571</v>
+      </c>
+      <c r="AA25">
+        <v>0.16</v>
+      </c>
+      <c r="AB25">
+        <v>0.1828571428571429</v>
+      </c>
+      <c r="AC25">
+        <v>0.2057142857142857</v>
+      </c>
+      <c r="AD25">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AE25">
+        <v>0.2514285714285714</v>
+      </c>
+      <c r="AF25">
+        <v>0.2742857142857143</v>
+      </c>
+      <c r="AG25">
+        <v>0.2971428571428572</v>
+      </c>
+      <c r="AH25">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="AI25">
+        <v>0.3428571428571429</v>
+      </c>
+      <c r="AJ25">
+        <v>0.3657142857142857</v>
+      </c>
+      <c r="AK25">
+        <v>0.3885714285714286</v>
+      </c>
+      <c r="AL25">
+        <v>0.4114285714285714</v>
+      </c>
+      <c r="AM25">
+        <v>0.4342857142857143</v>
+      </c>
+      <c r="AN25">
+        <v>0.4571428571428571</v>
+      </c>
+      <c r="AO25">
+        <v>0.48</v>
+      </c>
+      <c r="AP25">
+        <v>0.5028571428571429</v>
+      </c>
+      <c r="AQ25">
+        <v>0.5257142857142857</v>
+      </c>
+      <c r="AR25">
+        <v>0.5485714285714286</v>
+      </c>
+      <c r="AS25">
+        <v>0.5714285714285715</v>
+      </c>
+      <c r="AT25">
+        <v>0.5942857142857143</v>
+      </c>
+      <c r="AU25">
+        <v>0.6171428571428572</v>
+      </c>
+      <c r="AV25">
+        <v>0.6400000000000001</v>
+      </c>
+      <c r="AW25">
+        <v>0.6628571428571429</v>
+      </c>
+      <c r="AX25">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="AY25">
+        <v>0.7085714285714286</v>
+      </c>
+      <c r="AZ25">
+        <v>0.7314285714285714</v>
+      </c>
+      <c r="BA25">
+        <v>0.7542857142857143</v>
+      </c>
+      <c r="BB25">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="BC25">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:55">
+      <c r="A26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" t="s">
+        <v>174</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0.02285714285714286</v>
+      </c>
+      <c r="V26">
+        <v>0.04571428571428571</v>
+      </c>
+      <c r="W26">
+        <v>0.06857142857142857</v>
+      </c>
+      <c r="X26">
+        <v>0.09142857142857143</v>
+      </c>
+      <c r="Y26">
+        <v>0.1142857142857143</v>
+      </c>
+      <c r="Z26">
+        <v>0.1371428571428571</v>
+      </c>
+      <c r="AA26">
+        <v>0.16</v>
+      </c>
+      <c r="AB26">
+        <v>0.1828571428571429</v>
+      </c>
+      <c r="AC26">
+        <v>0.2057142857142857</v>
+      </c>
+      <c r="AD26">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AE26">
+        <v>0.2514285714285714</v>
+      </c>
+      <c r="AF26">
+        <v>0.2742857142857143</v>
+      </c>
+      <c r="AG26">
+        <v>0.2971428571428572</v>
+      </c>
+      <c r="AH26">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="AI26">
+        <v>0.3428571428571429</v>
+      </c>
+      <c r="AJ26">
+        <v>0.3657142857142857</v>
+      </c>
+      <c r="AK26">
+        <v>0.3885714285714286</v>
+      </c>
+      <c r="AL26">
+        <v>0.4114285714285714</v>
+      </c>
+      <c r="AM26">
+        <v>0.4342857142857143</v>
+      </c>
+      <c r="AN26">
+        <v>0.4571428571428571</v>
+      </c>
+      <c r="AO26">
+        <v>0.48</v>
+      </c>
+      <c r="AP26">
+        <v>0.5028571428571429</v>
+      </c>
+      <c r="AQ26">
+        <v>0.5257142857142857</v>
+      </c>
+      <c r="AR26">
+        <v>0.5485714285714286</v>
+      </c>
+      <c r="AS26">
+        <v>0.5714285714285715</v>
+      </c>
+      <c r="AT26">
+        <v>0.5942857142857143</v>
+      </c>
+      <c r="AU26">
+        <v>0.6171428571428572</v>
+      </c>
+      <c r="AV26">
+        <v>0.6400000000000001</v>
+      </c>
+      <c r="AW26">
+        <v>0.6628571428571429</v>
+      </c>
+      <c r="AX26">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="AY26">
+        <v>0.7085714285714286</v>
+      </c>
+      <c r="AZ26">
+        <v>0.7314285714285714</v>
+      </c>
+      <c r="BA26">
+        <v>0.7542857142857143</v>
+      </c>
+      <c r="BB26">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="BC26">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:55">
+      <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" t="s">
+        <v>175</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>0.9</v>
+      </c>
+      <c r="K27">
+        <v>0.9</v>
+      </c>
+      <c r="L27">
+        <v>0.9</v>
+      </c>
+      <c r="M27">
+        <v>0.9</v>
+      </c>
+      <c r="N27">
+        <v>0.9</v>
+      </c>
+      <c r="O27">
+        <v>0.9</v>
+      </c>
+      <c r="P27">
+        <v>0.9</v>
+      </c>
+      <c r="Q27">
+        <v>0.9</v>
+      </c>
+      <c r="R27">
+        <v>0.9</v>
+      </c>
+      <c r="S27">
+        <v>0.9</v>
+      </c>
+      <c r="T27">
+        <v>0.9</v>
+      </c>
+      <c r="U27">
+        <v>0.9</v>
+      </c>
+      <c r="V27">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W27">
+        <v>0.9</v>
+      </c>
+      <c r="X27">
+        <v>0.9</v>
+      </c>
+      <c r="Y27">
+        <v>0.9</v>
+      </c>
+      <c r="Z27">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA27">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AB27">
+        <v>0.9</v>
+      </c>
+      <c r="AC27">
+        <v>0.9</v>
+      </c>
+      <c r="AD27">
+        <v>0.9</v>
+      </c>
+      <c r="AE27">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AF27">
+        <v>0.9</v>
+      </c>
+      <c r="AG27">
+        <v>0.9</v>
+      </c>
+      <c r="AH27">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI27">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AJ27">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AK27">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AL27">
+        <v>0.9</v>
+      </c>
+      <c r="AM27">
+        <v>0.9</v>
+      </c>
+      <c r="AN27">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO27">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AP27">
+        <v>0.9</v>
+      </c>
+      <c r="AQ27">
+        <v>0.9</v>
+      </c>
+      <c r="AR27">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS27">
+        <v>0.9</v>
+      </c>
+      <c r="AT27">
+        <v>0.9</v>
+      </c>
+      <c r="AU27">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AV27">
+        <v>0.9</v>
+      </c>
+      <c r="AW27">
+        <v>0.9</v>
+      </c>
+      <c r="AX27">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AY27">
+        <v>0.9</v>
+      </c>
+      <c r="AZ27">
+        <v>0.9</v>
+      </c>
+      <c r="BA27">
+        <v>0.9</v>
+      </c>
+      <c r="BB27">
+        <v>0.9</v>
+      </c>
+      <c r="BC27">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:55">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" t="s">
+        <v>176</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>0.9</v>
+      </c>
+      <c r="K28">
+        <v>0.9</v>
+      </c>
+      <c r="L28">
+        <v>0.9</v>
+      </c>
+      <c r="M28">
+        <v>0.9</v>
+      </c>
+      <c r="N28">
+        <v>0.9</v>
+      </c>
+      <c r="O28">
+        <v>0.9</v>
+      </c>
+      <c r="P28">
+        <v>0.9</v>
+      </c>
+      <c r="Q28">
+        <v>0.9</v>
+      </c>
+      <c r="R28">
+        <v>0.9</v>
+      </c>
+      <c r="S28">
+        <v>0.9</v>
+      </c>
+      <c r="T28">
+        <v>0.9</v>
+      </c>
+      <c r="U28">
+        <v>0.9</v>
+      </c>
+      <c r="V28">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W28">
+        <v>0.9</v>
+      </c>
+      <c r="X28">
+        <v>0.9</v>
+      </c>
+      <c r="Y28">
+        <v>0.9</v>
+      </c>
+      <c r="Z28">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA28">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AB28">
+        <v>0.9</v>
+      </c>
+      <c r="AC28">
+        <v>0.9</v>
+      </c>
+      <c r="AD28">
+        <v>0.9</v>
+      </c>
+      <c r="AE28">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AF28">
+        <v>0.9</v>
+      </c>
+      <c r="AG28">
+        <v>0.9</v>
+      </c>
+      <c r="AH28">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI28">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AJ28">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AK28">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AL28">
+        <v>0.9</v>
+      </c>
+      <c r="AM28">
+        <v>0.9</v>
+      </c>
+      <c r="AN28">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO28">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AP28">
+        <v>0.9</v>
+      </c>
+      <c r="AQ28">
+        <v>0.9</v>
+      </c>
+      <c r="AR28">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS28">
+        <v>0.9</v>
+      </c>
+      <c r="AT28">
+        <v>0.9</v>
+      </c>
+      <c r="AU28">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AV28">
+        <v>0.9</v>
+      </c>
+      <c r="AW28">
+        <v>0.9</v>
+      </c>
+      <c r="AX28">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AY28">
+        <v>0.9</v>
+      </c>
+      <c r="AZ28">
+        <v>0.9</v>
+      </c>
+      <c r="BA28">
+        <v>0.9</v>
+      </c>
+      <c r="BB28">
+        <v>0.9</v>
+      </c>
+      <c r="BC28">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:55">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" t="s">
+        <v>177</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>0.9</v>
+      </c>
+      <c r="K29">
+        <v>0.9</v>
+      </c>
+      <c r="L29">
+        <v>0.9</v>
+      </c>
+      <c r="M29">
+        <v>0.9</v>
+      </c>
+      <c r="N29">
+        <v>0.9</v>
+      </c>
+      <c r="O29">
+        <v>0.9</v>
+      </c>
+      <c r="P29">
+        <v>0.9</v>
+      </c>
+      <c r="Q29">
+        <v>0.9</v>
+      </c>
+      <c r="R29">
+        <v>0.9</v>
+      </c>
+      <c r="S29">
+        <v>0.9</v>
+      </c>
+      <c r="T29">
+        <v>0.9</v>
+      </c>
+      <c r="U29">
+        <v>0.9</v>
+      </c>
+      <c r="V29">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W29">
+        <v>0.9</v>
+      </c>
+      <c r="X29">
+        <v>0.9</v>
+      </c>
+      <c r="Y29">
+        <v>0.9</v>
+      </c>
+      <c r="Z29">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA29">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AB29">
+        <v>0.9</v>
+      </c>
+      <c r="AC29">
+        <v>0.9</v>
+      </c>
+      <c r="AD29">
+        <v>0.9</v>
+      </c>
+      <c r="AE29">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AF29">
+        <v>0.9</v>
+      </c>
+      <c r="AG29">
+        <v>0.9</v>
+      </c>
+      <c r="AH29">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI29">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AJ29">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AK29">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AL29">
+        <v>0.9</v>
+      </c>
+      <c r="AM29">
+        <v>0.9</v>
+      </c>
+      <c r="AN29">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO29">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AP29">
+        <v>0.9</v>
+      </c>
+      <c r="AQ29">
+        <v>0.9</v>
+      </c>
+      <c r="AR29">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS29">
+        <v>0.9</v>
+      </c>
+      <c r="AT29">
+        <v>0.9</v>
+      </c>
+      <c r="AU29">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AV29">
+        <v>0.9</v>
+      </c>
+      <c r="AW29">
+        <v>0.9</v>
+      </c>
+      <c r="AX29">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AY29">
+        <v>0.9</v>
+      </c>
+      <c r="AZ29">
+        <v>0.9</v>
+      </c>
+      <c r="BA29">
+        <v>0.9</v>
+      </c>
+      <c r="BB29">
+        <v>0.9</v>
+      </c>
+      <c r="BC29">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:55">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" t="s">
+        <v>178</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>0.9</v>
+      </c>
+      <c r="K30">
+        <v>0.9</v>
+      </c>
+      <c r="L30">
+        <v>0.9</v>
+      </c>
+      <c r="M30">
+        <v>0.9</v>
+      </c>
+      <c r="N30">
+        <v>0.9</v>
+      </c>
+      <c r="O30">
+        <v>0.9</v>
+      </c>
+      <c r="P30">
+        <v>0.9</v>
+      </c>
+      <c r="Q30">
+        <v>0.9</v>
+      </c>
+      <c r="R30">
+        <v>0.9</v>
+      </c>
+      <c r="S30">
+        <v>0.9</v>
+      </c>
+      <c r="T30">
+        <v>0.9</v>
+      </c>
+      <c r="U30">
+        <v>0.9</v>
+      </c>
+      <c r="V30">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W30">
+        <v>0.9</v>
+      </c>
+      <c r="X30">
+        <v>0.9</v>
+      </c>
+      <c r="Y30">
+        <v>0.9</v>
+      </c>
+      <c r="Z30">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA30">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AB30">
+        <v>0.9</v>
+      </c>
+      <c r="AC30">
+        <v>0.9</v>
+      </c>
+      <c r="AD30">
+        <v>0.9</v>
+      </c>
+      <c r="AE30">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AF30">
+        <v>0.9</v>
+      </c>
+      <c r="AG30">
+        <v>0.9</v>
+      </c>
+      <c r="AH30">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI30">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AJ30">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AK30">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AL30">
+        <v>0.9</v>
+      </c>
+      <c r="AM30">
+        <v>0.9</v>
+      </c>
+      <c r="AN30">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO30">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AP30">
+        <v>0.9</v>
+      </c>
+      <c r="AQ30">
+        <v>0.9</v>
+      </c>
+      <c r="AR30">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS30">
+        <v>0.9</v>
+      </c>
+      <c r="AT30">
+        <v>0.9</v>
+      </c>
+      <c r="AU30">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AV30">
+        <v>0.9</v>
+      </c>
+      <c r="AW30">
+        <v>0.9</v>
+      </c>
+      <c r="AX30">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AY30">
+        <v>0.9</v>
+      </c>
+      <c r="AZ30">
+        <v>0.9</v>
+      </c>
+      <c r="BA30">
+        <v>0.9</v>
+      </c>
+      <c r="BB30">
+        <v>0.9</v>
+      </c>
+      <c r="BC30">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:55">
+      <c r="A31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" t="s">
+        <v>179</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>0.9</v>
+      </c>
+      <c r="K31">
+        <v>0.9</v>
+      </c>
+      <c r="L31">
+        <v>0.9</v>
+      </c>
+      <c r="M31">
+        <v>0.9</v>
+      </c>
+      <c r="N31">
+        <v>0.9</v>
+      </c>
+      <c r="O31">
+        <v>0.9</v>
+      </c>
+      <c r="P31">
+        <v>0.9</v>
+      </c>
+      <c r="Q31">
+        <v>0.9</v>
+      </c>
+      <c r="R31">
+        <v>0.9</v>
+      </c>
+      <c r="S31">
+        <v>0.9</v>
+      </c>
+      <c r="T31">
+        <v>0.9</v>
+      </c>
+      <c r="U31">
+        <v>0.9</v>
+      </c>
+      <c r="V31">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W31">
+        <v>0.9</v>
+      </c>
+      <c r="X31">
+        <v>0.9</v>
+      </c>
+      <c r="Y31">
+        <v>0.9</v>
+      </c>
+      <c r="Z31">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA31">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AB31">
+        <v>0.9</v>
+      </c>
+      <c r="AC31">
+        <v>0.9</v>
+      </c>
+      <c r="AD31">
+        <v>0.9</v>
+      </c>
+      <c r="AE31">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AF31">
+        <v>0.9</v>
+      </c>
+      <c r="AG31">
+        <v>0.9</v>
+      </c>
+      <c r="AH31">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI31">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AJ31">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AK31">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AL31">
+        <v>0.9</v>
+      </c>
+      <c r="AM31">
+        <v>0.9</v>
+      </c>
+      <c r="AN31">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO31">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AP31">
+        <v>0.9</v>
+      </c>
+      <c r="AQ31">
+        <v>0.9</v>
+      </c>
+      <c r="AR31">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS31">
+        <v>0.9</v>
+      </c>
+      <c r="AT31">
+        <v>0.9</v>
+      </c>
+      <c r="AU31">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AV31">
+        <v>0.9</v>
+      </c>
+      <c r="AW31">
+        <v>0.9</v>
+      </c>
+      <c r="AX31">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AY31">
+        <v>0.9</v>
+      </c>
+      <c r="AZ31">
+        <v>0.9</v>
+      </c>
+      <c r="BA31">
+        <v>0.9</v>
+      </c>
+      <c r="BB31">
+        <v>0.9</v>
+      </c>
+      <c r="BC31">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:55">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" t="s">
+        <v>180</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>0.9</v>
+      </c>
+      <c r="K32">
+        <v>0.9</v>
+      </c>
+      <c r="L32">
+        <v>0.9</v>
+      </c>
+      <c r="M32">
+        <v>0.9</v>
+      </c>
+      <c r="N32">
+        <v>0.9</v>
+      </c>
+      <c r="O32">
+        <v>0.9</v>
+      </c>
+      <c r="P32">
+        <v>0.9</v>
+      </c>
+      <c r="Q32">
+        <v>0.9</v>
+      </c>
+      <c r="R32">
+        <v>0.9</v>
+      </c>
+      <c r="S32">
+        <v>0.9</v>
+      </c>
+      <c r="T32">
+        <v>0.9</v>
+      </c>
+      <c r="U32">
+        <v>0.9</v>
+      </c>
+      <c r="V32">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W32">
+        <v>0.9</v>
+      </c>
+      <c r="X32">
+        <v>0.9</v>
+      </c>
+      <c r="Y32">
+        <v>0.9</v>
+      </c>
+      <c r="Z32">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA32">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AB32">
+        <v>0.9</v>
+      </c>
+      <c r="AC32">
+        <v>0.9</v>
+      </c>
+      <c r="AD32">
+        <v>0.9</v>
+      </c>
+      <c r="AE32">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AF32">
+        <v>0.9</v>
+      </c>
+      <c r="AG32">
+        <v>0.9</v>
+      </c>
+      <c r="AH32">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI32">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AJ32">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AK32">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AL32">
+        <v>0.9</v>
+      </c>
+      <c r="AM32">
+        <v>0.9</v>
+      </c>
+      <c r="AN32">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO32">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AP32">
+        <v>0.9</v>
+      </c>
+      <c r="AQ32">
+        <v>0.9</v>
+      </c>
+      <c r="AR32">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS32">
+        <v>0.9</v>
+      </c>
+      <c r="AT32">
+        <v>0.9</v>
+      </c>
+      <c r="AU32">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AV32">
+        <v>0.9</v>
+      </c>
+      <c r="AW32">
+        <v>0.9</v>
+      </c>
+      <c r="AX32">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AY32">
+        <v>0.9</v>
+      </c>
+      <c r="AZ32">
+        <v>0.9</v>
+      </c>
+      <c r="BA32">
+        <v>0.9</v>
+      </c>
+      <c r="BB32">
+        <v>0.9</v>
+      </c>
+      <c r="BC32">
+        <v>0.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ssp_modeling/transformations/templates/calibrated/mexico/model_input_variables_mexico_ip_calibrated.xlsx
+++ b/ssp_modeling/transformations/templates/calibrated/mexico/model_input_variables_mexico_ip_calibrated.xlsx
@@ -11,14 +11,13 @@
     <sheet name="strategy_id-6003" sheetId="2" r:id="rId2"/>
     <sheet name="strategy_id-6004" sheetId="3" r:id="rId3"/>
     <sheet name="strategy_id-6005" sheetId="4" r:id="rId4"/>
-    <sheet name="strategy_id-6006" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="242">
   <si>
     <t>subsector</t>
   </si>
@@ -42541,4893 +42540,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BC32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:55">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:55">
-      <c r="A2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H2">
-        <v>1.5</v>
-      </c>
-      <c r="I2">
-        <v>0.5</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
-      </c>
-      <c r="U2">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V2">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W2">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X2">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y2">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z2">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA2">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB2">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC2">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD2">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE2">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF2">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG2">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH2">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI2">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ2">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK2">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL2">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM2">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN2">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO2">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP2">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ2">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR2">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS2">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT2">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU2">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV2">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW2">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX2">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY2">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ2">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA2">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB2">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC2">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:55">
-      <c r="A3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H3">
-        <v>1.5</v>
-      </c>
-      <c r="I3">
-        <v>0.5</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
-      </c>
-      <c r="U3">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V3">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W3">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X3">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y3">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z3">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA3">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB3">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC3">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD3">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE3">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF3">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG3">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH3">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI3">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ3">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK3">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL3">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM3">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN3">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO3">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP3">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ3">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR3">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS3">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT3">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU3">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV3">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW3">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX3">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY3">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ3">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA3">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB3">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC3">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:55">
-      <c r="A4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H4">
-        <v>1.5</v>
-      </c>
-      <c r="I4">
-        <v>0.5</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>1</v>
-      </c>
-      <c r="S4">
-        <v>1</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
-      </c>
-      <c r="U4">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V4">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W4">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X4">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y4">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z4">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA4">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB4">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC4">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD4">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE4">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF4">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG4">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH4">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI4">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ4">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK4">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL4">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM4">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN4">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO4">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP4">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ4">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR4">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS4">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT4">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU4">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV4">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW4">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX4">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY4">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ4">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA4">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB4">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC4">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:55">
-      <c r="A5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5">
-        <v>1.5</v>
-      </c>
-      <c r="I5">
-        <v>0.5</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
-      <c r="T5">
-        <v>1</v>
-      </c>
-      <c r="U5">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V5">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W5">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X5">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y5">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z5">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA5">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB5">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC5">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD5">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE5">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF5">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG5">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH5">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI5">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ5">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK5">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL5">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM5">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN5">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO5">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP5">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ5">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR5">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS5">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT5">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU5">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV5">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW5">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX5">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY5">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ5">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA5">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB5">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC5">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:55">
-      <c r="A6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6">
-        <v>1.5</v>
-      </c>
-      <c r="I6">
-        <v>0.5</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
-      </c>
-      <c r="S6">
-        <v>1</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
-      </c>
-      <c r="U6">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V6">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W6">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X6">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y6">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z6">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA6">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB6">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC6">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD6">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE6">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF6">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG6">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH6">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI6">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ6">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK6">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL6">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM6">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN6">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO6">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP6">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ6">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR6">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS6">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT6">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU6">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV6">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW6">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX6">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY6">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ6">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA6">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB6">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC6">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:55">
-      <c r="A7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7">
-        <v>1.5</v>
-      </c>
-      <c r="I7">
-        <v>0.5</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>1</v>
-      </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="U7">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V7">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W7">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X7">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y7">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z7">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA7">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB7">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC7">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD7">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE7">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF7">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG7">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH7">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI7">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ7">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK7">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL7">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM7">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN7">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO7">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP7">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ7">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR7">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS7">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT7">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU7">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV7">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW7">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX7">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY7">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ7">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA7">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB7">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC7">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:55">
-      <c r="A8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8">
-        <v>1.5</v>
-      </c>
-      <c r="I8">
-        <v>0.5</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>1</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8">
-        <v>1</v>
-      </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
-      <c r="U8">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V8">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W8">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X8">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y8">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z8">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA8">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB8">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC8">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD8">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE8">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF8">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG8">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH8">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI8">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ8">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK8">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL8">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM8">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN8">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO8">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP8">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ8">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR8">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS8">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT8">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU8">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV8">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW8">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX8">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY8">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ8">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA8">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB8">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC8">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:55">
-      <c r="A9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9">
-        <v>1.5</v>
-      </c>
-      <c r="I9">
-        <v>0.5</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="S9">
-        <v>1</v>
-      </c>
-      <c r="T9">
-        <v>1</v>
-      </c>
-      <c r="U9">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V9">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W9">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X9">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y9">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z9">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA9">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB9">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC9">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD9">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE9">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF9">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG9">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH9">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI9">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ9">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK9">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL9">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM9">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN9">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO9">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP9">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ9">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR9">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS9">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT9">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU9">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV9">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW9">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX9">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY9">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ9">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA9">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB9">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC9">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:55">
-      <c r="A10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10">
-        <v>1.5</v>
-      </c>
-      <c r="I10">
-        <v>0.5</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-      <c r="P10">
-        <v>1</v>
-      </c>
-      <c r="Q10">
-        <v>1</v>
-      </c>
-      <c r="R10">
-        <v>1</v>
-      </c>
-      <c r="S10">
-        <v>1</v>
-      </c>
-      <c r="T10">
-        <v>1</v>
-      </c>
-      <c r="U10">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V10">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W10">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X10">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y10">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z10">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA10">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB10">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC10">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD10">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE10">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF10">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG10">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH10">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI10">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ10">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK10">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL10">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM10">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN10">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO10">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP10">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ10">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR10">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS10">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT10">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU10">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV10">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW10">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX10">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY10">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ10">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA10">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB10">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC10">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:55">
-      <c r="A11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11">
-        <v>1.5</v>
-      </c>
-      <c r="I11">
-        <v>0.5</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11">
-        <v>1</v>
-      </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
-      <c r="S11">
-        <v>1</v>
-      </c>
-      <c r="T11">
-        <v>1</v>
-      </c>
-      <c r="U11">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V11">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W11">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X11">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y11">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z11">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA11">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB11">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC11">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD11">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE11">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF11">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG11">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH11">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI11">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ11">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK11">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL11">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM11">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN11">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO11">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP11">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ11">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR11">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS11">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT11">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU11">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV11">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW11">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX11">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY11">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ11">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA11">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB11">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC11">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:55">
-      <c r="A12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="H12">
-        <v>1.5</v>
-      </c>
-      <c r="I12">
-        <v>0.5</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
-      <c r="Q12">
-        <v>1</v>
-      </c>
-      <c r="R12">
-        <v>1</v>
-      </c>
-      <c r="S12">
-        <v>1</v>
-      </c>
-      <c r="T12">
-        <v>1</v>
-      </c>
-      <c r="U12">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V12">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W12">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X12">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y12">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z12">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA12">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB12">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC12">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD12">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE12">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF12">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG12">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH12">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI12">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ12">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK12">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL12">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM12">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN12">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO12">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP12">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ12">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR12">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS12">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT12">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU12">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV12">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW12">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX12">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY12">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ12">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA12">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB12">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC12">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:55">
-      <c r="A13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="H13">
-        <v>1.5</v>
-      </c>
-      <c r="I13">
-        <v>0.5</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13">
-        <v>1</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
-      <c r="P13">
-        <v>1</v>
-      </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
-      <c r="R13">
-        <v>1</v>
-      </c>
-      <c r="S13">
-        <v>1</v>
-      </c>
-      <c r="T13">
-        <v>1</v>
-      </c>
-      <c r="U13">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V13">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W13">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X13">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y13">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z13">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA13">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB13">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC13">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD13">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE13">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF13">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG13">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH13">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI13">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ13">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK13">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL13">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM13">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN13">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO13">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP13">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ13">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR13">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS13">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT13">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU13">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV13">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW13">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX13">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY13">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ13">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA13">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB13">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC13">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:55">
-      <c r="A14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="H14">
-        <v>1.5</v>
-      </c>
-      <c r="I14">
-        <v>0.5</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>1</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-      <c r="O14">
-        <v>1</v>
-      </c>
-      <c r="P14">
-        <v>1</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
-      </c>
-      <c r="R14">
-        <v>1</v>
-      </c>
-      <c r="S14">
-        <v>1</v>
-      </c>
-      <c r="T14">
-        <v>1</v>
-      </c>
-      <c r="U14">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V14">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W14">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X14">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y14">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z14">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA14">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB14">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC14">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD14">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE14">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF14">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG14">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH14">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI14">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ14">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK14">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL14">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM14">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN14">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO14">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP14">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ14">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR14">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS14">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT14">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU14">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV14">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW14">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX14">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY14">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ14">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA14">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB14">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC14">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:55">
-      <c r="A15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="H15">
-        <v>1.5</v>
-      </c>
-      <c r="I15">
-        <v>0.5</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15">
-        <v>1</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-      <c r="O15">
-        <v>1</v>
-      </c>
-      <c r="P15">
-        <v>1</v>
-      </c>
-      <c r="Q15">
-        <v>1</v>
-      </c>
-      <c r="R15">
-        <v>1</v>
-      </c>
-      <c r="S15">
-        <v>1</v>
-      </c>
-      <c r="T15">
-        <v>1</v>
-      </c>
-      <c r="U15">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V15">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W15">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X15">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y15">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z15">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA15">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB15">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC15">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD15">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE15">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF15">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG15">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH15">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI15">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ15">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK15">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL15">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM15">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN15">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO15">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP15">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ15">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR15">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS15">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT15">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU15">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV15">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW15">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX15">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY15">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ15">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA15">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB15">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC15">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:55">
-      <c r="A16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="H16">
-        <v>1.5</v>
-      </c>
-      <c r="I16">
-        <v>0.5</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="N16">
-        <v>1</v>
-      </c>
-      <c r="O16">
-        <v>1</v>
-      </c>
-      <c r="P16">
-        <v>1</v>
-      </c>
-      <c r="Q16">
-        <v>1</v>
-      </c>
-      <c r="R16">
-        <v>1</v>
-      </c>
-      <c r="S16">
-        <v>1</v>
-      </c>
-      <c r="T16">
-        <v>1</v>
-      </c>
-      <c r="U16">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V16">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W16">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X16">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y16">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z16">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA16">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB16">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC16">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD16">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE16">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF16">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG16">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH16">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI16">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ16">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK16">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL16">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM16">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN16">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO16">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP16">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ16">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR16">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS16">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT16">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU16">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV16">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW16">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX16">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY16">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ16">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA16">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB16">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC16">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:55">
-      <c r="A17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17">
-        <v>1.5</v>
-      </c>
-      <c r="I17">
-        <v>0.5</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17">
-        <v>1</v>
-      </c>
-      <c r="O17">
-        <v>1</v>
-      </c>
-      <c r="P17">
-        <v>1</v>
-      </c>
-      <c r="Q17">
-        <v>1</v>
-      </c>
-      <c r="R17">
-        <v>1</v>
-      </c>
-      <c r="S17">
-        <v>1</v>
-      </c>
-      <c r="T17">
-        <v>1</v>
-      </c>
-      <c r="U17">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V17">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W17">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X17">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y17">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z17">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA17">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB17">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC17">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD17">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE17">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF17">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG17">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH17">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI17">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ17">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK17">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL17">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM17">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN17">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO17">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP17">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ17">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR17">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS17">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT17">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU17">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV17">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW17">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX17">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY17">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ17">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA17">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB17">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC17">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:55">
-      <c r="A18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18">
-        <v>1.5</v>
-      </c>
-      <c r="I18">
-        <v>0.5</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18">
-        <v>1</v>
-      </c>
-      <c r="O18">
-        <v>1</v>
-      </c>
-      <c r="P18">
-        <v>1</v>
-      </c>
-      <c r="Q18">
-        <v>1</v>
-      </c>
-      <c r="R18">
-        <v>1</v>
-      </c>
-      <c r="S18">
-        <v>1</v>
-      </c>
-      <c r="T18">
-        <v>1</v>
-      </c>
-      <c r="U18">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V18">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W18">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X18">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y18">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z18">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA18">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB18">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC18">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD18">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE18">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF18">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG18">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH18">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI18">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ18">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK18">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL18">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM18">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN18">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO18">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP18">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ18">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR18">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS18">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT18">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU18">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV18">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW18">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX18">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY18">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ18">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA18">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB18">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC18">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:55">
-      <c r="A19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19">
-        <v>1.5</v>
-      </c>
-      <c r="I19">
-        <v>0.5</v>
-      </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19">
-        <v>1</v>
-      </c>
-      <c r="P19">
-        <v>1</v>
-      </c>
-      <c r="Q19">
-        <v>1</v>
-      </c>
-      <c r="R19">
-        <v>1</v>
-      </c>
-      <c r="S19">
-        <v>1</v>
-      </c>
-      <c r="T19">
-        <v>1</v>
-      </c>
-      <c r="U19">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V19">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W19">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X19">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y19">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z19">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA19">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB19">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC19">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD19">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE19">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF19">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG19">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH19">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI19">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ19">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK19">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL19">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM19">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN19">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO19">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP19">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ19">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR19">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS19">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT19">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU19">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV19">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW19">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX19">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY19">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ19">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA19">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB19">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC19">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:55">
-      <c r="A20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20">
-        <v>1.5</v>
-      </c>
-      <c r="I20">
-        <v>0.5</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
-      <c r="O20">
-        <v>1</v>
-      </c>
-      <c r="P20">
-        <v>1</v>
-      </c>
-      <c r="Q20">
-        <v>1</v>
-      </c>
-      <c r="R20">
-        <v>1</v>
-      </c>
-      <c r="S20">
-        <v>1</v>
-      </c>
-      <c r="T20">
-        <v>1</v>
-      </c>
-      <c r="U20">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V20">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W20">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X20">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y20">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z20">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA20">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB20">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC20">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD20">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE20">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF20">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG20">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH20">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI20">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ20">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK20">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL20">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM20">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN20">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO20">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP20">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ20">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR20">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS20">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT20">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU20">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV20">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW20">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX20">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY20">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ20">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA20">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB20">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC20">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:55">
-      <c r="A21" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21">
-        <v>1.5</v>
-      </c>
-      <c r="I21">
-        <v>0.5</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-      <c r="L21">
-        <v>1</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-      <c r="N21">
-        <v>1</v>
-      </c>
-      <c r="O21">
-        <v>1</v>
-      </c>
-      <c r="P21">
-        <v>1</v>
-      </c>
-      <c r="Q21">
-        <v>1</v>
-      </c>
-      <c r="R21">
-        <v>1</v>
-      </c>
-      <c r="S21">
-        <v>1</v>
-      </c>
-      <c r="T21">
-        <v>1</v>
-      </c>
-      <c r="U21">
-        <v>0.9914285714285714</v>
-      </c>
-      <c r="V21">
-        <v>0.9828571428571429</v>
-      </c>
-      <c r="W21">
-        <v>0.9742857142857142</v>
-      </c>
-      <c r="X21">
-        <v>0.9657142857142856</v>
-      </c>
-      <c r="Y21">
-        <v>0.9571428571428572</v>
-      </c>
-      <c r="Z21">
-        <v>0.9485714285714285</v>
-      </c>
-      <c r="AA21">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="AB21">
-        <v>0.9314285714285715</v>
-      </c>
-      <c r="AC21">
-        <v>0.9228571428571428</v>
-      </c>
-      <c r="AD21">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="AE21">
-        <v>0.9057142857142857</v>
-      </c>
-      <c r="AF21">
-        <v>0.8971428571428571</v>
-      </c>
-      <c r="AG21">
-        <v>0.8885714285714286</v>
-      </c>
-      <c r="AH21">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AI21">
-        <v>0.8714285714285714</v>
-      </c>
-      <c r="AJ21">
-        <v>0.8628571428571429</v>
-      </c>
-      <c r="AK21">
-        <v>0.8542857142857142</v>
-      </c>
-      <c r="AL21">
-        <v>0.8457142857142856</v>
-      </c>
-      <c r="AM21">
-        <v>0.8371428571428572</v>
-      </c>
-      <c r="AN21">
-        <v>0.8285714285714285</v>
-      </c>
-      <c r="AO21">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AP21">
-        <v>0.8114285714285714</v>
-      </c>
-      <c r="AQ21">
-        <v>0.8028571428571428</v>
-      </c>
-      <c r="AR21">
-        <v>0.7942857142857143</v>
-      </c>
-      <c r="AS21">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AT21">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="AU21">
-        <v>0.7685714285714286</v>
-      </c>
-      <c r="AV21">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="AW21">
-        <v>0.7514285714285713</v>
-      </c>
-      <c r="AX21">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="AY21">
-        <v>0.7342857142857142</v>
-      </c>
-      <c r="AZ21">
-        <v>0.7257142857142856</v>
-      </c>
-      <c r="BA21">
-        <v>0.7171428571428571</v>
-      </c>
-      <c r="BB21">
-        <v>0.7085714285714285</v>
-      </c>
-      <c r="BC21">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:55">
-      <c r="A22" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" t="s">
-        <v>168</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>0.75</v>
-      </c>
-      <c r="K22">
-        <v>0.75</v>
-      </c>
-      <c r="L22">
-        <v>0.75</v>
-      </c>
-      <c r="M22">
-        <v>0.75</v>
-      </c>
-      <c r="N22">
-        <v>0.75</v>
-      </c>
-      <c r="O22">
-        <v>0.75</v>
-      </c>
-      <c r="P22">
-        <v>0.75</v>
-      </c>
-      <c r="Q22">
-        <v>0.75</v>
-      </c>
-      <c r="R22">
-        <v>0.75</v>
-      </c>
-      <c r="S22">
-        <v>0.75</v>
-      </c>
-      <c r="T22">
-        <v>0.75</v>
-      </c>
-      <c r="U22">
-        <v>0.7428571428571428</v>
-      </c>
-      <c r="V22">
-        <v>0.7357142857142857</v>
-      </c>
-      <c r="W22">
-        <v>0.7285714285714285</v>
-      </c>
-      <c r="X22">
-        <v>0.7214285714285714</v>
-      </c>
-      <c r="Y22">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="Z22">
-        <v>0.7071428571428572</v>
-      </c>
-      <c r="AA22">
-        <v>0.7000000000000001</v>
-      </c>
-      <c r="AB22">
-        <v>0.6928571428571429</v>
-      </c>
-      <c r="AC22">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="AD22">
-        <v>0.6785714285714286</v>
-      </c>
-      <c r="AE22">
-        <v>0.6714285714285714</v>
-      </c>
-      <c r="AF22">
-        <v>0.6642857142857144</v>
-      </c>
-      <c r="AG22">
-        <v>0.6571428571428571</v>
-      </c>
-      <c r="AH22">
-        <v>0.6499999999999999</v>
-      </c>
-      <c r="AI22">
-        <v>0.6428571428571428</v>
-      </c>
-      <c r="AJ22">
-        <v>0.6357142857142858</v>
-      </c>
-      <c r="AK22">
-        <v>0.6285714285714286</v>
-      </c>
-      <c r="AL22">
-        <v>0.6214285714285714</v>
-      </c>
-      <c r="AM22">
-        <v>0.6142857142857143</v>
-      </c>
-      <c r="AN22">
-        <v>0.6071428571428572</v>
-      </c>
-      <c r="AO22">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="AP22">
-        <v>0.5928571428571429</v>
-      </c>
-      <c r="AQ22">
-        <v>0.5857142857142856</v>
-      </c>
-      <c r="AR22">
-        <v>0.5785714285714285</v>
-      </c>
-      <c r="AS22">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="AT22">
-        <v>0.5642857142857143</v>
-      </c>
-      <c r="AU22">
-        <v>0.5571428571428572</v>
-      </c>
-      <c r="AV22">
-        <v>0.55</v>
-      </c>
-      <c r="AW22">
-        <v>0.5428571428571428</v>
-      </c>
-      <c r="AX22">
-        <v>0.5357142857142857</v>
-      </c>
-      <c r="AY22">
-        <v>0.5285714285714286</v>
-      </c>
-      <c r="AZ22">
-        <v>0.5214285714285715</v>
-      </c>
-      <c r="BA22">
-        <v>0.5142857142857142</v>
-      </c>
-      <c r="BB22">
-        <v>0.5071428571428571</v>
-      </c>
-      <c r="BC22">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:55">
-      <c r="A23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" t="s">
-        <v>169</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0.02285714285714286</v>
-      </c>
-      <c r="V23">
-        <v>0.04571428571428571</v>
-      </c>
-      <c r="W23">
-        <v>0.06857142857142857</v>
-      </c>
-      <c r="X23">
-        <v>0.09142857142857143</v>
-      </c>
-      <c r="Y23">
-        <v>0.1142857142857143</v>
-      </c>
-      <c r="Z23">
-        <v>0.1371428571428571</v>
-      </c>
-      <c r="AA23">
-        <v>0.16</v>
-      </c>
-      <c r="AB23">
-        <v>0.1828571428571429</v>
-      </c>
-      <c r="AC23">
-        <v>0.2057142857142857</v>
-      </c>
-      <c r="AD23">
-        <v>0.2285714285714286</v>
-      </c>
-      <c r="AE23">
-        <v>0.2514285714285714</v>
-      </c>
-      <c r="AF23">
-        <v>0.2742857142857143</v>
-      </c>
-      <c r="AG23">
-        <v>0.2971428571428572</v>
-      </c>
-      <c r="AH23">
-        <v>0.3200000000000001</v>
-      </c>
-      <c r="AI23">
-        <v>0.3428571428571429</v>
-      </c>
-      <c r="AJ23">
-        <v>0.3657142857142857</v>
-      </c>
-      <c r="AK23">
-        <v>0.3885714285714286</v>
-      </c>
-      <c r="AL23">
-        <v>0.4114285714285714</v>
-      </c>
-      <c r="AM23">
-        <v>0.4342857142857143</v>
-      </c>
-      <c r="AN23">
-        <v>0.4571428571428571</v>
-      </c>
-      <c r="AO23">
-        <v>0.48</v>
-      </c>
-      <c r="AP23">
-        <v>0.5028571428571429</v>
-      </c>
-      <c r="AQ23">
-        <v>0.5257142857142857</v>
-      </c>
-      <c r="AR23">
-        <v>0.5485714285714286</v>
-      </c>
-      <c r="AS23">
-        <v>0.5714285714285715</v>
-      </c>
-      <c r="AT23">
-        <v>0.5942857142857143</v>
-      </c>
-      <c r="AU23">
-        <v>0.6171428571428572</v>
-      </c>
-      <c r="AV23">
-        <v>0.6400000000000001</v>
-      </c>
-      <c r="AW23">
-        <v>0.6628571428571429</v>
-      </c>
-      <c r="AX23">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="AY23">
-        <v>0.7085714285714286</v>
-      </c>
-      <c r="AZ23">
-        <v>0.7314285714285714</v>
-      </c>
-      <c r="BA23">
-        <v>0.7542857142857143</v>
-      </c>
-      <c r="BB23">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="BC23">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:55">
-      <c r="A24" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" t="s">
-        <v>170</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0.02285714285714286</v>
-      </c>
-      <c r="V24">
-        <v>0.04571428571428571</v>
-      </c>
-      <c r="W24">
-        <v>0.06857142857142857</v>
-      </c>
-      <c r="X24">
-        <v>0.09142857142857143</v>
-      </c>
-      <c r="Y24">
-        <v>0.1142857142857143</v>
-      </c>
-      <c r="Z24">
-        <v>0.1371428571428571</v>
-      </c>
-      <c r="AA24">
-        <v>0.16</v>
-      </c>
-      <c r="AB24">
-        <v>0.1828571428571429</v>
-      </c>
-      <c r="AC24">
-        <v>0.2057142857142857</v>
-      </c>
-      <c r="AD24">
-        <v>0.2285714285714286</v>
-      </c>
-      <c r="AE24">
-        <v>0.2514285714285714</v>
-      </c>
-      <c r="AF24">
-        <v>0.2742857142857143</v>
-      </c>
-      <c r="AG24">
-        <v>0.2971428571428572</v>
-      </c>
-      <c r="AH24">
-        <v>0.3200000000000001</v>
-      </c>
-      <c r="AI24">
-        <v>0.3428571428571429</v>
-      </c>
-      <c r="AJ24">
-        <v>0.3657142857142857</v>
-      </c>
-      <c r="AK24">
-        <v>0.3885714285714286</v>
-      </c>
-      <c r="AL24">
-        <v>0.4114285714285714</v>
-      </c>
-      <c r="AM24">
-        <v>0.4342857142857143</v>
-      </c>
-      <c r="AN24">
-        <v>0.4571428571428571</v>
-      </c>
-      <c r="AO24">
-        <v>0.48</v>
-      </c>
-      <c r="AP24">
-        <v>0.5028571428571429</v>
-      </c>
-      <c r="AQ24">
-        <v>0.5257142857142857</v>
-      </c>
-      <c r="AR24">
-        <v>0.5485714285714286</v>
-      </c>
-      <c r="AS24">
-        <v>0.5714285714285715</v>
-      </c>
-      <c r="AT24">
-        <v>0.5942857142857143</v>
-      </c>
-      <c r="AU24">
-        <v>0.6171428571428572</v>
-      </c>
-      <c r="AV24">
-        <v>0.6400000000000001</v>
-      </c>
-      <c r="AW24">
-        <v>0.6628571428571429</v>
-      </c>
-      <c r="AX24">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="AY24">
-        <v>0.7085714285714286</v>
-      </c>
-      <c r="AZ24">
-        <v>0.7314285714285714</v>
-      </c>
-      <c r="BA24">
-        <v>0.7542857142857143</v>
-      </c>
-      <c r="BB24">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="BC24">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:55">
-      <c r="A25" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" t="s">
-        <v>173</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0.02285714285714286</v>
-      </c>
-      <c r="V25">
-        <v>0.04571428571428571</v>
-      </c>
-      <c r="W25">
-        <v>0.06857142857142857</v>
-      </c>
-      <c r="X25">
-        <v>0.09142857142857143</v>
-      </c>
-      <c r="Y25">
-        <v>0.1142857142857143</v>
-      </c>
-      <c r="Z25">
-        <v>0.1371428571428571</v>
-      </c>
-      <c r="AA25">
-        <v>0.16</v>
-      </c>
-      <c r="AB25">
-        <v>0.1828571428571429</v>
-      </c>
-      <c r="AC25">
-        <v>0.2057142857142857</v>
-      </c>
-      <c r="AD25">
-        <v>0.2285714285714286</v>
-      </c>
-      <c r="AE25">
-        <v>0.2514285714285714</v>
-      </c>
-      <c r="AF25">
-        <v>0.2742857142857143</v>
-      </c>
-      <c r="AG25">
-        <v>0.2971428571428572</v>
-      </c>
-      <c r="AH25">
-        <v>0.3200000000000001</v>
-      </c>
-      <c r="AI25">
-        <v>0.3428571428571429</v>
-      </c>
-      <c r="AJ25">
-        <v>0.3657142857142857</v>
-      </c>
-      <c r="AK25">
-        <v>0.3885714285714286</v>
-      </c>
-      <c r="AL25">
-        <v>0.4114285714285714</v>
-      </c>
-      <c r="AM25">
-        <v>0.4342857142857143</v>
-      </c>
-      <c r="AN25">
-        <v>0.4571428571428571</v>
-      </c>
-      <c r="AO25">
-        <v>0.48</v>
-      </c>
-      <c r="AP25">
-        <v>0.5028571428571429</v>
-      </c>
-      <c r="AQ25">
-        <v>0.5257142857142857</v>
-      </c>
-      <c r="AR25">
-        <v>0.5485714285714286</v>
-      </c>
-      <c r="AS25">
-        <v>0.5714285714285715</v>
-      </c>
-      <c r="AT25">
-        <v>0.5942857142857143</v>
-      </c>
-      <c r="AU25">
-        <v>0.6171428571428572</v>
-      </c>
-      <c r="AV25">
-        <v>0.6400000000000001</v>
-      </c>
-      <c r="AW25">
-        <v>0.6628571428571429</v>
-      </c>
-      <c r="AX25">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="AY25">
-        <v>0.7085714285714286</v>
-      </c>
-      <c r="AZ25">
-        <v>0.7314285714285714</v>
-      </c>
-      <c r="BA25">
-        <v>0.7542857142857143</v>
-      </c>
-      <c r="BB25">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="BC25">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:55">
-      <c r="A26" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" t="s">
-        <v>174</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0.02285714285714286</v>
-      </c>
-      <c r="V26">
-        <v>0.04571428571428571</v>
-      </c>
-      <c r="W26">
-        <v>0.06857142857142857</v>
-      </c>
-      <c r="X26">
-        <v>0.09142857142857143</v>
-      </c>
-      <c r="Y26">
-        <v>0.1142857142857143</v>
-      </c>
-      <c r="Z26">
-        <v>0.1371428571428571</v>
-      </c>
-      <c r="AA26">
-        <v>0.16</v>
-      </c>
-      <c r="AB26">
-        <v>0.1828571428571429</v>
-      </c>
-      <c r="AC26">
-        <v>0.2057142857142857</v>
-      </c>
-      <c r="AD26">
-        <v>0.2285714285714286</v>
-      </c>
-      <c r="AE26">
-        <v>0.2514285714285714</v>
-      </c>
-      <c r="AF26">
-        <v>0.2742857142857143</v>
-      </c>
-      <c r="AG26">
-        <v>0.2971428571428572</v>
-      </c>
-      <c r="AH26">
-        <v>0.3200000000000001</v>
-      </c>
-      <c r="AI26">
-        <v>0.3428571428571429</v>
-      </c>
-      <c r="AJ26">
-        <v>0.3657142857142857</v>
-      </c>
-      <c r="AK26">
-        <v>0.3885714285714286</v>
-      </c>
-      <c r="AL26">
-        <v>0.4114285714285714</v>
-      </c>
-      <c r="AM26">
-        <v>0.4342857142857143</v>
-      </c>
-      <c r="AN26">
-        <v>0.4571428571428571</v>
-      </c>
-      <c r="AO26">
-        <v>0.48</v>
-      </c>
-      <c r="AP26">
-        <v>0.5028571428571429</v>
-      </c>
-      <c r="AQ26">
-        <v>0.5257142857142857</v>
-      </c>
-      <c r="AR26">
-        <v>0.5485714285714286</v>
-      </c>
-      <c r="AS26">
-        <v>0.5714285714285715</v>
-      </c>
-      <c r="AT26">
-        <v>0.5942857142857143</v>
-      </c>
-      <c r="AU26">
-        <v>0.6171428571428572</v>
-      </c>
-      <c r="AV26">
-        <v>0.6400000000000001</v>
-      </c>
-      <c r="AW26">
-        <v>0.6628571428571429</v>
-      </c>
-      <c r="AX26">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="AY26">
-        <v>0.7085714285714286</v>
-      </c>
-      <c r="AZ26">
-        <v>0.7314285714285714</v>
-      </c>
-      <c r="BA26">
-        <v>0.7542857142857143</v>
-      </c>
-      <c r="BB26">
-        <v>0.7771428571428571</v>
-      </c>
-      <c r="BC26">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:55">
-      <c r="A27" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" t="s">
-        <v>175</v>
-      </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="J27">
-        <v>0.9</v>
-      </c>
-      <c r="K27">
-        <v>0.9</v>
-      </c>
-      <c r="L27">
-        <v>0.9</v>
-      </c>
-      <c r="M27">
-        <v>0.9</v>
-      </c>
-      <c r="N27">
-        <v>0.9</v>
-      </c>
-      <c r="O27">
-        <v>0.9</v>
-      </c>
-      <c r="P27">
-        <v>0.9</v>
-      </c>
-      <c r="Q27">
-        <v>0.9</v>
-      </c>
-      <c r="R27">
-        <v>0.9</v>
-      </c>
-      <c r="S27">
-        <v>0.9</v>
-      </c>
-      <c r="T27">
-        <v>0.9</v>
-      </c>
-      <c r="U27">
-        <v>0.9</v>
-      </c>
-      <c r="V27">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="W27">
-        <v>0.9</v>
-      </c>
-      <c r="X27">
-        <v>0.9</v>
-      </c>
-      <c r="Y27">
-        <v>0.9</v>
-      </c>
-      <c r="Z27">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AA27">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AB27">
-        <v>0.9</v>
-      </c>
-      <c r="AC27">
-        <v>0.9</v>
-      </c>
-      <c r="AD27">
-        <v>0.9</v>
-      </c>
-      <c r="AE27">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AF27">
-        <v>0.9</v>
-      </c>
-      <c r="AG27">
-        <v>0.9</v>
-      </c>
-      <c r="AH27">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AI27">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AJ27">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AK27">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AL27">
-        <v>0.9</v>
-      </c>
-      <c r="AM27">
-        <v>0.9</v>
-      </c>
-      <c r="AN27">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AO27">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AP27">
-        <v>0.9</v>
-      </c>
-      <c r="AQ27">
-        <v>0.9</v>
-      </c>
-      <c r="AR27">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AS27">
-        <v>0.9</v>
-      </c>
-      <c r="AT27">
-        <v>0.9</v>
-      </c>
-      <c r="AU27">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AV27">
-        <v>0.9</v>
-      </c>
-      <c r="AW27">
-        <v>0.9</v>
-      </c>
-      <c r="AX27">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AY27">
-        <v>0.9</v>
-      </c>
-      <c r="AZ27">
-        <v>0.9</v>
-      </c>
-      <c r="BA27">
-        <v>0.9</v>
-      </c>
-      <c r="BB27">
-        <v>0.9</v>
-      </c>
-      <c r="BC27">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:55">
-      <c r="A28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" t="s">
-        <v>176</v>
-      </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="I28">
-        <v>1</v>
-      </c>
-      <c r="J28">
-        <v>0.9</v>
-      </c>
-      <c r="K28">
-        <v>0.9</v>
-      </c>
-      <c r="L28">
-        <v>0.9</v>
-      </c>
-      <c r="M28">
-        <v>0.9</v>
-      </c>
-      <c r="N28">
-        <v>0.9</v>
-      </c>
-      <c r="O28">
-        <v>0.9</v>
-      </c>
-      <c r="P28">
-        <v>0.9</v>
-      </c>
-      <c r="Q28">
-        <v>0.9</v>
-      </c>
-      <c r="R28">
-        <v>0.9</v>
-      </c>
-      <c r="S28">
-        <v>0.9</v>
-      </c>
-      <c r="T28">
-        <v>0.9</v>
-      </c>
-      <c r="U28">
-        <v>0.9</v>
-      </c>
-      <c r="V28">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="W28">
-        <v>0.9</v>
-      </c>
-      <c r="X28">
-        <v>0.9</v>
-      </c>
-      <c r="Y28">
-        <v>0.9</v>
-      </c>
-      <c r="Z28">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AA28">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AB28">
-        <v>0.9</v>
-      </c>
-      <c r="AC28">
-        <v>0.9</v>
-      </c>
-      <c r="AD28">
-        <v>0.9</v>
-      </c>
-      <c r="AE28">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AF28">
-        <v>0.9</v>
-      </c>
-      <c r="AG28">
-        <v>0.9</v>
-      </c>
-      <c r="AH28">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AI28">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AJ28">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AK28">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AL28">
-        <v>0.9</v>
-      </c>
-      <c r="AM28">
-        <v>0.9</v>
-      </c>
-      <c r="AN28">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AO28">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AP28">
-        <v>0.9</v>
-      </c>
-      <c r="AQ28">
-        <v>0.9</v>
-      </c>
-      <c r="AR28">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AS28">
-        <v>0.9</v>
-      </c>
-      <c r="AT28">
-        <v>0.9</v>
-      </c>
-      <c r="AU28">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AV28">
-        <v>0.9</v>
-      </c>
-      <c r="AW28">
-        <v>0.9</v>
-      </c>
-      <c r="AX28">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AY28">
-        <v>0.9</v>
-      </c>
-      <c r="AZ28">
-        <v>0.9</v>
-      </c>
-      <c r="BA28">
-        <v>0.9</v>
-      </c>
-      <c r="BB28">
-        <v>0.9</v>
-      </c>
-      <c r="BC28">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:55">
-      <c r="A29" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" t="s">
-        <v>177</v>
-      </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-      <c r="J29">
-        <v>0.9</v>
-      </c>
-      <c r="K29">
-        <v>0.9</v>
-      </c>
-      <c r="L29">
-        <v>0.9</v>
-      </c>
-      <c r="M29">
-        <v>0.9</v>
-      </c>
-      <c r="N29">
-        <v>0.9</v>
-      </c>
-      <c r="O29">
-        <v>0.9</v>
-      </c>
-      <c r="P29">
-        <v>0.9</v>
-      </c>
-      <c r="Q29">
-        <v>0.9</v>
-      </c>
-      <c r="R29">
-        <v>0.9</v>
-      </c>
-      <c r="S29">
-        <v>0.9</v>
-      </c>
-      <c r="T29">
-        <v>0.9</v>
-      </c>
-      <c r="U29">
-        <v>0.9</v>
-      </c>
-      <c r="V29">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="W29">
-        <v>0.9</v>
-      </c>
-      <c r="X29">
-        <v>0.9</v>
-      </c>
-      <c r="Y29">
-        <v>0.9</v>
-      </c>
-      <c r="Z29">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AA29">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AB29">
-        <v>0.9</v>
-      </c>
-      <c r="AC29">
-        <v>0.9</v>
-      </c>
-      <c r="AD29">
-        <v>0.9</v>
-      </c>
-      <c r="AE29">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AF29">
-        <v>0.9</v>
-      </c>
-      <c r="AG29">
-        <v>0.9</v>
-      </c>
-      <c r="AH29">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AI29">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AJ29">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AK29">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AL29">
-        <v>0.9</v>
-      </c>
-      <c r="AM29">
-        <v>0.9</v>
-      </c>
-      <c r="AN29">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AO29">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AP29">
-        <v>0.9</v>
-      </c>
-      <c r="AQ29">
-        <v>0.9</v>
-      </c>
-      <c r="AR29">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AS29">
-        <v>0.9</v>
-      </c>
-      <c r="AT29">
-        <v>0.9</v>
-      </c>
-      <c r="AU29">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AV29">
-        <v>0.9</v>
-      </c>
-      <c r="AW29">
-        <v>0.9</v>
-      </c>
-      <c r="AX29">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AY29">
-        <v>0.9</v>
-      </c>
-      <c r="AZ29">
-        <v>0.9</v>
-      </c>
-      <c r="BA29">
-        <v>0.9</v>
-      </c>
-      <c r="BB29">
-        <v>0.9</v>
-      </c>
-      <c r="BC29">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:55">
-      <c r="A30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" t="s">
-        <v>178</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-      <c r="J30">
-        <v>0.9</v>
-      </c>
-      <c r="K30">
-        <v>0.9</v>
-      </c>
-      <c r="L30">
-        <v>0.9</v>
-      </c>
-      <c r="M30">
-        <v>0.9</v>
-      </c>
-      <c r="N30">
-        <v>0.9</v>
-      </c>
-      <c r="O30">
-        <v>0.9</v>
-      </c>
-      <c r="P30">
-        <v>0.9</v>
-      </c>
-      <c r="Q30">
-        <v>0.9</v>
-      </c>
-      <c r="R30">
-        <v>0.9</v>
-      </c>
-      <c r="S30">
-        <v>0.9</v>
-      </c>
-      <c r="T30">
-        <v>0.9</v>
-      </c>
-      <c r="U30">
-        <v>0.9</v>
-      </c>
-      <c r="V30">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="W30">
-        <v>0.9</v>
-      </c>
-      <c r="X30">
-        <v>0.9</v>
-      </c>
-      <c r="Y30">
-        <v>0.9</v>
-      </c>
-      <c r="Z30">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AA30">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AB30">
-        <v>0.9</v>
-      </c>
-      <c r="AC30">
-        <v>0.9</v>
-      </c>
-      <c r="AD30">
-        <v>0.9</v>
-      </c>
-      <c r="AE30">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AF30">
-        <v>0.9</v>
-      </c>
-      <c r="AG30">
-        <v>0.9</v>
-      </c>
-      <c r="AH30">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AI30">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AJ30">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AK30">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AL30">
-        <v>0.9</v>
-      </c>
-      <c r="AM30">
-        <v>0.9</v>
-      </c>
-      <c r="AN30">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AO30">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AP30">
-        <v>0.9</v>
-      </c>
-      <c r="AQ30">
-        <v>0.9</v>
-      </c>
-      <c r="AR30">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AS30">
-        <v>0.9</v>
-      </c>
-      <c r="AT30">
-        <v>0.9</v>
-      </c>
-      <c r="AU30">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AV30">
-        <v>0.9</v>
-      </c>
-      <c r="AW30">
-        <v>0.9</v>
-      </c>
-      <c r="AX30">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AY30">
-        <v>0.9</v>
-      </c>
-      <c r="AZ30">
-        <v>0.9</v>
-      </c>
-      <c r="BA30">
-        <v>0.9</v>
-      </c>
-      <c r="BB30">
-        <v>0.9</v>
-      </c>
-      <c r="BC30">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:55">
-      <c r="A31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" t="s">
-        <v>179</v>
-      </c>
-      <c r="H31">
-        <v>1</v>
-      </c>
-      <c r="I31">
-        <v>1</v>
-      </c>
-      <c r="J31">
-        <v>0.9</v>
-      </c>
-      <c r="K31">
-        <v>0.9</v>
-      </c>
-      <c r="L31">
-        <v>0.9</v>
-      </c>
-      <c r="M31">
-        <v>0.9</v>
-      </c>
-      <c r="N31">
-        <v>0.9</v>
-      </c>
-      <c r="O31">
-        <v>0.9</v>
-      </c>
-      <c r="P31">
-        <v>0.9</v>
-      </c>
-      <c r="Q31">
-        <v>0.9</v>
-      </c>
-      <c r="R31">
-        <v>0.9</v>
-      </c>
-      <c r="S31">
-        <v>0.9</v>
-      </c>
-      <c r="T31">
-        <v>0.9</v>
-      </c>
-      <c r="U31">
-        <v>0.9</v>
-      </c>
-      <c r="V31">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="W31">
-        <v>0.9</v>
-      </c>
-      <c r="X31">
-        <v>0.9</v>
-      </c>
-      <c r="Y31">
-        <v>0.9</v>
-      </c>
-      <c r="Z31">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AA31">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AB31">
-        <v>0.9</v>
-      </c>
-      <c r="AC31">
-        <v>0.9</v>
-      </c>
-      <c r="AD31">
-        <v>0.9</v>
-      </c>
-      <c r="AE31">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AF31">
-        <v>0.9</v>
-      </c>
-      <c r="AG31">
-        <v>0.9</v>
-      </c>
-      <c r="AH31">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AI31">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AJ31">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AK31">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AL31">
-        <v>0.9</v>
-      </c>
-      <c r="AM31">
-        <v>0.9</v>
-      </c>
-      <c r="AN31">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AO31">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AP31">
-        <v>0.9</v>
-      </c>
-      <c r="AQ31">
-        <v>0.9</v>
-      </c>
-      <c r="AR31">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AS31">
-        <v>0.9</v>
-      </c>
-      <c r="AT31">
-        <v>0.9</v>
-      </c>
-      <c r="AU31">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AV31">
-        <v>0.9</v>
-      </c>
-      <c r="AW31">
-        <v>0.9</v>
-      </c>
-      <c r="AX31">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AY31">
-        <v>0.9</v>
-      </c>
-      <c r="AZ31">
-        <v>0.9</v>
-      </c>
-      <c r="BA31">
-        <v>0.9</v>
-      </c>
-      <c r="BB31">
-        <v>0.9</v>
-      </c>
-      <c r="BC31">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:55">
-      <c r="A32" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" t="s">
-        <v>180</v>
-      </c>
-      <c r="H32">
-        <v>1</v>
-      </c>
-      <c r="I32">
-        <v>1</v>
-      </c>
-      <c r="J32">
-        <v>0.9</v>
-      </c>
-      <c r="K32">
-        <v>0.9</v>
-      </c>
-      <c r="L32">
-        <v>0.9</v>
-      </c>
-      <c r="M32">
-        <v>0.9</v>
-      </c>
-      <c r="N32">
-        <v>0.9</v>
-      </c>
-      <c r="O32">
-        <v>0.9</v>
-      </c>
-      <c r="P32">
-        <v>0.9</v>
-      </c>
-      <c r="Q32">
-        <v>0.9</v>
-      </c>
-      <c r="R32">
-        <v>0.9</v>
-      </c>
-      <c r="S32">
-        <v>0.9</v>
-      </c>
-      <c r="T32">
-        <v>0.9</v>
-      </c>
-      <c r="U32">
-        <v>0.9</v>
-      </c>
-      <c r="V32">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="W32">
-        <v>0.9</v>
-      </c>
-      <c r="X32">
-        <v>0.9</v>
-      </c>
-      <c r="Y32">
-        <v>0.9</v>
-      </c>
-      <c r="Z32">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AA32">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AB32">
-        <v>0.9</v>
-      </c>
-      <c r="AC32">
-        <v>0.9</v>
-      </c>
-      <c r="AD32">
-        <v>0.9</v>
-      </c>
-      <c r="AE32">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AF32">
-        <v>0.9</v>
-      </c>
-      <c r="AG32">
-        <v>0.9</v>
-      </c>
-      <c r="AH32">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AI32">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AJ32">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AK32">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AL32">
-        <v>0.9</v>
-      </c>
-      <c r="AM32">
-        <v>0.9</v>
-      </c>
-      <c r="AN32">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AO32">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AP32">
-        <v>0.9</v>
-      </c>
-      <c r="AQ32">
-        <v>0.9</v>
-      </c>
-      <c r="AR32">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AS32">
-        <v>0.9</v>
-      </c>
-      <c r="AT32">
-        <v>0.9</v>
-      </c>
-      <c r="AU32">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AV32">
-        <v>0.9</v>
-      </c>
-      <c r="AW32">
-        <v>0.9</v>
-      </c>
-      <c r="AX32">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="AY32">
-        <v>0.9</v>
-      </c>
-      <c r="AZ32">
-        <v>0.9</v>
-      </c>
-      <c r="BA32">
-        <v>0.9</v>
-      </c>
-      <c r="BB32">
-        <v>0.9</v>
-      </c>
-      <c r="BC32">
-        <v>0.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/ssp_modeling/transformations/templates/calibrated/mexico/model_input_variables_mexico_ip_calibrated.xlsx
+++ b/ssp_modeling/transformations/templates/calibrated/mexico/model_input_variables_mexico_ip_calibrated.xlsx
@@ -32805,109 +32805,109 @@
         <v>0.273680173</v>
       </c>
       <c r="U22">
-        <v>0.26546976781</v>
+        <v>0.261364565215</v>
       </c>
       <c r="V22">
-        <v>0.25725936262</v>
+        <v>0.24904895743</v>
       </c>
       <c r="W22">
-        <v>0.24904895743</v>
+        <v>0.236733349645</v>
       </c>
       <c r="X22">
-        <v>0.2408385522400001</v>
+        <v>0.22441774186</v>
       </c>
       <c r="Y22">
-        <v>0.23262814705</v>
+        <v>0.212102134075</v>
       </c>
       <c r="Z22">
-        <v>0.22441774186</v>
+        <v>0.19978652629</v>
       </c>
       <c r="AA22">
-        <v>0.21620733667</v>
+        <v>0.187470918505</v>
       </c>
       <c r="AB22">
-        <v>0.20799693148</v>
+        <v>0.17515531072</v>
       </c>
       <c r="AC22">
-        <v>0.19978652629</v>
+        <v>0.1628397029350001</v>
       </c>
       <c r="AD22">
-        <v>0.1915761211</v>
+        <v>0.15052409515</v>
       </c>
       <c r="AE22">
-        <v>0.18336571591</v>
+        <v>0.138208487365</v>
       </c>
       <c r="AF22">
-        <v>0.17515531072</v>
+        <v>0.12589287958</v>
       </c>
       <c r="AG22">
-        <v>0.16694490553</v>
+        <v>0.113577271795</v>
       </c>
       <c r="AH22">
-        <v>0.15873450034</v>
+        <v>0.10126166401</v>
       </c>
       <c r="AI22">
-        <v>0.15052409515</v>
+        <v>0.08894605622500001</v>
       </c>
       <c r="AJ22">
-        <v>0.14231368996</v>
+        <v>0.07663044844</v>
       </c>
       <c r="AK22">
-        <v>0.13410328477</v>
+        <v>0.06431484065500001</v>
       </c>
       <c r="AL22">
-        <v>0.12589287958</v>
+        <v>0.05199923287</v>
       </c>
       <c r="AM22">
-        <v>0.11768247439</v>
+        <v>0.03968362508500002</v>
       </c>
       <c r="AN22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
       <c r="AO22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
       <c r="AP22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
       <c r="AQ22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
       <c r="AR22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
       <c r="AS22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
       <c r="AT22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
       <c r="AU22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
       <c r="AV22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
       <c r="AW22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
       <c r="AX22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
       <c r="AY22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
       <c r="AZ22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
       <c r="BA22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
       <c r="BB22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
       <c r="BC22">
-        <v>0.1094720692</v>
+        <v>0.02736801730000001</v>
       </c>
     </row>
     <row r="23" spans="1:55">
@@ -32957,109 +32957,109 @@
         <v>0.187179706</v>
       </c>
       <c r="U23">
-        <v>0.18156431482</v>
+        <v>0.17875661923</v>
       </c>
       <c r="V23">
-        <v>0.17594892364</v>
+        <v>0.17033353246</v>
       </c>
       <c r="W23">
-        <v>0.17033353246</v>
+        <v>0.16191044569</v>
       </c>
       <c r="X23">
-        <v>0.16471814128</v>
+        <v>0.15348735892</v>
       </c>
       <c r="Y23">
-        <v>0.1591027501</v>
+        <v>0.14506427215</v>
       </c>
       <c r="Z23">
-        <v>0.15348735892</v>
+        <v>0.13664118538</v>
       </c>
       <c r="AA23">
-        <v>0.14787196774</v>
+        <v>0.12821809861</v>
       </c>
       <c r="AB23">
-        <v>0.14225657656</v>
+        <v>0.11979501184</v>
       </c>
       <c r="AC23">
-        <v>0.13664118538</v>
+        <v>0.11137192507</v>
       </c>
       <c r="AD23">
-        <v>0.1310257942</v>
+        <v>0.1029488383</v>
       </c>
       <c r="AE23">
-        <v>0.12541040302</v>
+        <v>0.09452575152999999</v>
       </c>
       <c r="AF23">
-        <v>0.11979501184</v>
+        <v>0.08610266476</v>
       </c>
       <c r="AG23">
-        <v>0.11417962066</v>
+        <v>0.07767957799</v>
       </c>
       <c r="AH23">
-        <v>0.10856422948</v>
+        <v>0.06925649122000001</v>
       </c>
       <c r="AI23">
-        <v>0.1029488383</v>
+        <v>0.06083340445</v>
       </c>
       <c r="AJ23">
-        <v>0.09733344712</v>
+        <v>0.05241031767999999</v>
       </c>
       <c r="AK23">
-        <v>0.09171805594000002</v>
+        <v>0.04398723091000001</v>
       </c>
       <c r="AL23">
-        <v>0.08610266476</v>
+        <v>0.03556414414</v>
       </c>
       <c r="AM23">
-        <v>0.08048727358000002</v>
+        <v>0.02714105737000001</v>
       </c>
       <c r="AN23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AO23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AP23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AQ23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AR23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AS23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AT23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AU23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AV23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AW23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AX23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AY23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AZ23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="BA23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="BB23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="BC23">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
     </row>
     <row r="24" spans="1:55">
@@ -33109,109 +33109,109 @@
         <v>0.187179706</v>
       </c>
       <c r="U24">
-        <v>0.18156431482</v>
+        <v>0.17875661923</v>
       </c>
       <c r="V24">
-        <v>0.17594892364</v>
+        <v>0.17033353246</v>
       </c>
       <c r="W24">
-        <v>0.17033353246</v>
+        <v>0.16191044569</v>
       </c>
       <c r="X24">
-        <v>0.16471814128</v>
+        <v>0.15348735892</v>
       </c>
       <c r="Y24">
-        <v>0.1591027501</v>
+        <v>0.14506427215</v>
       </c>
       <c r="Z24">
-        <v>0.15348735892</v>
+        <v>0.13664118538</v>
       </c>
       <c r="AA24">
-        <v>0.14787196774</v>
+        <v>0.12821809861</v>
       </c>
       <c r="AB24">
-        <v>0.14225657656</v>
+        <v>0.11979501184</v>
       </c>
       <c r="AC24">
-        <v>0.13664118538</v>
+        <v>0.11137192507</v>
       </c>
       <c r="AD24">
-        <v>0.1310257942</v>
+        <v>0.1029488383</v>
       </c>
       <c r="AE24">
-        <v>0.12541040302</v>
+        <v>0.09452575152999999</v>
       </c>
       <c r="AF24">
-        <v>0.11979501184</v>
+        <v>0.08610266476</v>
       </c>
       <c r="AG24">
-        <v>0.11417962066</v>
+        <v>0.07767957799</v>
       </c>
       <c r="AH24">
-        <v>0.10856422948</v>
+        <v>0.06925649122000001</v>
       </c>
       <c r="AI24">
-        <v>0.1029488383</v>
+        <v>0.06083340445</v>
       </c>
       <c r="AJ24">
-        <v>0.09733344712</v>
+        <v>0.05241031767999999</v>
       </c>
       <c r="AK24">
-        <v>0.09171805594000002</v>
+        <v>0.04398723091000001</v>
       </c>
       <c r="AL24">
-        <v>0.08610266476</v>
+        <v>0.03556414414</v>
       </c>
       <c r="AM24">
-        <v>0.08048727358000002</v>
+        <v>0.02714105737000001</v>
       </c>
       <c r="AN24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AO24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AP24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AQ24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AR24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AS24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AT24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AU24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AV24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AW24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AX24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AY24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="AZ24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="BA24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="BB24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
       <c r="BC24">
-        <v>0.07487188240000001</v>
+        <v>0.0187179706</v>
       </c>
     </row>
     <row r="25" spans="1:55">
@@ -33261,109 +33261,109 @@
         <v>0.141458864</v>
       </c>
       <c r="U25">
-        <v>0.13721509808</v>
+        <v>0.13509321512</v>
       </c>
       <c r="V25">
-        <v>0.13297133216</v>
+        <v>0.12872756624</v>
       </c>
       <c r="W25">
-        <v>0.12872756624</v>
+        <v>0.12236191736</v>
       </c>
       <c r="X25">
-        <v>0.12448380032</v>
+        <v>0.11599626848</v>
       </c>
       <c r="Y25">
-        <v>0.1202400344</v>
+        <v>0.1096306196</v>
       </c>
       <c r="Z25">
-        <v>0.11599626848</v>
+        <v>0.10326497072</v>
       </c>
       <c r="AA25">
-        <v>0.11175250256</v>
+        <v>0.09689932184</v>
       </c>
       <c r="AB25">
-        <v>0.10750873664</v>
+        <v>0.09053367295999999</v>
       </c>
       <c r="AC25">
-        <v>0.10326497072</v>
+        <v>0.08416802408</v>
       </c>
       <c r="AD25">
-        <v>0.0990212048</v>
+        <v>0.0778023752</v>
       </c>
       <c r="AE25">
-        <v>0.09477743888</v>
+        <v>0.07143672631999999</v>
       </c>
       <c r="AF25">
-        <v>0.09053367296000001</v>
+        <v>0.06507107744</v>
       </c>
       <c r="AG25">
-        <v>0.08628990704</v>
+        <v>0.05870542855999999</v>
       </c>
       <c r="AH25">
-        <v>0.08204614112</v>
+        <v>0.05233977968</v>
       </c>
       <c r="AI25">
-        <v>0.0778023752</v>
+        <v>0.0459741308</v>
       </c>
       <c r="AJ25">
-        <v>0.07355860927999999</v>
+        <v>0.03960848191999999</v>
       </c>
       <c r="AK25">
-        <v>0.06931484336</v>
+        <v>0.03324283304</v>
       </c>
       <c r="AL25">
-        <v>0.06507107744</v>
+        <v>0.02687718416</v>
       </c>
       <c r="AM25">
-        <v>0.06082731152</v>
+        <v>0.02051153528000001</v>
       </c>
       <c r="AN25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AO25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AP25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AQ25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AR25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AS25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AT25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AU25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AV25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AW25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AX25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AY25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AZ25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="BA25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="BB25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="BC25">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
     </row>
     <row r="26" spans="1:55">
@@ -33413,109 +33413,109 @@
         <v>0.141458864</v>
       </c>
       <c r="U26">
-        <v>0.13721509808</v>
+        <v>0.13509321512</v>
       </c>
       <c r="V26">
-        <v>0.13297133216</v>
+        <v>0.12872756624</v>
       </c>
       <c r="W26">
-        <v>0.12872756624</v>
+        <v>0.12236191736</v>
       </c>
       <c r="X26">
-        <v>0.12448380032</v>
+        <v>0.11599626848</v>
       </c>
       <c r="Y26">
-        <v>0.1202400344</v>
+        <v>0.1096306196</v>
       </c>
       <c r="Z26">
-        <v>0.11599626848</v>
+        <v>0.10326497072</v>
       </c>
       <c r="AA26">
-        <v>0.11175250256</v>
+        <v>0.09689932184</v>
       </c>
       <c r="AB26">
-        <v>0.10750873664</v>
+        <v>0.09053367295999999</v>
       </c>
       <c r="AC26">
-        <v>0.10326497072</v>
+        <v>0.08416802408</v>
       </c>
       <c r="AD26">
-        <v>0.0990212048</v>
+        <v>0.0778023752</v>
       </c>
       <c r="AE26">
-        <v>0.09477743888</v>
+        <v>0.07143672631999999</v>
       </c>
       <c r="AF26">
-        <v>0.09053367296000001</v>
+        <v>0.06507107744</v>
       </c>
       <c r="AG26">
-        <v>0.08628990704</v>
+        <v>0.05870542855999999</v>
       </c>
       <c r="AH26">
-        <v>0.08204614112</v>
+        <v>0.05233977968</v>
       </c>
       <c r="AI26">
-        <v>0.0778023752</v>
+        <v>0.0459741308</v>
       </c>
       <c r="AJ26">
-        <v>0.07355860927999999</v>
+        <v>0.03960848191999999</v>
       </c>
       <c r="AK26">
-        <v>0.06931484336</v>
+        <v>0.03324283304</v>
       </c>
       <c r="AL26">
-        <v>0.06507107744</v>
+        <v>0.02687718416</v>
       </c>
       <c r="AM26">
-        <v>0.06082731152</v>
+        <v>0.02051153528000001</v>
       </c>
       <c r="AN26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AO26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AP26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AQ26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AR26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AS26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AT26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AU26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AV26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AW26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AX26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AY26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="AZ26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="BA26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="BB26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
       <c r="BC26">
-        <v>0.0565835456</v>
+        <v>0.0141458864</v>
       </c>
     </row>
     <row r="27" spans="1:55">
@@ -33565,109 +33565,109 @@
         <v>0.028164596</v>
       </c>
       <c r="U27">
-        <v>0.02731965812</v>
+        <v>0.02689718918</v>
       </c>
       <c r="V27">
-        <v>0.02647472024</v>
+        <v>0.02562978236</v>
       </c>
       <c r="W27">
-        <v>0.02562978236</v>
+        <v>0.02436237554</v>
       </c>
       <c r="X27">
-        <v>0.02478484448</v>
+        <v>0.02309496872</v>
       </c>
       <c r="Y27">
-        <v>0.0239399066</v>
+        <v>0.0218275619</v>
       </c>
       <c r="Z27">
-        <v>0.02309496872</v>
+        <v>0.02056015508</v>
       </c>
       <c r="AA27">
-        <v>0.02225003084</v>
+        <v>0.01929274826</v>
       </c>
       <c r="AB27">
-        <v>0.02140509296</v>
+        <v>0.01802534144</v>
       </c>
       <c r="AC27">
-        <v>0.02056015508</v>
+        <v>0.01675793462</v>
       </c>
       <c r="AD27">
-        <v>0.0197152172</v>
+        <v>0.0154905278</v>
       </c>
       <c r="AE27">
-        <v>0.01887027932</v>
+        <v>0.01422312098</v>
       </c>
       <c r="AF27">
-        <v>0.01802534144</v>
+        <v>0.01295571416</v>
       </c>
       <c r="AG27">
-        <v>0.01718040356</v>
+        <v>0.01168830734</v>
       </c>
       <c r="AH27">
-        <v>0.01633546568</v>
+        <v>0.01042090052</v>
       </c>
       <c r="AI27">
-        <v>0.0154905278</v>
+        <v>0.009153493700000001</v>
       </c>
       <c r="AJ27">
-        <v>0.01464558992</v>
+        <v>0.007886086879999999</v>
       </c>
       <c r="AK27">
-        <v>0.01380065204</v>
+        <v>0.00661868006</v>
       </c>
       <c r="AL27">
-        <v>0.01295571416</v>
+        <v>0.005351273239999999</v>
       </c>
       <c r="AM27">
-        <v>0.01211077628</v>
+        <v>0.004083866420000001</v>
       </c>
       <c r="AN27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
       <c r="AO27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
       <c r="AP27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
       <c r="AQ27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
       <c r="AR27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
       <c r="AS27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
       <c r="AT27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
       <c r="AU27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
       <c r="AV27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
       <c r="AW27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
       <c r="AX27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
       <c r="AY27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
       <c r="AZ27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
       <c r="BA27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
       <c r="BB27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
       <c r="BC27">
-        <v>0.0112658384</v>
+        <v>0.0028164596</v>
       </c>
     </row>
     <row r="28" spans="1:55">
@@ -33717,109 +33717,109 @@
         <v>0.004187006</v>
       </c>
       <c r="U28">
-        <v>0.00406139582</v>
+        <v>0.003998590729999999</v>
       </c>
       <c r="V28">
-        <v>0.00393578564</v>
+        <v>0.00381017546</v>
       </c>
       <c r="W28">
-        <v>0.00381017546</v>
+        <v>0.00362176019</v>
       </c>
       <c r="X28">
-        <v>0.003684565280000001</v>
+        <v>0.00343334492</v>
       </c>
       <c r="Y28">
-        <v>0.0035589551</v>
+        <v>0.00324492965</v>
       </c>
       <c r="Z28">
-        <v>0.00343334492</v>
+        <v>0.00305651438</v>
       </c>
       <c r="AA28">
-        <v>0.00330773474</v>
+        <v>0.00286809911</v>
       </c>
       <c r="AB28">
-        <v>0.00318212456</v>
+        <v>0.00267968384</v>
       </c>
       <c r="AC28">
-        <v>0.00305651438</v>
+        <v>0.00249126857</v>
       </c>
       <c r="AD28">
-        <v>0.0029309042</v>
+        <v>0.0023028533</v>
       </c>
       <c r="AE28">
-        <v>0.00280529402</v>
+        <v>0.00211443803</v>
       </c>
       <c r="AF28">
-        <v>0.00267968384</v>
+        <v>0.00192602276</v>
       </c>
       <c r="AG28">
-        <v>0.00255407366</v>
+        <v>0.00173760749</v>
       </c>
       <c r="AH28">
-        <v>0.00242846348</v>
+        <v>0.00154919222</v>
       </c>
       <c r="AI28">
-        <v>0.0023028533</v>
+        <v>0.00136077695</v>
       </c>
       <c r="AJ28">
-        <v>0.00217724312</v>
+        <v>0.00117236168</v>
       </c>
       <c r="AK28">
-        <v>0.00205163294</v>
+        <v>0.0009839464100000002</v>
       </c>
       <c r="AL28">
-        <v>0.00192602276</v>
+        <v>0.00079553114</v>
       </c>
       <c r="AM28">
-        <v>0.00180041258</v>
+        <v>0.0006071158700000002</v>
       </c>
       <c r="AN28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
       <c r="AO28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
       <c r="AP28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
       <c r="AQ28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
       <c r="AR28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
       <c r="AS28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
       <c r="AT28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
       <c r="AU28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
       <c r="AV28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
       <c r="AW28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
       <c r="AX28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
       <c r="AY28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
       <c r="AZ28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
       <c r="BA28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
       <c r="BB28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
       <c r="BC28">
-        <v>0.0016748024</v>
+        <v>0.0004187006</v>
       </c>
     </row>
     <row r="29" spans="1:55">
@@ -33869,109 +33869,109 @@
         <v>0.142656839</v>
       </c>
       <c r="U29">
-        <v>0.13837713383</v>
+        <v>0.136237281245</v>
       </c>
       <c r="V29">
-        <v>0.13409742866</v>
+        <v>0.12981772349</v>
       </c>
       <c r="W29">
-        <v>0.12981772349</v>
+        <v>0.123398165735</v>
       </c>
       <c r="X29">
-        <v>0.12553801832</v>
+        <v>0.11697860798</v>
       </c>
       <c r="Y29">
-        <v>0.12125831315</v>
+        <v>0.110559050225</v>
       </c>
       <c r="Z29">
-        <v>0.11697860798</v>
+        <v>0.10413949247</v>
       </c>
       <c r="AA29">
-        <v>0.11269890281</v>
+        <v>0.09771993471500001</v>
       </c>
       <c r="AB29">
-        <v>0.10841919764</v>
+        <v>0.09130037696</v>
       </c>
       <c r="AC29">
-        <v>0.10413949247</v>
+        <v>0.08488081920500001</v>
       </c>
       <c r="AD29">
-        <v>0.0998597873</v>
+        <v>0.07846126145</v>
       </c>
       <c r="AE29">
-        <v>0.09558008212999999</v>
+        <v>0.072041703695</v>
       </c>
       <c r="AF29">
-        <v>0.09130037696000001</v>
+        <v>0.06562214594</v>
       </c>
       <c r="AG29">
-        <v>0.08702067179</v>
+        <v>0.059202588185</v>
       </c>
       <c r="AH29">
-        <v>0.08274096662000002</v>
+        <v>0.05278303043000002</v>
       </c>
       <c r="AI29">
-        <v>0.07846126145000001</v>
+        <v>0.046363472675</v>
       </c>
       <c r="AJ29">
-        <v>0.07418155628000001</v>
+        <v>0.03994391492</v>
       </c>
       <c r="AK29">
-        <v>0.06990185111000001</v>
+        <v>0.033524357165</v>
       </c>
       <c r="AL29">
-        <v>0.06562214594</v>
+        <v>0.02710479941</v>
       </c>
       <c r="AM29">
-        <v>0.06134244077000001</v>
+        <v>0.02068524165500001</v>
       </c>
       <c r="AN29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
       <c r="AO29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
       <c r="AP29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
       <c r="AQ29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
       <c r="AR29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
       <c r="AS29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
       <c r="AT29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
       <c r="AU29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
       <c r="AV29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
       <c r="AW29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
       <c r="AX29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
       <c r="AY29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
       <c r="AZ29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
       <c r="BA29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
       <c r="BB29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
       <c r="BC29">
-        <v>0.0570627356</v>
+        <v>0.0142656839</v>
       </c>
     </row>
     <row r="30" spans="1:55">
@@ -34021,109 +34021,109 @@
         <v>1.98E-05</v>
       </c>
       <c r="U30">
-        <v>1.9206E-05</v>
+        <v>1.8909E-05</v>
       </c>
       <c r="V30">
-        <v>1.8612E-05</v>
+        <v>1.8018E-05</v>
       </c>
       <c r="W30">
-        <v>1.8018E-05</v>
+        <v>1.7127E-05</v>
       </c>
       <c r="X30">
-        <v>1.7424E-05</v>
+        <v>1.6236E-05</v>
       </c>
       <c r="Y30">
-        <v>1.683E-05</v>
+        <v>1.5345E-05</v>
       </c>
       <c r="Z30">
-        <v>1.6236E-05</v>
+        <v>1.4454E-05</v>
       </c>
       <c r="AA30">
-        <v>1.5642E-05</v>
+        <v>1.3563E-05</v>
       </c>
       <c r="AB30">
-        <v>1.5048E-05</v>
+        <v>1.2672E-05</v>
       </c>
       <c r="AC30">
-        <v>1.4454E-05</v>
+        <v>1.1781E-05</v>
       </c>
       <c r="AD30">
-        <v>1.386E-05</v>
+        <v>1.089E-05</v>
       </c>
       <c r="AE30">
-        <v>1.3266E-05</v>
+        <v>9.999E-06</v>
       </c>
       <c r="AF30">
-        <v>1.2672E-05</v>
+        <v>9.108E-06</v>
       </c>
       <c r="AG30">
-        <v>1.2078E-05</v>
+        <v>8.216999999999999E-06</v>
       </c>
       <c r="AH30">
-        <v>1.1484E-05</v>
+        <v>7.326000000000001E-06</v>
       </c>
       <c r="AI30">
-        <v>1.089E-05</v>
+        <v>6.435E-06</v>
       </c>
       <c r="AJ30">
-        <v>1.0296E-05</v>
+        <v>5.544E-06</v>
       </c>
       <c r="AK30">
-        <v>9.702E-06</v>
+        <v>4.653E-06</v>
       </c>
       <c r="AL30">
-        <v>9.108E-06</v>
+        <v>3.762E-06</v>
       </c>
       <c r="AM30">
-        <v>8.514000000000002E-06</v>
+        <v>2.871000000000001E-06</v>
       </c>
       <c r="AN30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
       <c r="AO30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
       <c r="AP30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
       <c r="AQ30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
       <c r="AR30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
       <c r="AS30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
       <c r="AT30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
       <c r="AU30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
       <c r="AV30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
       <c r="AW30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
       <c r="AX30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
       <c r="AY30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
       <c r="AZ30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
       <c r="BA30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
       <c r="BB30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
       <c r="BC30">
-        <v>7.92E-06</v>
+        <v>1.98E-06</v>
       </c>
     </row>
     <row r="31" spans="1:55">
@@ -34173,109 +34173,109 @@
         <v>1.423626227</v>
       </c>
       <c r="U31">
-        <v>1.38091744019</v>
+        <v>1.359563046785</v>
       </c>
       <c r="V31">
-        <v>1.33820865338</v>
+        <v>1.29549986657</v>
       </c>
       <c r="W31">
-        <v>1.29549986657</v>
+        <v>1.231436686355</v>
       </c>
       <c r="X31">
-        <v>1.25279107976</v>
+        <v>1.16737350614</v>
       </c>
       <c r="Y31">
-        <v>1.21008229295</v>
+        <v>1.103310325925</v>
       </c>
       <c r="Z31">
-        <v>1.16737350614</v>
+        <v>1.03924714571</v>
       </c>
       <c r="AA31">
-        <v>1.12466471933</v>
+        <v>0.9751839654950001</v>
       </c>
       <c r="AB31">
-        <v>1.08195593252</v>
+        <v>0.91112078528</v>
       </c>
       <c r="AC31">
-        <v>1.03924714571</v>
+        <v>0.8470576050650001</v>
       </c>
       <c r="AD31">
-        <v>0.9965383589</v>
+        <v>0.78299442485</v>
       </c>
       <c r="AE31">
-        <v>0.95382957209</v>
+        <v>0.7189312446349999</v>
       </c>
       <c r="AF31">
-        <v>0.91112078528</v>
+        <v>0.65486806442</v>
       </c>
       <c r="AG31">
-        <v>0.8684119984699999</v>
+        <v>0.590804884205</v>
       </c>
       <c r="AH31">
-        <v>0.82570321166</v>
+        <v>0.52674170399</v>
       </c>
       <c r="AI31">
-        <v>0.78299442485</v>
+        <v>0.462678523775</v>
       </c>
       <c r="AJ31">
-        <v>0.74028563804</v>
+        <v>0.3986153435599999</v>
       </c>
       <c r="AK31">
-        <v>0.69757685123</v>
+        <v>0.334552163345</v>
       </c>
       <c r="AL31">
-        <v>0.65486806442</v>
+        <v>0.27048898313</v>
       </c>
       <c r="AM31">
-        <v>0.61215927761</v>
+        <v>0.2064258029150001</v>
       </c>
       <c r="AN31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AO31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AP31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AQ31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AR31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AS31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AT31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AU31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AV31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AW31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AX31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AY31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AZ31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="BA31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="BB31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="BC31">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
     </row>
     <row r="32" spans="1:55">
@@ -34325,109 +34325,109 @@
         <v>1.423626227</v>
       </c>
       <c r="U32">
-        <v>1.38091744019</v>
+        <v>1.359563046785</v>
       </c>
       <c r="V32">
-        <v>1.33820865338</v>
+        <v>1.29549986657</v>
       </c>
       <c r="W32">
-        <v>1.29549986657</v>
+        <v>1.231436686355</v>
       </c>
       <c r="X32">
-        <v>1.25279107976</v>
+        <v>1.16737350614</v>
       </c>
       <c r="Y32">
-        <v>1.21008229295</v>
+        <v>1.103310325925</v>
       </c>
       <c r="Z32">
-        <v>1.16737350614</v>
+        <v>1.03924714571</v>
       </c>
       <c r="AA32">
-        <v>1.12466471933</v>
+        <v>0.9751839654950001</v>
       </c>
       <c r="AB32">
-        <v>1.08195593252</v>
+        <v>0.91112078528</v>
       </c>
       <c r="AC32">
-        <v>1.03924714571</v>
+        <v>0.8470576050650001</v>
       </c>
       <c r="AD32">
-        <v>0.9965383589</v>
+        <v>0.78299442485</v>
       </c>
       <c r="AE32">
-        <v>0.95382957209</v>
+        <v>0.7189312446349999</v>
       </c>
       <c r="AF32">
-        <v>0.91112078528</v>
+        <v>0.65486806442</v>
       </c>
       <c r="AG32">
-        <v>0.8684119984699999</v>
+        <v>0.590804884205</v>
       </c>
       <c r="AH32">
-        <v>0.82570321166</v>
+        <v>0.52674170399</v>
       </c>
       <c r="AI32">
-        <v>0.78299442485</v>
+        <v>0.462678523775</v>
       </c>
       <c r="AJ32">
-        <v>0.74028563804</v>
+        <v>0.3986153435599999</v>
       </c>
       <c r="AK32">
-        <v>0.69757685123</v>
+        <v>0.334552163345</v>
       </c>
       <c r="AL32">
-        <v>0.65486806442</v>
+        <v>0.27048898313</v>
       </c>
       <c r="AM32">
-        <v>0.61215927761</v>
+        <v>0.2064258029150001</v>
       </c>
       <c r="AN32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AO32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AP32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AQ32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AR32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AS32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AT32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AU32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AV32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AW32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AX32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AY32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="AZ32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="BA32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="BB32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
       <c r="BC32">
-        <v>0.5694504908</v>
+        <v>0.1423626227</v>
       </c>
     </row>
     <row r="33" spans="1:55">
@@ -34477,109 +34477,109 @@
         <v>3.39E-05</v>
       </c>
       <c r="U33">
-        <v>3.2883E-05</v>
+        <v>3.237449999999999E-05</v>
       </c>
       <c r="V33">
-        <v>3.1866E-05</v>
+        <v>3.0849E-05</v>
       </c>
       <c r="W33">
-        <v>3.0849E-05</v>
+        <v>2.93235E-05</v>
       </c>
       <c r="X33">
-        <v>2.9832E-05</v>
+        <v>2.7798E-05</v>
       </c>
       <c r="Y33">
-        <v>2.8815E-05</v>
+        <v>2.62725E-05</v>
       </c>
       <c r="Z33">
-        <v>2.7798E-05</v>
+        <v>2.4747E-05</v>
       </c>
       <c r="AA33">
-        <v>2.6781E-05</v>
+        <v>2.32215E-05</v>
       </c>
       <c r="AB33">
-        <v>2.5764E-05</v>
+        <v>2.1696E-05</v>
       </c>
       <c r="AC33">
-        <v>2.4747E-05</v>
+        <v>2.01705E-05</v>
       </c>
       <c r="AD33">
-        <v>2.373E-05</v>
+        <v>1.8645E-05</v>
       </c>
       <c r="AE33">
-        <v>2.2713E-05</v>
+        <v>1.71195E-05</v>
       </c>
       <c r="AF33">
-        <v>2.1696E-05</v>
+        <v>1.5594E-05</v>
       </c>
       <c r="AG33">
-        <v>2.0679E-05</v>
+        <v>1.40685E-05</v>
       </c>
       <c r="AH33">
-        <v>1.9662E-05</v>
+        <v>1.2543E-05</v>
       </c>
       <c r="AI33">
-        <v>1.8645E-05</v>
+        <v>1.10175E-05</v>
       </c>
       <c r="AJ33">
-        <v>1.7628E-05</v>
+        <v>9.491999999999998E-06</v>
       </c>
       <c r="AK33">
-        <v>1.6611E-05</v>
+        <v>7.966500000000001E-06</v>
       </c>
       <c r="AL33">
-        <v>1.5594E-05</v>
+        <v>6.440999999999998E-06</v>
       </c>
       <c r="AM33">
-        <v>1.4577E-05</v>
+        <v>4.915500000000001E-06</v>
       </c>
       <c r="AN33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
       <c r="AO33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
       <c r="AP33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
       <c r="AQ33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
       <c r="AR33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
       <c r="AS33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
       <c r="AT33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
       <c r="AU33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
       <c r="AV33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
       <c r="AW33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
       <c r="AX33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
       <c r="AY33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
       <c r="AZ33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
       <c r="BA33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
       <c r="BB33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
       <c r="BC33">
-        <v>1.356E-05</v>
+        <v>3.39E-06</v>
       </c>
     </row>
     <row r="34" spans="1:55">

--- a/ssp_modeling/transformations/templates/calibrated/mexico/model_input_variables_mexico_ip_calibrated.xlsx
+++ b/ssp_modeling/transformations/templates/calibrated/mexico/model_input_variables_mexico_ip_calibrated.xlsx
@@ -32805,109 +32805,109 @@
         <v>0.273680173</v>
       </c>
       <c r="U22">
-        <v>0.261364565215</v>
+        <v>0.26546976781</v>
       </c>
       <c r="V22">
+        <v>0.25725936262</v>
+      </c>
+      <c r="W22">
         <v>0.24904895743</v>
       </c>
-      <c r="W22">
-        <v>0.236733349645</v>
-      </c>
       <c r="X22">
+        <v>0.2408385522400001</v>
+      </c>
+      <c r="Y22">
+        <v>0.23262814705</v>
+      </c>
+      <c r="Z22">
         <v>0.22441774186</v>
       </c>
-      <c r="Y22">
-        <v>0.212102134075</v>
-      </c>
-      <c r="Z22">
+      <c r="AA22">
+        <v>0.21620733667</v>
+      </c>
+      <c r="AB22">
+        <v>0.20799693148</v>
+      </c>
+      <c r="AC22">
         <v>0.19978652629</v>
       </c>
-      <c r="AA22">
-        <v>0.187470918505</v>
-      </c>
-      <c r="AB22">
+      <c r="AD22">
+        <v>0.1915761211</v>
+      </c>
+      <c r="AE22">
+        <v>0.18336571591</v>
+      </c>
+      <c r="AF22">
         <v>0.17515531072</v>
       </c>
-      <c r="AC22">
-        <v>0.1628397029350001</v>
-      </c>
-      <c r="AD22">
+      <c r="AG22">
+        <v>0.16694490553</v>
+      </c>
+      <c r="AH22">
+        <v>0.15873450034</v>
+      </c>
+      <c r="AI22">
         <v>0.15052409515</v>
       </c>
-      <c r="AE22">
-        <v>0.138208487365</v>
-      </c>
-      <c r="AF22">
+      <c r="AJ22">
+        <v>0.14231368996</v>
+      </c>
+      <c r="AK22">
+        <v>0.13410328477</v>
+      </c>
+      <c r="AL22">
         <v>0.12589287958</v>
       </c>
-      <c r="AG22">
-        <v>0.113577271795</v>
-      </c>
-      <c r="AH22">
-        <v>0.10126166401</v>
-      </c>
-      <c r="AI22">
-        <v>0.08894605622500001</v>
-      </c>
-      <c r="AJ22">
-        <v>0.07663044844</v>
-      </c>
-      <c r="AK22">
-        <v>0.06431484065500001</v>
-      </c>
-      <c r="AL22">
-        <v>0.05199923287</v>
-      </c>
       <c r="AM22">
-        <v>0.03968362508500002</v>
+        <v>0.11768247439</v>
       </c>
       <c r="AN22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
       <c r="AO22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
       <c r="AP22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
       <c r="AQ22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
       <c r="AR22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
       <c r="AS22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
       <c r="AT22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
       <c r="AU22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
       <c r="AV22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
       <c r="AW22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
       <c r="AX22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
       <c r="AY22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
       <c r="AZ22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
       <c r="BA22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
       <c r="BB22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
       <c r="BC22">
-        <v>0.02736801730000001</v>
+        <v>0.1094720692</v>
       </c>
     </row>
     <row r="23" spans="1:55">
@@ -32957,109 +32957,109 @@
         <v>0.187179706</v>
       </c>
       <c r="U23">
-        <v>0.17875661923</v>
+        <v>0.18156431482</v>
       </c>
       <c r="V23">
+        <v>0.17594892364</v>
+      </c>
+      <c r="W23">
         <v>0.17033353246</v>
       </c>
-      <c r="W23">
-        <v>0.16191044569</v>
-      </c>
       <c r="X23">
+        <v>0.16471814128</v>
+      </c>
+      <c r="Y23">
+        <v>0.1591027501</v>
+      </c>
+      <c r="Z23">
         <v>0.15348735892</v>
       </c>
-      <c r="Y23">
-        <v>0.14506427215</v>
-      </c>
-      <c r="Z23">
+      <c r="AA23">
+        <v>0.14787196774</v>
+      </c>
+      <c r="AB23">
+        <v>0.14225657656</v>
+      </c>
+      <c r="AC23">
         <v>0.13664118538</v>
       </c>
-      <c r="AA23">
-        <v>0.12821809861</v>
-      </c>
-      <c r="AB23">
+      <c r="AD23">
+        <v>0.1310257942</v>
+      </c>
+      <c r="AE23">
+        <v>0.12541040302</v>
+      </c>
+      <c r="AF23">
         <v>0.11979501184</v>
       </c>
-      <c r="AC23">
-        <v>0.11137192507</v>
-      </c>
-      <c r="AD23">
+      <c r="AG23">
+        <v>0.11417962066</v>
+      </c>
+      <c r="AH23">
+        <v>0.10856422948</v>
+      </c>
+      <c r="AI23">
         <v>0.1029488383</v>
       </c>
-      <c r="AE23">
-        <v>0.09452575152999999</v>
-      </c>
-      <c r="AF23">
+      <c r="AJ23">
+        <v>0.09733344712</v>
+      </c>
+      <c r="AK23">
+        <v>0.09171805594000002</v>
+      </c>
+      <c r="AL23">
         <v>0.08610266476</v>
       </c>
-      <c r="AG23">
-        <v>0.07767957799</v>
-      </c>
-      <c r="AH23">
-        <v>0.06925649122000001</v>
-      </c>
-      <c r="AI23">
-        <v>0.06083340445</v>
-      </c>
-      <c r="AJ23">
-        <v>0.05241031767999999</v>
-      </c>
-      <c r="AK23">
-        <v>0.04398723091000001</v>
-      </c>
-      <c r="AL23">
-        <v>0.03556414414</v>
-      </c>
       <c r="AM23">
-        <v>0.02714105737000001</v>
+        <v>0.08048727358000002</v>
       </c>
       <c r="AN23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AO23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AP23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AQ23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AR23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AS23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AT23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AU23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AV23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AW23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AX23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AY23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AZ23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="BA23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="BB23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="BC23">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
     </row>
     <row r="24" spans="1:55">
@@ -33109,109 +33109,109 @@
         <v>0.187179706</v>
       </c>
       <c r="U24">
-        <v>0.17875661923</v>
+        <v>0.18156431482</v>
       </c>
       <c r="V24">
+        <v>0.17594892364</v>
+      </c>
+      <c r="W24">
         <v>0.17033353246</v>
       </c>
-      <c r="W24">
-        <v>0.16191044569</v>
-      </c>
       <c r="X24">
+        <v>0.16471814128</v>
+      </c>
+      <c r="Y24">
+        <v>0.1591027501</v>
+      </c>
+      <c r="Z24">
         <v>0.15348735892</v>
       </c>
-      <c r="Y24">
-        <v>0.14506427215</v>
-      </c>
-      <c r="Z24">
+      <c r="AA24">
+        <v>0.14787196774</v>
+      </c>
+      <c r="AB24">
+        <v>0.14225657656</v>
+      </c>
+      <c r="AC24">
         <v>0.13664118538</v>
       </c>
-      <c r="AA24">
-        <v>0.12821809861</v>
-      </c>
-      <c r="AB24">
+      <c r="AD24">
+        <v>0.1310257942</v>
+      </c>
+      <c r="AE24">
+        <v>0.12541040302</v>
+      </c>
+      <c r="AF24">
         <v>0.11979501184</v>
       </c>
-      <c r="AC24">
-        <v>0.11137192507</v>
-      </c>
-      <c r="AD24">
+      <c r="AG24">
+        <v>0.11417962066</v>
+      </c>
+      <c r="AH24">
+        <v>0.10856422948</v>
+      </c>
+      <c r="AI24">
         <v>0.1029488383</v>
       </c>
-      <c r="AE24">
-        <v>0.09452575152999999</v>
-      </c>
-      <c r="AF24">
+      <c r="AJ24">
+        <v>0.09733344712</v>
+      </c>
+      <c r="AK24">
+        <v>0.09171805594000002</v>
+      </c>
+      <c r="AL24">
         <v>0.08610266476</v>
       </c>
-      <c r="AG24">
-        <v>0.07767957799</v>
-      </c>
-      <c r="AH24">
-        <v>0.06925649122000001</v>
-      </c>
-      <c r="AI24">
-        <v>0.06083340445</v>
-      </c>
-      <c r="AJ24">
-        <v>0.05241031767999999</v>
-      </c>
-      <c r="AK24">
-        <v>0.04398723091000001</v>
-      </c>
-      <c r="AL24">
-        <v>0.03556414414</v>
-      </c>
       <c r="AM24">
-        <v>0.02714105737000001</v>
+        <v>0.08048727358000002</v>
       </c>
       <c r="AN24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AO24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AP24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AQ24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AR24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AS24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AT24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AU24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AV24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AW24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AX24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AY24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="AZ24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="BA24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="BB24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
       <c r="BC24">
-        <v>0.0187179706</v>
+        <v>0.07487188240000001</v>
       </c>
     </row>
     <row r="25" spans="1:55">
@@ -33261,109 +33261,109 @@
         <v>0.141458864</v>
       </c>
       <c r="U25">
-        <v>0.13509321512</v>
+        <v>0.13721509808</v>
       </c>
       <c r="V25">
+        <v>0.13297133216</v>
+      </c>
+      <c r="W25">
         <v>0.12872756624</v>
       </c>
-      <c r="W25">
-        <v>0.12236191736</v>
-      </c>
       <c r="X25">
+        <v>0.12448380032</v>
+      </c>
+      <c r="Y25">
+        <v>0.1202400344</v>
+      </c>
+      <c r="Z25">
         <v>0.11599626848</v>
       </c>
-      <c r="Y25">
-        <v>0.1096306196</v>
-      </c>
-      <c r="Z25">
+      <c r="AA25">
+        <v>0.11175250256</v>
+      </c>
+      <c r="AB25">
+        <v>0.10750873664</v>
+      </c>
+      <c r="AC25">
         <v>0.10326497072</v>
       </c>
-      <c r="AA25">
-        <v>0.09689932184</v>
-      </c>
-      <c r="AB25">
-        <v>0.09053367295999999</v>
-      </c>
-      <c r="AC25">
-        <v>0.08416802408</v>
-      </c>
       <c r="AD25">
+        <v>0.0990212048</v>
+      </c>
+      <c r="AE25">
+        <v>0.09477743888</v>
+      </c>
+      <c r="AF25">
+        <v>0.09053367296000001</v>
+      </c>
+      <c r="AG25">
+        <v>0.08628990704</v>
+      </c>
+      <c r="AH25">
+        <v>0.08204614112</v>
+      </c>
+      <c r="AI25">
         <v>0.0778023752</v>
       </c>
-      <c r="AE25">
-        <v>0.07143672631999999</v>
-      </c>
-      <c r="AF25">
+      <c r="AJ25">
+        <v>0.07355860927999999</v>
+      </c>
+      <c r="AK25">
+        <v>0.06931484336</v>
+      </c>
+      <c r="AL25">
         <v>0.06507107744</v>
       </c>
-      <c r="AG25">
-        <v>0.05870542855999999</v>
-      </c>
-      <c r="AH25">
-        <v>0.05233977968</v>
-      </c>
-      <c r="AI25">
-        <v>0.0459741308</v>
-      </c>
-      <c r="AJ25">
-        <v>0.03960848191999999</v>
-      </c>
-      <c r="AK25">
-        <v>0.03324283304</v>
-      </c>
-      <c r="AL25">
-        <v>0.02687718416</v>
-      </c>
       <c r="AM25">
-        <v>0.02051153528000001</v>
+        <v>0.06082731152</v>
       </c>
       <c r="AN25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AO25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AP25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AQ25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AR25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AS25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AT25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AU25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AV25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AW25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AX25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AY25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AZ25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="BA25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="BB25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="BC25">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
     </row>
     <row r="26" spans="1:55">
@@ -33413,109 +33413,109 @@
         <v>0.141458864</v>
       </c>
       <c r="U26">
-        <v>0.13509321512</v>
+        <v>0.13721509808</v>
       </c>
       <c r="V26">
+        <v>0.13297133216</v>
+      </c>
+      <c r="W26">
         <v>0.12872756624</v>
       </c>
-      <c r="W26">
-        <v>0.12236191736</v>
-      </c>
       <c r="X26">
+        <v>0.12448380032</v>
+      </c>
+      <c r="Y26">
+        <v>0.1202400344</v>
+      </c>
+      <c r="Z26">
         <v>0.11599626848</v>
       </c>
-      <c r="Y26">
-        <v>0.1096306196</v>
-      </c>
-      <c r="Z26">
+      <c r="AA26">
+        <v>0.11175250256</v>
+      </c>
+      <c r="AB26">
+        <v>0.10750873664</v>
+      </c>
+      <c r="AC26">
         <v>0.10326497072</v>
       </c>
-      <c r="AA26">
-        <v>0.09689932184</v>
-      </c>
-      <c r="AB26">
-        <v>0.09053367295999999</v>
-      </c>
-      <c r="AC26">
-        <v>0.08416802408</v>
-      </c>
       <c r="AD26">
+        <v>0.0990212048</v>
+      </c>
+      <c r="AE26">
+        <v>0.09477743888</v>
+      </c>
+      <c r="AF26">
+        <v>0.09053367296000001</v>
+      </c>
+      <c r="AG26">
+        <v>0.08628990704</v>
+      </c>
+      <c r="AH26">
+        <v>0.08204614112</v>
+      </c>
+      <c r="AI26">
         <v>0.0778023752</v>
       </c>
-      <c r="AE26">
-        <v>0.07143672631999999</v>
-      </c>
-      <c r="AF26">
+      <c r="AJ26">
+        <v>0.07355860927999999</v>
+      </c>
+      <c r="AK26">
+        <v>0.06931484336</v>
+      </c>
+      <c r="AL26">
         <v>0.06507107744</v>
       </c>
-      <c r="AG26">
-        <v>0.05870542855999999</v>
-      </c>
-      <c r="AH26">
-        <v>0.05233977968</v>
-      </c>
-      <c r="AI26">
-        <v>0.0459741308</v>
-      </c>
-      <c r="AJ26">
-        <v>0.03960848191999999</v>
-      </c>
-      <c r="AK26">
-        <v>0.03324283304</v>
-      </c>
-      <c r="AL26">
-        <v>0.02687718416</v>
-      </c>
       <c r="AM26">
-        <v>0.02051153528000001</v>
+        <v>0.06082731152</v>
       </c>
       <c r="AN26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AO26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AP26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AQ26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AR26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AS26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AT26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AU26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AV26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AW26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AX26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AY26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="AZ26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="BA26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="BB26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
       <c r="BC26">
-        <v>0.0141458864</v>
+        <v>0.0565835456</v>
       </c>
     </row>
     <row r="27" spans="1:55">
@@ -33565,109 +33565,109 @@
         <v>0.028164596</v>
       </c>
       <c r="U27">
-        <v>0.02689718918</v>
+        <v>0.02731965812</v>
       </c>
       <c r="V27">
+        <v>0.02647472024</v>
+      </c>
+      <c r="W27">
         <v>0.02562978236</v>
       </c>
-      <c r="W27">
-        <v>0.02436237554</v>
-      </c>
       <c r="X27">
+        <v>0.02478484448</v>
+      </c>
+      <c r="Y27">
+        <v>0.0239399066</v>
+      </c>
+      <c r="Z27">
         <v>0.02309496872</v>
       </c>
-      <c r="Y27">
-        <v>0.0218275619</v>
-      </c>
-      <c r="Z27">
+      <c r="AA27">
+        <v>0.02225003084</v>
+      </c>
+      <c r="AB27">
+        <v>0.02140509296</v>
+      </c>
+      <c r="AC27">
         <v>0.02056015508</v>
       </c>
-      <c r="AA27">
-        <v>0.01929274826</v>
-      </c>
-      <c r="AB27">
+      <c r="AD27">
+        <v>0.0197152172</v>
+      </c>
+      <c r="AE27">
+        <v>0.01887027932</v>
+      </c>
+      <c r="AF27">
         <v>0.01802534144</v>
       </c>
-      <c r="AC27">
-        <v>0.01675793462</v>
-      </c>
-      <c r="AD27">
+      <c r="AG27">
+        <v>0.01718040356</v>
+      </c>
+      <c r="AH27">
+        <v>0.01633546568</v>
+      </c>
+      <c r="AI27">
         <v>0.0154905278</v>
       </c>
-      <c r="AE27">
-        <v>0.01422312098</v>
-      </c>
-      <c r="AF27">
+      <c r="AJ27">
+        <v>0.01464558992</v>
+      </c>
+      <c r="AK27">
+        <v>0.01380065204</v>
+      </c>
+      <c r="AL27">
         <v>0.01295571416</v>
       </c>
-      <c r="AG27">
-        <v>0.01168830734</v>
-      </c>
-      <c r="AH27">
-        <v>0.01042090052</v>
-      </c>
-      <c r="AI27">
-        <v>0.009153493700000001</v>
-      </c>
-      <c r="AJ27">
-        <v>0.007886086879999999</v>
-      </c>
-      <c r="AK27">
-        <v>0.00661868006</v>
-      </c>
-      <c r="AL27">
-        <v>0.005351273239999999</v>
-      </c>
       <c r="AM27">
-        <v>0.004083866420000001</v>
+        <v>0.01211077628</v>
       </c>
       <c r="AN27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
       <c r="AO27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
       <c r="AP27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
       <c r="AQ27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
       <c r="AR27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
       <c r="AS27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
       <c r="AT27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
       <c r="AU27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
       <c r="AV27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
       <c r="AW27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
       <c r="AX27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
       <c r="AY27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
       <c r="AZ27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
       <c r="BA27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
       <c r="BB27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
       <c r="BC27">
-        <v>0.0028164596</v>
+        <v>0.0112658384</v>
       </c>
     </row>
     <row r="28" spans="1:55">
@@ -33717,109 +33717,109 @@
         <v>0.004187006</v>
       </c>
       <c r="U28">
-        <v>0.003998590729999999</v>
+        <v>0.00406139582</v>
       </c>
       <c r="V28">
+        <v>0.00393578564</v>
+      </c>
+      <c r="W28">
         <v>0.00381017546</v>
       </c>
-      <c r="W28">
-        <v>0.00362176019</v>
-      </c>
       <c r="X28">
+        <v>0.003684565280000001</v>
+      </c>
+      <c r="Y28">
+        <v>0.0035589551</v>
+      </c>
+      <c r="Z28">
         <v>0.00343334492</v>
       </c>
-      <c r="Y28">
-        <v>0.00324492965</v>
-      </c>
-      <c r="Z28">
+      <c r="AA28">
+        <v>0.00330773474</v>
+      </c>
+      <c r="AB28">
+        <v>0.00318212456</v>
+      </c>
+      <c r="AC28">
         <v>0.00305651438</v>
       </c>
-      <c r="AA28">
-        <v>0.00286809911</v>
-      </c>
-      <c r="AB28">
+      <c r="AD28">
+        <v>0.0029309042</v>
+      </c>
+      <c r="AE28">
+        <v>0.00280529402</v>
+      </c>
+      <c r="AF28">
         <v>0.00267968384</v>
       </c>
-      <c r="AC28">
-        <v>0.00249126857</v>
-      </c>
-      <c r="AD28">
+      <c r="AG28">
+        <v>0.00255407366</v>
+      </c>
+      <c r="AH28">
+        <v>0.00242846348</v>
+      </c>
+      <c r="AI28">
         <v>0.0023028533</v>
       </c>
-      <c r="AE28">
-        <v>0.00211443803</v>
-      </c>
-      <c r="AF28">
+      <c r="AJ28">
+        <v>0.00217724312</v>
+      </c>
+      <c r="AK28">
+        <v>0.00205163294</v>
+      </c>
+      <c r="AL28">
         <v>0.00192602276</v>
       </c>
-      <c r="AG28">
-        <v>0.00173760749</v>
-      </c>
-      <c r="AH28">
-        <v>0.00154919222</v>
-      </c>
-      <c r="AI28">
-        <v>0.00136077695</v>
-      </c>
-      <c r="AJ28">
-        <v>0.00117236168</v>
-      </c>
-      <c r="AK28">
-        <v>0.0009839464100000002</v>
-      </c>
-      <c r="AL28">
-        <v>0.00079553114</v>
-      </c>
       <c r="AM28">
-        <v>0.0006071158700000002</v>
+        <v>0.00180041258</v>
       </c>
       <c r="AN28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
       <c r="AO28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
       <c r="AP28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
       <c r="AQ28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
       <c r="AR28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
       <c r="AS28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
       <c r="AT28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
       <c r="AU28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
       <c r="AV28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
       <c r="AW28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
       <c r="AX28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
       <c r="AY28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
       <c r="AZ28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
       <c r="BA28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
       <c r="BB28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
       <c r="BC28">
-        <v>0.0004187006</v>
+        <v>0.0016748024</v>
       </c>
     </row>
     <row r="29" spans="1:55">
@@ -33869,109 +33869,109 @@
         <v>0.142656839</v>
       </c>
       <c r="U29">
-        <v>0.136237281245</v>
+        <v>0.13837713383</v>
       </c>
       <c r="V29">
+        <v>0.13409742866</v>
+      </c>
+      <c r="W29">
         <v>0.12981772349</v>
       </c>
-      <c r="W29">
-        <v>0.123398165735</v>
-      </c>
       <c r="X29">
+        <v>0.12553801832</v>
+      </c>
+      <c r="Y29">
+        <v>0.12125831315</v>
+      </c>
+      <c r="Z29">
         <v>0.11697860798</v>
       </c>
-      <c r="Y29">
-        <v>0.110559050225</v>
-      </c>
-      <c r="Z29">
+      <c r="AA29">
+        <v>0.11269890281</v>
+      </c>
+      <c r="AB29">
+        <v>0.10841919764</v>
+      </c>
+      <c r="AC29">
         <v>0.10413949247</v>
       </c>
-      <c r="AA29">
-        <v>0.09771993471500001</v>
-      </c>
-      <c r="AB29">
-        <v>0.09130037696</v>
-      </c>
-      <c r="AC29">
-        <v>0.08488081920500001</v>
-      </c>
       <c r="AD29">
-        <v>0.07846126145</v>
+        <v>0.0998597873</v>
       </c>
       <c r="AE29">
-        <v>0.072041703695</v>
+        <v>0.09558008212999999</v>
       </c>
       <c r="AF29">
+        <v>0.09130037696000001</v>
+      </c>
+      <c r="AG29">
+        <v>0.08702067179</v>
+      </c>
+      <c r="AH29">
+        <v>0.08274096662000002</v>
+      </c>
+      <c r="AI29">
+        <v>0.07846126145000001</v>
+      </c>
+      <c r="AJ29">
+        <v>0.07418155628000001</v>
+      </c>
+      <c r="AK29">
+        <v>0.06990185111000001</v>
+      </c>
+      <c r="AL29">
         <v>0.06562214594</v>
       </c>
-      <c r="AG29">
-        <v>0.059202588185</v>
-      </c>
-      <c r="AH29">
-        <v>0.05278303043000002</v>
-      </c>
-      <c r="AI29">
-        <v>0.046363472675</v>
-      </c>
-      <c r="AJ29">
-        <v>0.03994391492</v>
-      </c>
-      <c r="AK29">
-        <v>0.033524357165</v>
-      </c>
-      <c r="AL29">
-        <v>0.02710479941</v>
-      </c>
       <c r="AM29">
-        <v>0.02068524165500001</v>
+        <v>0.06134244077000001</v>
       </c>
       <c r="AN29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
       <c r="AO29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
       <c r="AP29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
       <c r="AQ29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
       <c r="AR29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
       <c r="AS29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
       <c r="AT29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
       <c r="AU29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
       <c r="AV29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
       <c r="AW29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
       <c r="AX29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
       <c r="AY29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
       <c r="AZ29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
       <c r="BA29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
       <c r="BB29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
       <c r="BC29">
-        <v>0.0142656839</v>
+        <v>0.0570627356</v>
       </c>
     </row>
     <row r="30" spans="1:55">
@@ -34021,109 +34021,109 @@
         <v>1.98E-05</v>
       </c>
       <c r="U30">
-        <v>1.8909E-05</v>
+        <v>1.9206E-05</v>
       </c>
       <c r="V30">
+        <v>1.8612E-05</v>
+      </c>
+      <c r="W30">
         <v>1.8018E-05</v>
       </c>
-      <c r="W30">
-        <v>1.7127E-05</v>
-      </c>
       <c r="X30">
+        <v>1.7424E-05</v>
+      </c>
+      <c r="Y30">
+        <v>1.683E-05</v>
+      </c>
+      <c r="Z30">
         <v>1.6236E-05</v>
       </c>
-      <c r="Y30">
-        <v>1.5345E-05</v>
-      </c>
-      <c r="Z30">
+      <c r="AA30">
+        <v>1.5642E-05</v>
+      </c>
+      <c r="AB30">
+        <v>1.5048E-05</v>
+      </c>
+      <c r="AC30">
         <v>1.4454E-05</v>
       </c>
-      <c r="AA30">
-        <v>1.3563E-05</v>
-      </c>
-      <c r="AB30">
+      <c r="AD30">
+        <v>1.386E-05</v>
+      </c>
+      <c r="AE30">
+        <v>1.3266E-05</v>
+      </c>
+      <c r="AF30">
         <v>1.2672E-05</v>
       </c>
-      <c r="AC30">
-        <v>1.1781E-05</v>
-      </c>
-      <c r="AD30">
+      <c r="AG30">
+        <v>1.2078E-05</v>
+      </c>
+      <c r="AH30">
+        <v>1.1484E-05</v>
+      </c>
+      <c r="AI30">
         <v>1.089E-05</v>
       </c>
-      <c r="AE30">
-        <v>9.999E-06</v>
-      </c>
-      <c r="AF30">
+      <c r="AJ30">
+        <v>1.0296E-05</v>
+      </c>
+      <c r="AK30">
+        <v>9.702E-06</v>
+      </c>
+      <c r="AL30">
         <v>9.108E-06</v>
       </c>
-      <c r="AG30">
-        <v>8.216999999999999E-06</v>
-      </c>
-      <c r="AH30">
-        <v>7.326000000000001E-06</v>
-      </c>
-      <c r="AI30">
-        <v>6.435E-06</v>
-      </c>
-      <c r="AJ30">
-        <v>5.544E-06</v>
-      </c>
-      <c r="AK30">
-        <v>4.653E-06</v>
-      </c>
-      <c r="AL30">
-        <v>3.762E-06</v>
-      </c>
       <c r="AM30">
-        <v>2.871000000000001E-06</v>
+        <v>8.514000000000002E-06</v>
       </c>
       <c r="AN30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
       <c r="AO30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
       <c r="AP30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
       <c r="AQ30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
       <c r="AR30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
       <c r="AS30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
       <c r="AT30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
       <c r="AU30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
       <c r="AV30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
       <c r="AW30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
       <c r="AX30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
       <c r="AY30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
       <c r="AZ30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
       <c r="BA30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
       <c r="BB30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
       <c r="BC30">
-        <v>1.98E-06</v>
+        <v>7.92E-06</v>
       </c>
     </row>
     <row r="31" spans="1:55">
@@ -34173,109 +34173,109 @@
         <v>1.423626227</v>
       </c>
       <c r="U31">
-        <v>1.359563046785</v>
+        <v>1.38091744019</v>
       </c>
       <c r="V31">
+        <v>1.33820865338</v>
+      </c>
+      <c r="W31">
         <v>1.29549986657</v>
       </c>
-      <c r="W31">
-        <v>1.231436686355</v>
-      </c>
       <c r="X31">
+        <v>1.25279107976</v>
+      </c>
+      <c r="Y31">
+        <v>1.21008229295</v>
+      </c>
+      <c r="Z31">
         <v>1.16737350614</v>
       </c>
-      <c r="Y31">
-        <v>1.103310325925</v>
-      </c>
-      <c r="Z31">
+      <c r="AA31">
+        <v>1.12466471933</v>
+      </c>
+      <c r="AB31">
+        <v>1.08195593252</v>
+      </c>
+      <c r="AC31">
         <v>1.03924714571</v>
       </c>
-      <c r="AA31">
-        <v>0.9751839654950001</v>
-      </c>
-      <c r="AB31">
+      <c r="AD31">
+        <v>0.9965383589</v>
+      </c>
+      <c r="AE31">
+        <v>0.95382957209</v>
+      </c>
+      <c r="AF31">
         <v>0.91112078528</v>
       </c>
-      <c r="AC31">
-        <v>0.8470576050650001</v>
-      </c>
-      <c r="AD31">
+      <c r="AG31">
+        <v>0.8684119984699999</v>
+      </c>
+      <c r="AH31">
+        <v>0.82570321166</v>
+      </c>
+      <c r="AI31">
         <v>0.78299442485</v>
       </c>
-      <c r="AE31">
-        <v>0.7189312446349999</v>
-      </c>
-      <c r="AF31">
+      <c r="AJ31">
+        <v>0.74028563804</v>
+      </c>
+      <c r="AK31">
+        <v>0.69757685123</v>
+      </c>
+      <c r="AL31">
         <v>0.65486806442</v>
       </c>
-      <c r="AG31">
-        <v>0.590804884205</v>
-      </c>
-      <c r="AH31">
-        <v>0.52674170399</v>
-      </c>
-      <c r="AI31">
-        <v>0.462678523775</v>
-      </c>
-      <c r="AJ31">
-        <v>0.3986153435599999</v>
-      </c>
-      <c r="AK31">
-        <v>0.334552163345</v>
-      </c>
-      <c r="AL31">
-        <v>0.27048898313</v>
-      </c>
       <c r="AM31">
-        <v>0.2064258029150001</v>
+        <v>0.61215927761</v>
       </c>
       <c r="AN31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AO31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AP31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AQ31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AR31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AS31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AT31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AU31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AV31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AW31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AX31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AY31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AZ31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="BA31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="BB31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="BC31">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
     </row>
     <row r="32" spans="1:55">
@@ -34325,109 +34325,109 @@
         <v>1.423626227</v>
       </c>
       <c r="U32">
-        <v>1.359563046785</v>
+        <v>1.38091744019</v>
       </c>
       <c r="V32">
+        <v>1.33820865338</v>
+      </c>
+      <c r="W32">
         <v>1.29549986657</v>
       </c>
-      <c r="W32">
-        <v>1.231436686355</v>
-      </c>
       <c r="X32">
+        <v>1.25279107976</v>
+      </c>
+      <c r="Y32">
+        <v>1.21008229295</v>
+      </c>
+      <c r="Z32">
         <v>1.16737350614</v>
       </c>
-      <c r="Y32">
-        <v>1.103310325925</v>
-      </c>
-      <c r="Z32">
+      <c r="AA32">
+        <v>1.12466471933</v>
+      </c>
+      <c r="AB32">
+        <v>1.08195593252</v>
+      </c>
+      <c r="AC32">
         <v>1.03924714571</v>
       </c>
-      <c r="AA32">
-        <v>0.9751839654950001</v>
-      </c>
-      <c r="AB32">
+      <c r="AD32">
+        <v>0.9965383589</v>
+      </c>
+      <c r="AE32">
+        <v>0.95382957209</v>
+      </c>
+      <c r="AF32">
         <v>0.91112078528</v>
       </c>
-      <c r="AC32">
-        <v>0.8470576050650001</v>
-      </c>
-      <c r="AD32">
+      <c r="AG32">
+        <v>0.8684119984699999</v>
+      </c>
+      <c r="AH32">
+        <v>0.82570321166</v>
+      </c>
+      <c r="AI32">
         <v>0.78299442485</v>
       </c>
-      <c r="AE32">
-        <v>0.7189312446349999</v>
-      </c>
-      <c r="AF32">
+      <c r="AJ32">
+        <v>0.74028563804</v>
+      </c>
+      <c r="AK32">
+        <v>0.69757685123</v>
+      </c>
+      <c r="AL32">
         <v>0.65486806442</v>
       </c>
-      <c r="AG32">
-        <v>0.590804884205</v>
-      </c>
-      <c r="AH32">
-        <v>0.52674170399</v>
-      </c>
-      <c r="AI32">
-        <v>0.462678523775</v>
-      </c>
-      <c r="AJ32">
-        <v>0.3986153435599999</v>
-      </c>
-      <c r="AK32">
-        <v>0.334552163345</v>
-      </c>
-      <c r="AL32">
-        <v>0.27048898313</v>
-      </c>
       <c r="AM32">
-        <v>0.2064258029150001</v>
+        <v>0.61215927761</v>
       </c>
       <c r="AN32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AO32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AP32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AQ32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AR32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AS32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AT32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AU32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AV32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AW32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AX32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AY32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="AZ32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="BA32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="BB32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
       <c r="BC32">
-        <v>0.1423626227</v>
+        <v>0.5694504908</v>
       </c>
     </row>
     <row r="33" spans="1:55">
@@ -34477,109 +34477,109 @@
         <v>3.39E-05</v>
       </c>
       <c r="U33">
-        <v>3.237449999999999E-05</v>
+        <v>3.2883E-05</v>
       </c>
       <c r="V33">
+        <v>3.1866E-05</v>
+      </c>
+      <c r="W33">
         <v>3.0849E-05</v>
       </c>
-      <c r="W33">
-        <v>2.93235E-05</v>
-      </c>
       <c r="X33">
+        <v>2.9832E-05</v>
+      </c>
+      <c r="Y33">
+        <v>2.8815E-05</v>
+      </c>
+      <c r="Z33">
         <v>2.7798E-05</v>
       </c>
-      <c r="Y33">
-        <v>2.62725E-05</v>
-      </c>
-      <c r="Z33">
+      <c r="AA33">
+        <v>2.6781E-05</v>
+      </c>
+      <c r="AB33">
+        <v>2.5764E-05</v>
+      </c>
+      <c r="AC33">
         <v>2.4747E-05</v>
       </c>
-      <c r="AA33">
-        <v>2.32215E-05</v>
-      </c>
-      <c r="AB33">
+      <c r="AD33">
+        <v>2.373E-05</v>
+      </c>
+      <c r="AE33">
+        <v>2.2713E-05</v>
+      </c>
+      <c r="AF33">
         <v>2.1696E-05</v>
       </c>
-      <c r="AC33">
-        <v>2.01705E-05</v>
-      </c>
-      <c r="AD33">
+      <c r="AG33">
+        <v>2.0679E-05</v>
+      </c>
+      <c r="AH33">
+        <v>1.9662E-05</v>
+      </c>
+      <c r="AI33">
         <v>1.8645E-05</v>
       </c>
-      <c r="AE33">
-        <v>1.71195E-05</v>
-      </c>
-      <c r="AF33">
+      <c r="AJ33">
+        <v>1.7628E-05</v>
+      </c>
+      <c r="AK33">
+        <v>1.6611E-05</v>
+      </c>
+      <c r="AL33">
         <v>1.5594E-05</v>
       </c>
-      <c r="AG33">
-        <v>1.40685E-05</v>
-      </c>
-      <c r="AH33">
-        <v>1.2543E-05</v>
-      </c>
-      <c r="AI33">
-        <v>1.10175E-05</v>
-      </c>
-      <c r="AJ33">
-        <v>9.491999999999998E-06</v>
-      </c>
-      <c r="AK33">
-        <v>7.966500000000001E-06</v>
-      </c>
-      <c r="AL33">
-        <v>6.440999999999998E-06</v>
-      </c>
       <c r="AM33">
-        <v>4.915500000000001E-06</v>
+        <v>1.4577E-05</v>
       </c>
       <c r="AN33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
       <c r="AO33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
       <c r="AP33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
       <c r="AQ33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
       <c r="AR33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
       <c r="AS33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
       <c r="AT33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
       <c r="AU33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
       <c r="AV33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
       <c r="AW33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
       <c r="AX33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
       <c r="AY33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
       <c r="AZ33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
       <c r="BA33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
       <c r="BB33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
       <c r="BC33">
-        <v>3.39E-06</v>
+        <v>1.356E-05</v>
       </c>
     </row>
     <row r="34" spans="1:55">
@@ -34772,115 +34772,115 @@
         <v>0</v>
       </c>
       <c r="R35">
-        <v>0.02105263157894737</v>
+        <v>0</v>
       </c>
       <c r="S35">
-        <v>0.04210526315789474</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>0.06315789473684211</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>0.08421052631578947</v>
+        <v>0.02285714285714286</v>
       </c>
       <c r="V35">
-        <v>0.1052631578947368</v>
+        <v>0.04571428571428571</v>
       </c>
       <c r="W35">
-        <v>0.1263157894736842</v>
+        <v>0.06857142857142857</v>
       </c>
       <c r="X35">
-        <v>0.1473684210526316</v>
+        <v>0.09142857142857143</v>
       </c>
       <c r="Y35">
-        <v>0.1684210526315789</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="Z35">
-        <v>0.1894736842105263</v>
+        <v>0.1371428571428571</v>
       </c>
       <c r="AA35">
-        <v>0.2105263157894737</v>
+        <v>0.16</v>
       </c>
       <c r="AB35">
-        <v>0.2315789473684211</v>
+        <v>0.1828571428571429</v>
       </c>
       <c r="AC35">
-        <v>0.2526315789473684</v>
+        <v>0.2057142857142857</v>
       </c>
       <c r="AD35">
-        <v>0.2736842105263158</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="AE35">
-        <v>0.2947368421052631</v>
+        <v>0.2514285714285714</v>
       </c>
       <c r="AF35">
-        <v>0.3157894736842106</v>
+        <v>0.2742857142857143</v>
       </c>
       <c r="AG35">
-        <v>0.3368421052631579</v>
+        <v>0.2971428571428572</v>
       </c>
       <c r="AH35">
-        <v>0.3578947368421053</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="AI35">
-        <v>0.3789473684210526</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="AJ35">
-        <v>0.4</v>
+        <v>0.3657142857142857</v>
       </c>
       <c r="AK35">
-        <v>0.4210526315789473</v>
+        <v>0.3885714285714286</v>
       </c>
       <c r="AL35">
-        <v>0.4421052631578948</v>
+        <v>0.4114285714285714</v>
       </c>
       <c r="AM35">
-        <v>0.4631578947368422</v>
+        <v>0.4342857142857143</v>
       </c>
       <c r="AN35">
-        <v>0.4842105263157895</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="AO35">
-        <v>0.5052631578947369</v>
+        <v>0.48</v>
       </c>
       <c r="AP35">
-        <v>0.5263157894736843</v>
+        <v>0.5028571428571429</v>
       </c>
       <c r="AQ35">
-        <v>0.5473684210526316</v>
+        <v>0.5257142857142857</v>
       </c>
       <c r="AR35">
-        <v>0.5684210526315789</v>
+        <v>0.5485714285714286</v>
       </c>
       <c r="AS35">
-        <v>0.5894736842105263</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="AT35">
-        <v>0.6105263157894738</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="AU35">
-        <v>0.6315789473684211</v>
+        <v>0.6171428571428572</v>
       </c>
       <c r="AV35">
-        <v>0.6526315789473685</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="AW35">
-        <v>0.6736842105263158</v>
+        <v>0.6628571428571429</v>
       </c>
       <c r="AX35">
-        <v>0.6947368421052632</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="AY35">
-        <v>0.7157894736842105</v>
+        <v>0.7085714285714286</v>
       </c>
       <c r="AZ35">
-        <v>0.736842105263158</v>
+        <v>0.7314285714285714</v>
       </c>
       <c r="BA35">
-        <v>0.7578947368421053</v>
+        <v>0.7542857142857143</v>
       </c>
       <c r="BB35">
-        <v>0.7789473684210527</v>
+        <v>0.7771428571428571</v>
       </c>
       <c r="BC35">
         <v>0.8</v>
@@ -34924,115 +34924,115 @@
         <v>0</v>
       </c>
       <c r="R36">
-        <v>0.02105263157894737</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>0.04210526315789474</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>0.06315789473684211</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>0.08421052631578947</v>
+        <v>0.02285714285714286</v>
       </c>
       <c r="V36">
-        <v>0.1052631578947368</v>
+        <v>0.04571428571428571</v>
       </c>
       <c r="W36">
-        <v>0.1263157894736842</v>
+        <v>0.06857142857142857</v>
       </c>
       <c r="X36">
-        <v>0.1473684210526316</v>
+        <v>0.09142857142857143</v>
       </c>
       <c r="Y36">
-        <v>0.1684210526315789</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="Z36">
-        <v>0.1894736842105263</v>
+        <v>0.1371428571428571</v>
       </c>
       <c r="AA36">
-        <v>0.2105263157894737</v>
+        <v>0.16</v>
       </c>
       <c r="AB36">
-        <v>0.2315789473684211</v>
+        <v>0.1828571428571429</v>
       </c>
       <c r="AC36">
-        <v>0.2526315789473684</v>
+        <v>0.2057142857142857</v>
       </c>
       <c r="AD36">
-        <v>0.2736842105263158</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="AE36">
-        <v>0.2947368421052631</v>
+        <v>0.2514285714285714</v>
       </c>
       <c r="AF36">
-        <v>0.3157894736842106</v>
+        <v>0.2742857142857143</v>
       </c>
       <c r="AG36">
-        <v>0.3368421052631579</v>
+        <v>0.2971428571428572</v>
       </c>
       <c r="AH36">
-        <v>0.3578947368421053</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="AI36">
-        <v>0.3789473684210526</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="AJ36">
-        <v>0.4</v>
+        <v>0.3657142857142857</v>
       </c>
       <c r="AK36">
-        <v>0.4210526315789473</v>
+        <v>0.3885714285714286</v>
       </c>
       <c r="AL36">
-        <v>0.4421052631578948</v>
+        <v>0.4114285714285714</v>
       </c>
       <c r="AM36">
-        <v>0.4631578947368422</v>
+        <v>0.4342857142857143</v>
       </c>
       <c r="AN36">
-        <v>0.4842105263157895</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="AO36">
-        <v>0.5052631578947369</v>
+        <v>0.48</v>
       </c>
       <c r="AP36">
-        <v>0.5263157894736843</v>
+        <v>0.5028571428571429</v>
       </c>
       <c r="AQ36">
-        <v>0.5473684210526316</v>
+        <v>0.5257142857142857</v>
       </c>
       <c r="AR36">
-        <v>0.5684210526315789</v>
+        <v>0.5485714285714286</v>
       </c>
       <c r="AS36">
-        <v>0.5894736842105263</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="AT36">
-        <v>0.6105263157894738</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="AU36">
-        <v>0.6315789473684211</v>
+        <v>0.6171428571428572</v>
       </c>
       <c r="AV36">
-        <v>0.6526315789473685</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="AW36">
-        <v>0.6736842105263158</v>
+        <v>0.6628571428571429</v>
       </c>
       <c r="AX36">
-        <v>0.6947368421052632</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="AY36">
-        <v>0.7157894736842105</v>
+        <v>0.7085714285714286</v>
       </c>
       <c r="AZ36">
-        <v>0.736842105263158</v>
+        <v>0.7314285714285714</v>
       </c>
       <c r="BA36">
-        <v>0.7578947368421053</v>
+        <v>0.7542857142857143</v>
       </c>
       <c r="BB36">
-        <v>0.7789473684210527</v>
+        <v>0.7771428571428571</v>
       </c>
       <c r="BC36">
         <v>0.8</v>
@@ -35076,115 +35076,115 @@
         <v>0</v>
       </c>
       <c r="R37">
-        <v>0.02105263157894737</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>0.04210526315789474</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>0.06315789473684211</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>0.08421052631578947</v>
+        <v>0.02285714285714286</v>
       </c>
       <c r="V37">
-        <v>0.1052631578947368</v>
+        <v>0.04571428571428571</v>
       </c>
       <c r="W37">
-        <v>0.1263157894736842</v>
+        <v>0.06857142857142857</v>
       </c>
       <c r="X37">
-        <v>0.1473684210526316</v>
+        <v>0.09142857142857143</v>
       </c>
       <c r="Y37">
-        <v>0.1684210526315789</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="Z37">
-        <v>0.1894736842105263</v>
+        <v>0.1371428571428571</v>
       </c>
       <c r="AA37">
-        <v>0.2105263157894737</v>
+        <v>0.16</v>
       </c>
       <c r="AB37">
-        <v>0.2315789473684211</v>
+        <v>0.1828571428571429</v>
       </c>
       <c r="AC37">
-        <v>0.2526315789473684</v>
+        <v>0.2057142857142857</v>
       </c>
       <c r="AD37">
-        <v>0.2736842105263158</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="AE37">
-        <v>0.2947368421052631</v>
+        <v>0.2514285714285714</v>
       </c>
       <c r="AF37">
-        <v>0.3157894736842106</v>
+        <v>0.2742857142857143</v>
       </c>
       <c r="AG37">
-        <v>0.3368421052631579</v>
+        <v>0.2971428571428572</v>
       </c>
       <c r="AH37">
-        <v>0.3578947368421053</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="AI37">
-        <v>0.3789473684210526</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="AJ37">
-        <v>0.4</v>
+        <v>0.3657142857142857</v>
       </c>
       <c r="AK37">
-        <v>0.4210526315789473</v>
+        <v>0.3885714285714286</v>
       </c>
       <c r="AL37">
-        <v>0.4421052631578948</v>
+        <v>0.4114285714285714</v>
       </c>
       <c r="AM37">
-        <v>0.4631578947368422</v>
+        <v>0.4342857142857143</v>
       </c>
       <c r="AN37">
-        <v>0.4842105263157895</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="AO37">
-        <v>0.5052631578947369</v>
+        <v>0.48</v>
       </c>
       <c r="AP37">
-        <v>0.5263157894736843</v>
+        <v>0.5028571428571429</v>
       </c>
       <c r="AQ37">
-        <v>0.5473684210526316</v>
+        <v>0.5257142857142857</v>
       </c>
       <c r="AR37">
-        <v>0.5684210526315789</v>
+        <v>0.5485714285714286</v>
       </c>
       <c r="AS37">
-        <v>0.5894736842105263</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="AT37">
-        <v>0.6105263157894738</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="AU37">
-        <v>0.6315789473684211</v>
+        <v>0.6171428571428572</v>
       </c>
       <c r="AV37">
-        <v>0.6526315789473685</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="AW37">
-        <v>0.6736842105263158</v>
+        <v>0.6628571428571429</v>
       </c>
       <c r="AX37">
-        <v>0.6947368421052632</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="AY37">
-        <v>0.7157894736842105</v>
+        <v>0.7085714285714286</v>
       </c>
       <c r="AZ37">
-        <v>0.736842105263158</v>
+        <v>0.7314285714285714</v>
       </c>
       <c r="BA37">
-        <v>0.7578947368421053</v>
+        <v>0.7542857142857143</v>
       </c>
       <c r="BB37">
-        <v>0.7789473684210527</v>
+        <v>0.7771428571428571</v>
       </c>
       <c r="BC37">
         <v>0.8</v>
@@ -35228,115 +35228,115 @@
         <v>0</v>
       </c>
       <c r="R38">
-        <v>0.02105263157894737</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>0.04210526315789474</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>0.06315789473684211</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>0.08421052631578947</v>
+        <v>0.02285714285714286</v>
       </c>
       <c r="V38">
-        <v>0.1052631578947368</v>
+        <v>0.04571428571428571</v>
       </c>
       <c r="W38">
-        <v>0.1263157894736842</v>
+        <v>0.06857142857142857</v>
       </c>
       <c r="X38">
-        <v>0.1473684210526316</v>
+        <v>0.09142857142857143</v>
       </c>
       <c r="Y38">
-        <v>0.1684210526315789</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="Z38">
-        <v>0.1894736842105263</v>
+        <v>0.1371428571428571</v>
       </c>
       <c r="AA38">
-        <v>0.2105263157894737</v>
+        <v>0.16</v>
       </c>
       <c r="AB38">
-        <v>0.2315789473684211</v>
+        <v>0.1828571428571429</v>
       </c>
       <c r="AC38">
-        <v>0.2526315789473684</v>
+        <v>0.2057142857142857</v>
       </c>
       <c r="AD38">
-        <v>0.2736842105263158</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="AE38">
-        <v>0.2947368421052631</v>
+        <v>0.2514285714285714</v>
       </c>
       <c r="AF38">
-        <v>0.3157894736842106</v>
+        <v>0.2742857142857143</v>
       </c>
       <c r="AG38">
-        <v>0.3368421052631579</v>
+        <v>0.2971428571428572</v>
       </c>
       <c r="AH38">
-        <v>0.3578947368421053</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="AI38">
-        <v>0.3789473684210526</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="AJ38">
-        <v>0.4</v>
+        <v>0.3657142857142857</v>
       </c>
       <c r="AK38">
-        <v>0.4210526315789473</v>
+        <v>0.3885714285714286</v>
       </c>
       <c r="AL38">
-        <v>0.4421052631578948</v>
+        <v>0.4114285714285714</v>
       </c>
       <c r="AM38">
-        <v>0.4631578947368422</v>
+        <v>0.4342857142857143</v>
       </c>
       <c r="AN38">
-        <v>0.4842105263157895</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="AO38">
-        <v>0.5052631578947369</v>
+        <v>0.48</v>
       </c>
       <c r="AP38">
-        <v>0.5263157894736843</v>
+        <v>0.5028571428571429</v>
       </c>
       <c r="AQ38">
-        <v>0.5473684210526316</v>
+        <v>0.5257142857142857</v>
       </c>
       <c r="AR38">
-        <v>0.5684210526315789</v>
+        <v>0.5485714285714286</v>
       </c>
       <c r="AS38">
-        <v>0.5894736842105263</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="AT38">
-        <v>0.6105263157894738</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="AU38">
-        <v>0.6315789473684211</v>
+        <v>0.6171428571428572</v>
       </c>
       <c r="AV38">
-        <v>0.6526315789473685</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="AW38">
-        <v>0.6736842105263158</v>
+        <v>0.6628571428571429</v>
       </c>
       <c r="AX38">
-        <v>0.6947368421052632</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="AY38">
-        <v>0.7157894736842105</v>
+        <v>0.7085714285714286</v>
       </c>
       <c r="AZ38">
-        <v>0.736842105263158</v>
+        <v>0.7314285714285714</v>
       </c>
       <c r="BA38">
-        <v>0.7578947368421053</v>
+        <v>0.7542857142857143</v>
       </c>
       <c r="BB38">
-        <v>0.7789473684210527</v>
+        <v>0.7771428571428571</v>
       </c>
       <c r="BC38">
         <v>0.8</v>
@@ -35383,100 +35383,100 @@
         <v>0.9</v>
       </c>
       <c r="S39">
+        <v>0.9</v>
+      </c>
+      <c r="T39">
+        <v>0.9</v>
+      </c>
+      <c r="U39">
+        <v>0.9</v>
+      </c>
+      <c r="V39">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W39">
+        <v>0.9</v>
+      </c>
+      <c r="X39">
+        <v>0.9</v>
+      </c>
+      <c r="Y39">
+        <v>0.9</v>
+      </c>
+      <c r="Z39">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA39">
         <v>0.9000000000000001</v>
       </c>
-      <c r="T39">
-        <v>0.9</v>
-      </c>
-      <c r="U39">
-        <v>0.9</v>
-      </c>
-      <c r="V39">
+      <c r="AB39">
+        <v>0.9</v>
+      </c>
+      <c r="AC39">
+        <v>0.9</v>
+      </c>
+      <c r="AD39">
+        <v>0.9</v>
+      </c>
+      <c r="AE39">
         <v>0.9000000000000001</v>
       </c>
-      <c r="W39">
-        <v>0.9</v>
-      </c>
-      <c r="X39">
+      <c r="AF39">
+        <v>0.9</v>
+      </c>
+      <c r="AG39">
+        <v>0.9</v>
+      </c>
+      <c r="AH39">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI39">
         <v>0.8999999999999999</v>
       </c>
-      <c r="Y39">
-        <v>0.9</v>
-      </c>
-      <c r="Z39">
-        <v>0.9</v>
-      </c>
-      <c r="AA39">
-        <v>0.9</v>
-      </c>
-      <c r="AB39">
-        <v>0.9</v>
-      </c>
-      <c r="AC39">
-        <v>0.9</v>
-      </c>
-      <c r="AD39">
+      <c r="AJ39">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AE39">
+      <c r="AK39">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AF39">
-        <v>0.9</v>
-      </c>
-      <c r="AG39">
+      <c r="AL39">
+        <v>0.9</v>
+      </c>
+      <c r="AM39">
+        <v>0.9</v>
+      </c>
+      <c r="AN39">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO39">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AH39">
+      <c r="AP39">
+        <v>0.9</v>
+      </c>
+      <c r="AQ39">
+        <v>0.9</v>
+      </c>
+      <c r="AR39">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS39">
+        <v>0.9</v>
+      </c>
+      <c r="AT39">
+        <v>0.9</v>
+      </c>
+      <c r="AU39">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AI39">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AJ39">
-        <v>0.9</v>
-      </c>
-      <c r="AK39">
-        <v>0.9</v>
-      </c>
-      <c r="AL39">
-        <v>0.9</v>
-      </c>
-      <c r="AM39">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AN39">
-        <v>0.9</v>
-      </c>
-      <c r="AO39">
-        <v>0.9</v>
-      </c>
-      <c r="AP39">
-        <v>0.9</v>
-      </c>
-      <c r="AQ39">
-        <v>0.9</v>
-      </c>
-      <c r="AR39">
-        <v>0.9</v>
-      </c>
-      <c r="AS39">
-        <v>0.9</v>
-      </c>
-      <c r="AT39">
-        <v>0.9</v>
-      </c>
-      <c r="AU39">
-        <v>0.9</v>
-      </c>
       <c r="AV39">
+        <v>0.9</v>
+      </c>
+      <c r="AW39">
+        <v>0.9</v>
+      </c>
+      <c r="AX39">
         <v>0.8999999999999999</v>
-      </c>
-      <c r="AW39">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AX39">
-        <v>0.9</v>
       </c>
       <c r="AY39">
         <v>0.9</v>
@@ -35535,100 +35535,100 @@
         <v>0.9</v>
       </c>
       <c r="S40">
+        <v>0.9</v>
+      </c>
+      <c r="T40">
+        <v>0.9</v>
+      </c>
+      <c r="U40">
+        <v>0.9</v>
+      </c>
+      <c r="V40">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W40">
+        <v>0.9</v>
+      </c>
+      <c r="X40">
+        <v>0.9</v>
+      </c>
+      <c r="Y40">
+        <v>0.9</v>
+      </c>
+      <c r="Z40">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA40">
         <v>0.9000000000000001</v>
       </c>
-      <c r="T40">
-        <v>0.9</v>
-      </c>
-      <c r="U40">
-        <v>0.9</v>
-      </c>
-      <c r="V40">
+      <c r="AB40">
+        <v>0.9</v>
+      </c>
+      <c r="AC40">
+        <v>0.9</v>
+      </c>
+      <c r="AD40">
+        <v>0.9</v>
+      </c>
+      <c r="AE40">
         <v>0.9000000000000001</v>
       </c>
-      <c r="W40">
-        <v>0.9</v>
-      </c>
-      <c r="X40">
+      <c r="AF40">
+        <v>0.9</v>
+      </c>
+      <c r="AG40">
+        <v>0.9</v>
+      </c>
+      <c r="AH40">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI40">
         <v>0.8999999999999999</v>
       </c>
-      <c r="Y40">
-        <v>0.9</v>
-      </c>
-      <c r="Z40">
-        <v>0.9</v>
-      </c>
-      <c r="AA40">
-        <v>0.9</v>
-      </c>
-      <c r="AB40">
-        <v>0.9</v>
-      </c>
-      <c r="AC40">
-        <v>0.9</v>
-      </c>
-      <c r="AD40">
+      <c r="AJ40">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AE40">
+      <c r="AK40">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AF40">
-        <v>0.9</v>
-      </c>
-      <c r="AG40">
+      <c r="AL40">
+        <v>0.9</v>
+      </c>
+      <c r="AM40">
+        <v>0.9</v>
+      </c>
+      <c r="AN40">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO40">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AH40">
+      <c r="AP40">
+        <v>0.9</v>
+      </c>
+      <c r="AQ40">
+        <v>0.9</v>
+      </c>
+      <c r="AR40">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS40">
+        <v>0.9</v>
+      </c>
+      <c r="AT40">
+        <v>0.9</v>
+      </c>
+      <c r="AU40">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AI40">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AJ40">
-        <v>0.9</v>
-      </c>
-      <c r="AK40">
-        <v>0.9</v>
-      </c>
-      <c r="AL40">
-        <v>0.9</v>
-      </c>
-      <c r="AM40">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AN40">
-        <v>0.9</v>
-      </c>
-      <c r="AO40">
-        <v>0.9</v>
-      </c>
-      <c r="AP40">
-        <v>0.9</v>
-      </c>
-      <c r="AQ40">
-        <v>0.9</v>
-      </c>
-      <c r="AR40">
-        <v>0.9</v>
-      </c>
-      <c r="AS40">
-        <v>0.9</v>
-      </c>
-      <c r="AT40">
-        <v>0.9</v>
-      </c>
-      <c r="AU40">
-        <v>0.9</v>
-      </c>
       <c r="AV40">
+        <v>0.9</v>
+      </c>
+      <c r="AW40">
+        <v>0.9</v>
+      </c>
+      <c r="AX40">
         <v>0.8999999999999999</v>
-      </c>
-      <c r="AW40">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AX40">
-        <v>0.9</v>
       </c>
       <c r="AY40">
         <v>0.9</v>
@@ -35687,100 +35687,100 @@
         <v>0.9</v>
       </c>
       <c r="S41">
+        <v>0.9</v>
+      </c>
+      <c r="T41">
+        <v>0.9</v>
+      </c>
+      <c r="U41">
+        <v>0.9</v>
+      </c>
+      <c r="V41">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W41">
+        <v>0.9</v>
+      </c>
+      <c r="X41">
+        <v>0.9</v>
+      </c>
+      <c r="Y41">
+        <v>0.9</v>
+      </c>
+      <c r="Z41">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA41">
         <v>0.9000000000000001</v>
       </c>
-      <c r="T41">
-        <v>0.9</v>
-      </c>
-      <c r="U41">
-        <v>0.9</v>
-      </c>
-      <c r="V41">
+      <c r="AB41">
+        <v>0.9</v>
+      </c>
+      <c r="AC41">
+        <v>0.9</v>
+      </c>
+      <c r="AD41">
+        <v>0.9</v>
+      </c>
+      <c r="AE41">
         <v>0.9000000000000001</v>
       </c>
-      <c r="W41">
-        <v>0.9</v>
-      </c>
-      <c r="X41">
+      <c r="AF41">
+        <v>0.9</v>
+      </c>
+      <c r="AG41">
+        <v>0.9</v>
+      </c>
+      <c r="AH41">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI41">
         <v>0.8999999999999999</v>
       </c>
-      <c r="Y41">
-        <v>0.9</v>
-      </c>
-      <c r="Z41">
-        <v>0.9</v>
-      </c>
-      <c r="AA41">
-        <v>0.9</v>
-      </c>
-      <c r="AB41">
-        <v>0.9</v>
-      </c>
-      <c r="AC41">
-        <v>0.9</v>
-      </c>
-      <c r="AD41">
+      <c r="AJ41">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AE41">
+      <c r="AK41">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AF41">
-        <v>0.9</v>
-      </c>
-      <c r="AG41">
+      <c r="AL41">
+        <v>0.9</v>
+      </c>
+      <c r="AM41">
+        <v>0.9</v>
+      </c>
+      <c r="AN41">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO41">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AH41">
+      <c r="AP41">
+        <v>0.9</v>
+      </c>
+      <c r="AQ41">
+        <v>0.9</v>
+      </c>
+      <c r="AR41">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS41">
+        <v>0.9</v>
+      </c>
+      <c r="AT41">
+        <v>0.9</v>
+      </c>
+      <c r="AU41">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AI41">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AJ41">
-        <v>0.9</v>
-      </c>
-      <c r="AK41">
-        <v>0.9</v>
-      </c>
-      <c r="AL41">
-        <v>0.9</v>
-      </c>
-      <c r="AM41">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AN41">
-        <v>0.9</v>
-      </c>
-      <c r="AO41">
-        <v>0.9</v>
-      </c>
-      <c r="AP41">
-        <v>0.9</v>
-      </c>
-      <c r="AQ41">
-        <v>0.9</v>
-      </c>
-      <c r="AR41">
-        <v>0.9</v>
-      </c>
-      <c r="AS41">
-        <v>0.9</v>
-      </c>
-      <c r="AT41">
-        <v>0.9</v>
-      </c>
-      <c r="AU41">
-        <v>0.9</v>
-      </c>
       <c r="AV41">
+        <v>0.9</v>
+      </c>
+      <c r="AW41">
+        <v>0.9</v>
+      </c>
+      <c r="AX41">
         <v>0.8999999999999999</v>
-      </c>
-      <c r="AW41">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AX41">
-        <v>0.9</v>
       </c>
       <c r="AY41">
         <v>0.9</v>
@@ -35839,100 +35839,100 @@
         <v>0.9</v>
       </c>
       <c r="S42">
+        <v>0.9</v>
+      </c>
+      <c r="T42">
+        <v>0.9</v>
+      </c>
+      <c r="U42">
+        <v>0.9</v>
+      </c>
+      <c r="V42">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W42">
+        <v>0.9</v>
+      </c>
+      <c r="X42">
+        <v>0.9</v>
+      </c>
+      <c r="Y42">
+        <v>0.9</v>
+      </c>
+      <c r="Z42">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA42">
         <v>0.9000000000000001</v>
       </c>
-      <c r="T42">
-        <v>0.9</v>
-      </c>
-      <c r="U42">
-        <v>0.9</v>
-      </c>
-      <c r="V42">
+      <c r="AB42">
+        <v>0.9</v>
+      </c>
+      <c r="AC42">
+        <v>0.9</v>
+      </c>
+      <c r="AD42">
+        <v>0.9</v>
+      </c>
+      <c r="AE42">
         <v>0.9000000000000001</v>
       </c>
-      <c r="W42">
-        <v>0.9</v>
-      </c>
-      <c r="X42">
+      <c r="AF42">
+        <v>0.9</v>
+      </c>
+      <c r="AG42">
+        <v>0.9</v>
+      </c>
+      <c r="AH42">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI42">
         <v>0.8999999999999999</v>
       </c>
-      <c r="Y42">
-        <v>0.9</v>
-      </c>
-      <c r="Z42">
-        <v>0.9</v>
-      </c>
-      <c r="AA42">
-        <v>0.9</v>
-      </c>
-      <c r="AB42">
-        <v>0.9</v>
-      </c>
-      <c r="AC42">
-        <v>0.9</v>
-      </c>
-      <c r="AD42">
+      <c r="AJ42">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AE42">
+      <c r="AK42">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AF42">
-        <v>0.9</v>
-      </c>
-      <c r="AG42">
+      <c r="AL42">
+        <v>0.9</v>
+      </c>
+      <c r="AM42">
+        <v>0.9</v>
+      </c>
+      <c r="AN42">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO42">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AH42">
+      <c r="AP42">
+        <v>0.9</v>
+      </c>
+      <c r="AQ42">
+        <v>0.9</v>
+      </c>
+      <c r="AR42">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS42">
+        <v>0.9</v>
+      </c>
+      <c r="AT42">
+        <v>0.9</v>
+      </c>
+      <c r="AU42">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AI42">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AJ42">
-        <v>0.9</v>
-      </c>
-      <c r="AK42">
-        <v>0.9</v>
-      </c>
-      <c r="AL42">
-        <v>0.9</v>
-      </c>
-      <c r="AM42">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AN42">
-        <v>0.9</v>
-      </c>
-      <c r="AO42">
-        <v>0.9</v>
-      </c>
-      <c r="AP42">
-        <v>0.9</v>
-      </c>
-      <c r="AQ42">
-        <v>0.9</v>
-      </c>
-      <c r="AR42">
-        <v>0.9</v>
-      </c>
-      <c r="AS42">
-        <v>0.9</v>
-      </c>
-      <c r="AT42">
-        <v>0.9</v>
-      </c>
-      <c r="AU42">
-        <v>0.9</v>
-      </c>
       <c r="AV42">
+        <v>0.9</v>
+      </c>
+      <c r="AW42">
+        <v>0.9</v>
+      </c>
+      <c r="AX42">
         <v>0.8999999999999999</v>
-      </c>
-      <c r="AW42">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AX42">
-        <v>0.9</v>
       </c>
       <c r="AY42">
         <v>0.9</v>
@@ -35991,100 +35991,100 @@
         <v>0.9</v>
       </c>
       <c r="S43">
+        <v>0.9</v>
+      </c>
+      <c r="T43">
+        <v>0.9</v>
+      </c>
+      <c r="U43">
+        <v>0.9</v>
+      </c>
+      <c r="V43">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W43">
+        <v>0.9</v>
+      </c>
+      <c r="X43">
+        <v>0.9</v>
+      </c>
+      <c r="Y43">
+        <v>0.9</v>
+      </c>
+      <c r="Z43">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA43">
         <v>0.9000000000000001</v>
       </c>
-      <c r="T43">
-        <v>0.9</v>
-      </c>
-      <c r="U43">
-        <v>0.9</v>
-      </c>
-      <c r="V43">
+      <c r="AB43">
+        <v>0.9</v>
+      </c>
+      <c r="AC43">
+        <v>0.9</v>
+      </c>
+      <c r="AD43">
+        <v>0.9</v>
+      </c>
+      <c r="AE43">
         <v>0.9000000000000001</v>
       </c>
-      <c r="W43">
-        <v>0.9</v>
-      </c>
-      <c r="X43">
+      <c r="AF43">
+        <v>0.9</v>
+      </c>
+      <c r="AG43">
+        <v>0.9</v>
+      </c>
+      <c r="AH43">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI43">
         <v>0.8999999999999999</v>
       </c>
-      <c r="Y43">
-        <v>0.9</v>
-      </c>
-      <c r="Z43">
-        <v>0.9</v>
-      </c>
-      <c r="AA43">
-        <v>0.9</v>
-      </c>
-      <c r="AB43">
-        <v>0.9</v>
-      </c>
-      <c r="AC43">
-        <v>0.9</v>
-      </c>
-      <c r="AD43">
+      <c r="AJ43">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AE43">
+      <c r="AK43">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AF43">
-        <v>0.9</v>
-      </c>
-      <c r="AG43">
+      <c r="AL43">
+        <v>0.9</v>
+      </c>
+      <c r="AM43">
+        <v>0.9</v>
+      </c>
+      <c r="AN43">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO43">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AH43">
+      <c r="AP43">
+        <v>0.9</v>
+      </c>
+      <c r="AQ43">
+        <v>0.9</v>
+      </c>
+      <c r="AR43">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS43">
+        <v>0.9</v>
+      </c>
+      <c r="AT43">
+        <v>0.9</v>
+      </c>
+      <c r="AU43">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AI43">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AJ43">
-        <v>0.9</v>
-      </c>
-      <c r="AK43">
-        <v>0.9</v>
-      </c>
-      <c r="AL43">
-        <v>0.9</v>
-      </c>
-      <c r="AM43">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AN43">
-        <v>0.9</v>
-      </c>
-      <c r="AO43">
-        <v>0.9</v>
-      </c>
-      <c r="AP43">
-        <v>0.9</v>
-      </c>
-      <c r="AQ43">
-        <v>0.9</v>
-      </c>
-      <c r="AR43">
-        <v>0.9</v>
-      </c>
-      <c r="AS43">
-        <v>0.9</v>
-      </c>
-      <c r="AT43">
-        <v>0.9</v>
-      </c>
-      <c r="AU43">
-        <v>0.9</v>
-      </c>
       <c r="AV43">
+        <v>0.9</v>
+      </c>
+      <c r="AW43">
+        <v>0.9</v>
+      </c>
+      <c r="AX43">
         <v>0.8999999999999999</v>
-      </c>
-      <c r="AW43">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AX43">
-        <v>0.9</v>
       </c>
       <c r="AY43">
         <v>0.9</v>
@@ -36143,100 +36143,100 @@
         <v>0.9</v>
       </c>
       <c r="S44">
+        <v>0.9</v>
+      </c>
+      <c r="T44">
+        <v>0.9</v>
+      </c>
+      <c r="U44">
+        <v>0.9</v>
+      </c>
+      <c r="V44">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W44">
+        <v>0.9</v>
+      </c>
+      <c r="X44">
+        <v>0.9</v>
+      </c>
+      <c r="Y44">
+        <v>0.9</v>
+      </c>
+      <c r="Z44">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA44">
         <v>0.9000000000000001</v>
       </c>
-      <c r="T44">
-        <v>0.9</v>
-      </c>
-      <c r="U44">
-        <v>0.9</v>
-      </c>
-      <c r="V44">
+      <c r="AB44">
+        <v>0.9</v>
+      </c>
+      <c r="AC44">
+        <v>0.9</v>
+      </c>
+      <c r="AD44">
+        <v>0.9</v>
+      </c>
+      <c r="AE44">
         <v>0.9000000000000001</v>
       </c>
-      <c r="W44">
-        <v>0.9</v>
-      </c>
-      <c r="X44">
+      <c r="AF44">
+        <v>0.9</v>
+      </c>
+      <c r="AG44">
+        <v>0.9</v>
+      </c>
+      <c r="AH44">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI44">
         <v>0.8999999999999999</v>
       </c>
-      <c r="Y44">
-        <v>0.9</v>
-      </c>
-      <c r="Z44">
-        <v>0.9</v>
-      </c>
-      <c r="AA44">
-        <v>0.9</v>
-      </c>
-      <c r="AB44">
-        <v>0.9</v>
-      </c>
-      <c r="AC44">
-        <v>0.9</v>
-      </c>
-      <c r="AD44">
+      <c r="AJ44">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AE44">
+      <c r="AK44">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AF44">
-        <v>0.9</v>
-      </c>
-      <c r="AG44">
+      <c r="AL44">
+        <v>0.9</v>
+      </c>
+      <c r="AM44">
+        <v>0.9</v>
+      </c>
+      <c r="AN44">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO44">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AH44">
+      <c r="AP44">
+        <v>0.9</v>
+      </c>
+      <c r="AQ44">
+        <v>0.9</v>
+      </c>
+      <c r="AR44">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS44">
+        <v>0.9</v>
+      </c>
+      <c r="AT44">
+        <v>0.9</v>
+      </c>
+      <c r="AU44">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AI44">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AJ44">
-        <v>0.9</v>
-      </c>
-      <c r="AK44">
-        <v>0.9</v>
-      </c>
-      <c r="AL44">
-        <v>0.9</v>
-      </c>
-      <c r="AM44">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AN44">
-        <v>0.9</v>
-      </c>
-      <c r="AO44">
-        <v>0.9</v>
-      </c>
-      <c r="AP44">
-        <v>0.9</v>
-      </c>
-      <c r="AQ44">
-        <v>0.9</v>
-      </c>
-      <c r="AR44">
-        <v>0.9</v>
-      </c>
-      <c r="AS44">
-        <v>0.9</v>
-      </c>
-      <c r="AT44">
-        <v>0.9</v>
-      </c>
-      <c r="AU44">
-        <v>0.9</v>
-      </c>
       <c r="AV44">
+        <v>0.9</v>
+      </c>
+      <c r="AW44">
+        <v>0.9</v>
+      </c>
+      <c r="AX44">
         <v>0.8999999999999999</v>
-      </c>
-      <c r="AW44">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AX44">
-        <v>0.9</v>
       </c>
       <c r="AY44">
         <v>0.9</v>
@@ -39661,115 +39661,115 @@
         <v>0</v>
       </c>
       <c r="R23">
-        <v>0.02105263157894737</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>0.04210526315789474</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>0.06315789473684211</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>0.08421052631578947</v>
+        <v>0.02285714285714286</v>
       </c>
       <c r="V23">
-        <v>0.1052631578947368</v>
+        <v>0.04571428571428571</v>
       </c>
       <c r="W23">
-        <v>0.1263157894736842</v>
+        <v>0.06857142857142857</v>
       </c>
       <c r="X23">
-        <v>0.1473684210526316</v>
+        <v>0.09142857142857143</v>
       </c>
       <c r="Y23">
-        <v>0.1684210526315789</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="Z23">
-        <v>0.1894736842105263</v>
+        <v>0.1371428571428571</v>
       </c>
       <c r="AA23">
-        <v>0.2105263157894737</v>
+        <v>0.16</v>
       </c>
       <c r="AB23">
-        <v>0.2315789473684211</v>
+        <v>0.1828571428571429</v>
       </c>
       <c r="AC23">
-        <v>0.2526315789473684</v>
+        <v>0.2057142857142857</v>
       </c>
       <c r="AD23">
-        <v>0.2736842105263158</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="AE23">
-        <v>0.2947368421052631</v>
+        <v>0.2514285714285714</v>
       </c>
       <c r="AF23">
-        <v>0.3157894736842106</v>
+        <v>0.2742857142857143</v>
       </c>
       <c r="AG23">
-        <v>0.3368421052631579</v>
+        <v>0.2971428571428572</v>
       </c>
       <c r="AH23">
-        <v>0.3578947368421053</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="AI23">
-        <v>0.3789473684210526</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="AJ23">
-        <v>0.4</v>
+        <v>0.3657142857142857</v>
       </c>
       <c r="AK23">
-        <v>0.4210526315789473</v>
+        <v>0.3885714285714286</v>
       </c>
       <c r="AL23">
-        <v>0.4421052631578948</v>
+        <v>0.4114285714285714</v>
       </c>
       <c r="AM23">
-        <v>0.4631578947368422</v>
+        <v>0.4342857142857143</v>
       </c>
       <c r="AN23">
-        <v>0.4842105263157895</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="AO23">
-        <v>0.5052631578947369</v>
+        <v>0.48</v>
       </c>
       <c r="AP23">
-        <v>0.5263157894736843</v>
+        <v>0.5028571428571429</v>
       </c>
       <c r="AQ23">
-        <v>0.5473684210526316</v>
+        <v>0.5257142857142857</v>
       </c>
       <c r="AR23">
-        <v>0.5684210526315789</v>
+        <v>0.5485714285714286</v>
       </c>
       <c r="AS23">
-        <v>0.5894736842105263</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="AT23">
-        <v>0.6105263157894738</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="AU23">
-        <v>0.6315789473684211</v>
+        <v>0.6171428571428572</v>
       </c>
       <c r="AV23">
-        <v>0.6526315789473685</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="AW23">
-        <v>0.6736842105263158</v>
+        <v>0.6628571428571429</v>
       </c>
       <c r="AX23">
-        <v>0.6947368421052632</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="AY23">
-        <v>0.7157894736842105</v>
+        <v>0.7085714285714286</v>
       </c>
       <c r="AZ23">
-        <v>0.736842105263158</v>
+        <v>0.7314285714285714</v>
       </c>
       <c r="BA23">
-        <v>0.7578947368421053</v>
+        <v>0.7542857142857143</v>
       </c>
       <c r="BB23">
-        <v>0.7789473684210527</v>
+        <v>0.7771428571428571</v>
       </c>
       <c r="BC23">
         <v>0.8</v>
@@ -39813,115 +39813,115 @@
         <v>0</v>
       </c>
       <c r="R24">
-        <v>0.02105263157894737</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>0.04210526315789474</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>0.06315789473684211</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>0.08421052631578947</v>
+        <v>0.02285714285714286</v>
       </c>
       <c r="V24">
-        <v>0.1052631578947368</v>
+        <v>0.04571428571428571</v>
       </c>
       <c r="W24">
-        <v>0.1263157894736842</v>
+        <v>0.06857142857142857</v>
       </c>
       <c r="X24">
-        <v>0.1473684210526316</v>
+        <v>0.09142857142857143</v>
       </c>
       <c r="Y24">
-        <v>0.1684210526315789</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="Z24">
-        <v>0.1894736842105263</v>
+        <v>0.1371428571428571</v>
       </c>
       <c r="AA24">
-        <v>0.2105263157894737</v>
+        <v>0.16</v>
       </c>
       <c r="AB24">
-        <v>0.2315789473684211</v>
+        <v>0.1828571428571429</v>
       </c>
       <c r="AC24">
-        <v>0.2526315789473684</v>
+        <v>0.2057142857142857</v>
       </c>
       <c r="AD24">
-        <v>0.2736842105263158</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="AE24">
-        <v>0.2947368421052631</v>
+        <v>0.2514285714285714</v>
       </c>
       <c r="AF24">
-        <v>0.3157894736842106</v>
+        <v>0.2742857142857143</v>
       </c>
       <c r="AG24">
-        <v>0.3368421052631579</v>
+        <v>0.2971428571428572</v>
       </c>
       <c r="AH24">
-        <v>0.3578947368421053</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="AI24">
-        <v>0.3789473684210526</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="AJ24">
-        <v>0.4</v>
+        <v>0.3657142857142857</v>
       </c>
       <c r="AK24">
-        <v>0.4210526315789473</v>
+        <v>0.3885714285714286</v>
       </c>
       <c r="AL24">
-        <v>0.4421052631578948</v>
+        <v>0.4114285714285714</v>
       </c>
       <c r="AM24">
-        <v>0.4631578947368422</v>
+        <v>0.4342857142857143</v>
       </c>
       <c r="AN24">
-        <v>0.4842105263157895</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="AO24">
-        <v>0.5052631578947369</v>
+        <v>0.48</v>
       </c>
       <c r="AP24">
-        <v>0.5263157894736843</v>
+        <v>0.5028571428571429</v>
       </c>
       <c r="AQ24">
-        <v>0.5473684210526316</v>
+        <v>0.5257142857142857</v>
       </c>
       <c r="AR24">
-        <v>0.5684210526315789</v>
+        <v>0.5485714285714286</v>
       </c>
       <c r="AS24">
-        <v>0.5894736842105263</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="AT24">
-        <v>0.6105263157894738</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="AU24">
-        <v>0.6315789473684211</v>
+        <v>0.6171428571428572</v>
       </c>
       <c r="AV24">
-        <v>0.6526315789473685</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="AW24">
-        <v>0.6736842105263158</v>
+        <v>0.6628571428571429</v>
       </c>
       <c r="AX24">
-        <v>0.6947368421052632</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="AY24">
-        <v>0.7157894736842105</v>
+        <v>0.7085714285714286</v>
       </c>
       <c r="AZ24">
-        <v>0.736842105263158</v>
+        <v>0.7314285714285714</v>
       </c>
       <c r="BA24">
-        <v>0.7578947368421053</v>
+        <v>0.7542857142857143</v>
       </c>
       <c r="BB24">
-        <v>0.7789473684210527</v>
+        <v>0.7771428571428571</v>
       </c>
       <c r="BC24">
         <v>0.8</v>
@@ -39965,115 +39965,115 @@
         <v>0</v>
       </c>
       <c r="R25">
-        <v>0.02105263157894737</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>0.04210526315789474</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>0.06315789473684211</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>0.08421052631578947</v>
+        <v>0.02285714285714286</v>
       </c>
       <c r="V25">
-        <v>0.1052631578947368</v>
+        <v>0.04571428571428571</v>
       </c>
       <c r="W25">
-        <v>0.1263157894736842</v>
+        <v>0.06857142857142857</v>
       </c>
       <c r="X25">
-        <v>0.1473684210526316</v>
+        <v>0.09142857142857143</v>
       </c>
       <c r="Y25">
-        <v>0.1684210526315789</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="Z25">
-        <v>0.1894736842105263</v>
+        <v>0.1371428571428571</v>
       </c>
       <c r="AA25">
-        <v>0.2105263157894737</v>
+        <v>0.16</v>
       </c>
       <c r="AB25">
-        <v>0.2315789473684211</v>
+        <v>0.1828571428571429</v>
       </c>
       <c r="AC25">
-        <v>0.2526315789473684</v>
+        <v>0.2057142857142857</v>
       </c>
       <c r="AD25">
-        <v>0.2736842105263158</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="AE25">
-        <v>0.2947368421052631</v>
+        <v>0.2514285714285714</v>
       </c>
       <c r="AF25">
-        <v>0.3157894736842106</v>
+        <v>0.2742857142857143</v>
       </c>
       <c r="AG25">
-        <v>0.3368421052631579</v>
+        <v>0.2971428571428572</v>
       </c>
       <c r="AH25">
-        <v>0.3578947368421053</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="AI25">
-        <v>0.3789473684210526</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="AJ25">
-        <v>0.4</v>
+        <v>0.3657142857142857</v>
       </c>
       <c r="AK25">
-        <v>0.4210526315789473</v>
+        <v>0.3885714285714286</v>
       </c>
       <c r="AL25">
-        <v>0.4421052631578948</v>
+        <v>0.4114285714285714</v>
       </c>
       <c r="AM25">
-        <v>0.4631578947368422</v>
+        <v>0.4342857142857143</v>
       </c>
       <c r="AN25">
-        <v>0.4842105263157895</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="AO25">
-        <v>0.5052631578947369</v>
+        <v>0.48</v>
       </c>
       <c r="AP25">
-        <v>0.5263157894736843</v>
+        <v>0.5028571428571429</v>
       </c>
       <c r="AQ25">
-        <v>0.5473684210526316</v>
+        <v>0.5257142857142857</v>
       </c>
       <c r="AR25">
-        <v>0.5684210526315789</v>
+        <v>0.5485714285714286</v>
       </c>
       <c r="AS25">
-        <v>0.5894736842105263</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="AT25">
-        <v>0.6105263157894738</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="AU25">
-        <v>0.6315789473684211</v>
+        <v>0.6171428571428572</v>
       </c>
       <c r="AV25">
-        <v>0.6526315789473685</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="AW25">
-        <v>0.6736842105263158</v>
+        <v>0.6628571428571429</v>
       </c>
       <c r="AX25">
-        <v>0.6947368421052632</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="AY25">
-        <v>0.7157894736842105</v>
+        <v>0.7085714285714286</v>
       </c>
       <c r="AZ25">
-        <v>0.736842105263158</v>
+        <v>0.7314285714285714</v>
       </c>
       <c r="BA25">
-        <v>0.7578947368421053</v>
+        <v>0.7542857142857143</v>
       </c>
       <c r="BB25">
-        <v>0.7789473684210527</v>
+        <v>0.7771428571428571</v>
       </c>
       <c r="BC25">
         <v>0.8</v>
@@ -40117,115 +40117,115 @@
         <v>0</v>
       </c>
       <c r="R26">
-        <v>0.02105263157894737</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>0.04210526315789474</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>0.06315789473684211</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>0.08421052631578947</v>
+        <v>0.02285714285714286</v>
       </c>
       <c r="V26">
-        <v>0.1052631578947368</v>
+        <v>0.04571428571428571</v>
       </c>
       <c r="W26">
-        <v>0.1263157894736842</v>
+        <v>0.06857142857142857</v>
       </c>
       <c r="X26">
-        <v>0.1473684210526316</v>
+        <v>0.09142857142857143</v>
       </c>
       <c r="Y26">
-        <v>0.1684210526315789</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="Z26">
-        <v>0.1894736842105263</v>
+        <v>0.1371428571428571</v>
       </c>
       <c r="AA26">
-        <v>0.2105263157894737</v>
+        <v>0.16</v>
       </c>
       <c r="AB26">
-        <v>0.2315789473684211</v>
+        <v>0.1828571428571429</v>
       </c>
       <c r="AC26">
-        <v>0.2526315789473684</v>
+        <v>0.2057142857142857</v>
       </c>
       <c r="AD26">
-        <v>0.2736842105263158</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="AE26">
-        <v>0.2947368421052631</v>
+        <v>0.2514285714285714</v>
       </c>
       <c r="AF26">
-        <v>0.3157894736842106</v>
+        <v>0.2742857142857143</v>
       </c>
       <c r="AG26">
-        <v>0.3368421052631579</v>
+        <v>0.2971428571428572</v>
       </c>
       <c r="AH26">
-        <v>0.3578947368421053</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="AI26">
-        <v>0.3789473684210526</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="AJ26">
-        <v>0.4</v>
+        <v>0.3657142857142857</v>
       </c>
       <c r="AK26">
-        <v>0.4210526315789473</v>
+        <v>0.3885714285714286</v>
       </c>
       <c r="AL26">
-        <v>0.4421052631578948</v>
+        <v>0.4114285714285714</v>
       </c>
       <c r="AM26">
-        <v>0.4631578947368422</v>
+        <v>0.4342857142857143</v>
       </c>
       <c r="AN26">
-        <v>0.4842105263157895</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="AO26">
-        <v>0.5052631578947369</v>
+        <v>0.48</v>
       </c>
       <c r="AP26">
-        <v>0.5263157894736843</v>
+        <v>0.5028571428571429</v>
       </c>
       <c r="AQ26">
-        <v>0.5473684210526316</v>
+        <v>0.5257142857142857</v>
       </c>
       <c r="AR26">
-        <v>0.5684210526315789</v>
+        <v>0.5485714285714286</v>
       </c>
       <c r="AS26">
-        <v>0.5894736842105263</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="AT26">
-        <v>0.6105263157894738</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="AU26">
-        <v>0.6315789473684211</v>
+        <v>0.6171428571428572</v>
       </c>
       <c r="AV26">
-        <v>0.6526315789473685</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="AW26">
-        <v>0.6736842105263158</v>
+        <v>0.6628571428571429</v>
       </c>
       <c r="AX26">
-        <v>0.6947368421052632</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="AY26">
-        <v>0.7157894736842105</v>
+        <v>0.7085714285714286</v>
       </c>
       <c r="AZ26">
-        <v>0.736842105263158</v>
+        <v>0.7314285714285714</v>
       </c>
       <c r="BA26">
-        <v>0.7578947368421053</v>
+        <v>0.7542857142857143</v>
       </c>
       <c r="BB26">
-        <v>0.7789473684210527</v>
+        <v>0.7771428571428571</v>
       </c>
       <c r="BC26">
         <v>0.8</v>
@@ -40272,100 +40272,100 @@
         <v>0.9</v>
       </c>
       <c r="S27">
+        <v>0.9</v>
+      </c>
+      <c r="T27">
+        <v>0.9</v>
+      </c>
+      <c r="U27">
+        <v>0.9</v>
+      </c>
+      <c r="V27">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W27">
+        <v>0.9</v>
+      </c>
+      <c r="X27">
+        <v>0.9</v>
+      </c>
+      <c r="Y27">
+        <v>0.9</v>
+      </c>
+      <c r="Z27">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA27">
         <v>0.9000000000000001</v>
       </c>
-      <c r="T27">
-        <v>0.9</v>
-      </c>
-      <c r="U27">
-        <v>0.9</v>
-      </c>
-      <c r="V27">
+      <c r="AB27">
+        <v>0.9</v>
+      </c>
+      <c r="AC27">
+        <v>0.9</v>
+      </c>
+      <c r="AD27">
+        <v>0.9</v>
+      </c>
+      <c r="AE27">
         <v>0.9000000000000001</v>
       </c>
-      <c r="W27">
-        <v>0.9</v>
-      </c>
-      <c r="X27">
+      <c r="AF27">
+        <v>0.9</v>
+      </c>
+      <c r="AG27">
+        <v>0.9</v>
+      </c>
+      <c r="AH27">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI27">
         <v>0.8999999999999999</v>
       </c>
-      <c r="Y27">
-        <v>0.9</v>
-      </c>
-      <c r="Z27">
-        <v>0.9</v>
-      </c>
-      <c r="AA27">
-        <v>0.9</v>
-      </c>
-      <c r="AB27">
-        <v>0.9</v>
-      </c>
-      <c r="AC27">
-        <v>0.9</v>
-      </c>
-      <c r="AD27">
+      <c r="AJ27">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AE27">
+      <c r="AK27">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AF27">
-        <v>0.9</v>
-      </c>
-      <c r="AG27">
+      <c r="AL27">
+        <v>0.9</v>
+      </c>
+      <c r="AM27">
+        <v>0.9</v>
+      </c>
+      <c r="AN27">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO27">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AH27">
+      <c r="AP27">
+        <v>0.9</v>
+      </c>
+      <c r="AQ27">
+        <v>0.9</v>
+      </c>
+      <c r="AR27">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS27">
+        <v>0.9</v>
+      </c>
+      <c r="AT27">
+        <v>0.9</v>
+      </c>
+      <c r="AU27">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AI27">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AJ27">
-        <v>0.9</v>
-      </c>
-      <c r="AK27">
-        <v>0.9</v>
-      </c>
-      <c r="AL27">
-        <v>0.9</v>
-      </c>
-      <c r="AM27">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AN27">
-        <v>0.9</v>
-      </c>
-      <c r="AO27">
-        <v>0.9</v>
-      </c>
-      <c r="AP27">
-        <v>0.9</v>
-      </c>
-      <c r="AQ27">
-        <v>0.9</v>
-      </c>
-      <c r="AR27">
-        <v>0.9</v>
-      </c>
-      <c r="AS27">
-        <v>0.9</v>
-      </c>
-      <c r="AT27">
-        <v>0.9</v>
-      </c>
-      <c r="AU27">
-        <v>0.9</v>
-      </c>
       <c r="AV27">
+        <v>0.9</v>
+      </c>
+      <c r="AW27">
+        <v>0.9</v>
+      </c>
+      <c r="AX27">
         <v>0.8999999999999999</v>
-      </c>
-      <c r="AW27">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AX27">
-        <v>0.9</v>
       </c>
       <c r="AY27">
         <v>0.9</v>
@@ -40424,100 +40424,100 @@
         <v>0.9</v>
       </c>
       <c r="S28">
+        <v>0.9</v>
+      </c>
+      <c r="T28">
+        <v>0.9</v>
+      </c>
+      <c r="U28">
+        <v>0.9</v>
+      </c>
+      <c r="V28">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W28">
+        <v>0.9</v>
+      </c>
+      <c r="X28">
+        <v>0.9</v>
+      </c>
+      <c r="Y28">
+        <v>0.9</v>
+      </c>
+      <c r="Z28">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA28">
         <v>0.9000000000000001</v>
       </c>
-      <c r="T28">
-        <v>0.9</v>
-      </c>
-      <c r="U28">
-        <v>0.9</v>
-      </c>
-      <c r="V28">
+      <c r="AB28">
+        <v>0.9</v>
+      </c>
+      <c r="AC28">
+        <v>0.9</v>
+      </c>
+      <c r="AD28">
+        <v>0.9</v>
+      </c>
+      <c r="AE28">
         <v>0.9000000000000001</v>
       </c>
-      <c r="W28">
-        <v>0.9</v>
-      </c>
-      <c r="X28">
+      <c r="AF28">
+        <v>0.9</v>
+      </c>
+      <c r="AG28">
+        <v>0.9</v>
+      </c>
+      <c r="AH28">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI28">
         <v>0.8999999999999999</v>
       </c>
-      <c r="Y28">
-        <v>0.9</v>
-      </c>
-      <c r="Z28">
-        <v>0.9</v>
-      </c>
-      <c r="AA28">
-        <v>0.9</v>
-      </c>
-      <c r="AB28">
-        <v>0.9</v>
-      </c>
-      <c r="AC28">
-        <v>0.9</v>
-      </c>
-      <c r="AD28">
+      <c r="AJ28">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AE28">
+      <c r="AK28">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AF28">
-        <v>0.9</v>
-      </c>
-      <c r="AG28">
+      <c r="AL28">
+        <v>0.9</v>
+      </c>
+      <c r="AM28">
+        <v>0.9</v>
+      </c>
+      <c r="AN28">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO28">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AH28">
+      <c r="AP28">
+        <v>0.9</v>
+      </c>
+      <c r="AQ28">
+        <v>0.9</v>
+      </c>
+      <c r="AR28">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS28">
+        <v>0.9</v>
+      </c>
+      <c r="AT28">
+        <v>0.9</v>
+      </c>
+      <c r="AU28">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AI28">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AJ28">
-        <v>0.9</v>
-      </c>
-      <c r="AK28">
-        <v>0.9</v>
-      </c>
-      <c r="AL28">
-        <v>0.9</v>
-      </c>
-      <c r="AM28">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AN28">
-        <v>0.9</v>
-      </c>
-      <c r="AO28">
-        <v>0.9</v>
-      </c>
-      <c r="AP28">
-        <v>0.9</v>
-      </c>
-      <c r="AQ28">
-        <v>0.9</v>
-      </c>
-      <c r="AR28">
-        <v>0.9</v>
-      </c>
-      <c r="AS28">
-        <v>0.9</v>
-      </c>
-      <c r="AT28">
-        <v>0.9</v>
-      </c>
-      <c r="AU28">
-        <v>0.9</v>
-      </c>
       <c r="AV28">
+        <v>0.9</v>
+      </c>
+      <c r="AW28">
+        <v>0.9</v>
+      </c>
+      <c r="AX28">
         <v>0.8999999999999999</v>
-      </c>
-      <c r="AW28">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AX28">
-        <v>0.9</v>
       </c>
       <c r="AY28">
         <v>0.9</v>
@@ -40576,100 +40576,100 @@
         <v>0.9</v>
       </c>
       <c r="S29">
+        <v>0.9</v>
+      </c>
+      <c r="T29">
+        <v>0.9</v>
+      </c>
+      <c r="U29">
+        <v>0.9</v>
+      </c>
+      <c r="V29">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W29">
+        <v>0.9</v>
+      </c>
+      <c r="X29">
+        <v>0.9</v>
+      </c>
+      <c r="Y29">
+        <v>0.9</v>
+      </c>
+      <c r="Z29">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA29">
         <v>0.9000000000000001</v>
       </c>
-      <c r="T29">
-        <v>0.9</v>
-      </c>
-      <c r="U29">
-        <v>0.9</v>
-      </c>
-      <c r="V29">
+      <c r="AB29">
+        <v>0.9</v>
+      </c>
+      <c r="AC29">
+        <v>0.9</v>
+      </c>
+      <c r="AD29">
+        <v>0.9</v>
+      </c>
+      <c r="AE29">
         <v>0.9000000000000001</v>
       </c>
-      <c r="W29">
-        <v>0.9</v>
-      </c>
-      <c r="X29">
+      <c r="AF29">
+        <v>0.9</v>
+      </c>
+      <c r="AG29">
+        <v>0.9</v>
+      </c>
+      <c r="AH29">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI29">
         <v>0.8999999999999999</v>
       </c>
-      <c r="Y29">
-        <v>0.9</v>
-      </c>
-      <c r="Z29">
-        <v>0.9</v>
-      </c>
-      <c r="AA29">
-        <v>0.9</v>
-      </c>
-      <c r="AB29">
-        <v>0.9</v>
-      </c>
-      <c r="AC29">
-        <v>0.9</v>
-      </c>
-      <c r="AD29">
+      <c r="AJ29">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AE29">
+      <c r="AK29">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AF29">
-        <v>0.9</v>
-      </c>
-      <c r="AG29">
+      <c r="AL29">
+        <v>0.9</v>
+      </c>
+      <c r="AM29">
+        <v>0.9</v>
+      </c>
+      <c r="AN29">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO29">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AH29">
+      <c r="AP29">
+        <v>0.9</v>
+      </c>
+      <c r="AQ29">
+        <v>0.9</v>
+      </c>
+      <c r="AR29">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS29">
+        <v>0.9</v>
+      </c>
+      <c r="AT29">
+        <v>0.9</v>
+      </c>
+      <c r="AU29">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AI29">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AJ29">
-        <v>0.9</v>
-      </c>
-      <c r="AK29">
-        <v>0.9</v>
-      </c>
-      <c r="AL29">
-        <v>0.9</v>
-      </c>
-      <c r="AM29">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AN29">
-        <v>0.9</v>
-      </c>
-      <c r="AO29">
-        <v>0.9</v>
-      </c>
-      <c r="AP29">
-        <v>0.9</v>
-      </c>
-      <c r="AQ29">
-        <v>0.9</v>
-      </c>
-      <c r="AR29">
-        <v>0.9</v>
-      </c>
-      <c r="AS29">
-        <v>0.9</v>
-      </c>
-      <c r="AT29">
-        <v>0.9</v>
-      </c>
-      <c r="AU29">
-        <v>0.9</v>
-      </c>
       <c r="AV29">
+        <v>0.9</v>
+      </c>
+      <c r="AW29">
+        <v>0.9</v>
+      </c>
+      <c r="AX29">
         <v>0.8999999999999999</v>
-      </c>
-      <c r="AW29">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AX29">
-        <v>0.9</v>
       </c>
       <c r="AY29">
         <v>0.9</v>
@@ -40728,100 +40728,100 @@
         <v>0.9</v>
       </c>
       <c r="S30">
+        <v>0.9</v>
+      </c>
+      <c r="T30">
+        <v>0.9</v>
+      </c>
+      <c r="U30">
+        <v>0.9</v>
+      </c>
+      <c r="V30">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W30">
+        <v>0.9</v>
+      </c>
+      <c r="X30">
+        <v>0.9</v>
+      </c>
+      <c r="Y30">
+        <v>0.9</v>
+      </c>
+      <c r="Z30">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA30">
         <v>0.9000000000000001</v>
       </c>
-      <c r="T30">
-        <v>0.9</v>
-      </c>
-      <c r="U30">
-        <v>0.9</v>
-      </c>
-      <c r="V30">
+      <c r="AB30">
+        <v>0.9</v>
+      </c>
+      <c r="AC30">
+        <v>0.9</v>
+      </c>
+      <c r="AD30">
+        <v>0.9</v>
+      </c>
+      <c r="AE30">
         <v>0.9000000000000001</v>
       </c>
-      <c r="W30">
-        <v>0.9</v>
-      </c>
-      <c r="X30">
+      <c r="AF30">
+        <v>0.9</v>
+      </c>
+      <c r="AG30">
+        <v>0.9</v>
+      </c>
+      <c r="AH30">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI30">
         <v>0.8999999999999999</v>
       </c>
-      <c r="Y30">
-        <v>0.9</v>
-      </c>
-      <c r="Z30">
-        <v>0.9</v>
-      </c>
-      <c r="AA30">
-        <v>0.9</v>
-      </c>
-      <c r="AB30">
-        <v>0.9</v>
-      </c>
-      <c r="AC30">
-        <v>0.9</v>
-      </c>
-      <c r="AD30">
+      <c r="AJ30">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AE30">
+      <c r="AK30">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AF30">
-        <v>0.9</v>
-      </c>
-      <c r="AG30">
+      <c r="AL30">
+        <v>0.9</v>
+      </c>
+      <c r="AM30">
+        <v>0.9</v>
+      </c>
+      <c r="AN30">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO30">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AH30">
+      <c r="AP30">
+        <v>0.9</v>
+      </c>
+      <c r="AQ30">
+        <v>0.9</v>
+      </c>
+      <c r="AR30">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS30">
+        <v>0.9</v>
+      </c>
+      <c r="AT30">
+        <v>0.9</v>
+      </c>
+      <c r="AU30">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AI30">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AJ30">
-        <v>0.9</v>
-      </c>
-      <c r="AK30">
-        <v>0.9</v>
-      </c>
-      <c r="AL30">
-        <v>0.9</v>
-      </c>
-      <c r="AM30">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AN30">
-        <v>0.9</v>
-      </c>
-      <c r="AO30">
-        <v>0.9</v>
-      </c>
-      <c r="AP30">
-        <v>0.9</v>
-      </c>
-      <c r="AQ30">
-        <v>0.9</v>
-      </c>
-      <c r="AR30">
-        <v>0.9</v>
-      </c>
-      <c r="AS30">
-        <v>0.9</v>
-      </c>
-      <c r="AT30">
-        <v>0.9</v>
-      </c>
-      <c r="AU30">
-        <v>0.9</v>
-      </c>
       <c r="AV30">
+        <v>0.9</v>
+      </c>
+      <c r="AW30">
+        <v>0.9</v>
+      </c>
+      <c r="AX30">
         <v>0.8999999999999999</v>
-      </c>
-      <c r="AW30">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AX30">
-        <v>0.9</v>
       </c>
       <c r="AY30">
         <v>0.9</v>
@@ -40880,100 +40880,100 @@
         <v>0.9</v>
       </c>
       <c r="S31">
+        <v>0.9</v>
+      </c>
+      <c r="T31">
+        <v>0.9</v>
+      </c>
+      <c r="U31">
+        <v>0.9</v>
+      </c>
+      <c r="V31">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W31">
+        <v>0.9</v>
+      </c>
+      <c r="X31">
+        <v>0.9</v>
+      </c>
+      <c r="Y31">
+        <v>0.9</v>
+      </c>
+      <c r="Z31">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA31">
         <v>0.9000000000000001</v>
       </c>
-      <c r="T31">
-        <v>0.9</v>
-      </c>
-      <c r="U31">
-        <v>0.9</v>
-      </c>
-      <c r="V31">
+      <c r="AB31">
+        <v>0.9</v>
+      </c>
+      <c r="AC31">
+        <v>0.9</v>
+      </c>
+      <c r="AD31">
+        <v>0.9</v>
+      </c>
+      <c r="AE31">
         <v>0.9000000000000001</v>
       </c>
-      <c r="W31">
-        <v>0.9</v>
-      </c>
-      <c r="X31">
+      <c r="AF31">
+        <v>0.9</v>
+      </c>
+      <c r="AG31">
+        <v>0.9</v>
+      </c>
+      <c r="AH31">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI31">
         <v>0.8999999999999999</v>
       </c>
-      <c r="Y31">
-        <v>0.9</v>
-      </c>
-      <c r="Z31">
-        <v>0.9</v>
-      </c>
-      <c r="AA31">
-        <v>0.9</v>
-      </c>
-      <c r="AB31">
-        <v>0.9</v>
-      </c>
-      <c r="AC31">
-        <v>0.9</v>
-      </c>
-      <c r="AD31">
+      <c r="AJ31">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AE31">
+      <c r="AK31">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AF31">
-        <v>0.9</v>
-      </c>
-      <c r="AG31">
+      <c r="AL31">
+        <v>0.9</v>
+      </c>
+      <c r="AM31">
+        <v>0.9</v>
+      </c>
+      <c r="AN31">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO31">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AH31">
+      <c r="AP31">
+        <v>0.9</v>
+      </c>
+      <c r="AQ31">
+        <v>0.9</v>
+      </c>
+      <c r="AR31">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS31">
+        <v>0.9</v>
+      </c>
+      <c r="AT31">
+        <v>0.9</v>
+      </c>
+      <c r="AU31">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AI31">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AJ31">
-        <v>0.9</v>
-      </c>
-      <c r="AK31">
-        <v>0.9</v>
-      </c>
-      <c r="AL31">
-        <v>0.9</v>
-      </c>
-      <c r="AM31">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AN31">
-        <v>0.9</v>
-      </c>
-      <c r="AO31">
-        <v>0.9</v>
-      </c>
-      <c r="AP31">
-        <v>0.9</v>
-      </c>
-      <c r="AQ31">
-        <v>0.9</v>
-      </c>
-      <c r="AR31">
-        <v>0.9</v>
-      </c>
-      <c r="AS31">
-        <v>0.9</v>
-      </c>
-      <c r="AT31">
-        <v>0.9</v>
-      </c>
-      <c r="AU31">
-        <v>0.9</v>
-      </c>
       <c r="AV31">
+        <v>0.9</v>
+      </c>
+      <c r="AW31">
+        <v>0.9</v>
+      </c>
+      <c r="AX31">
         <v>0.8999999999999999</v>
-      </c>
-      <c r="AW31">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AX31">
-        <v>0.9</v>
       </c>
       <c r="AY31">
         <v>0.9</v>
@@ -41032,100 +41032,100 @@
         <v>0.9</v>
       </c>
       <c r="S32">
+        <v>0.9</v>
+      </c>
+      <c r="T32">
+        <v>0.9</v>
+      </c>
+      <c r="U32">
+        <v>0.9</v>
+      </c>
+      <c r="V32">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="W32">
+        <v>0.9</v>
+      </c>
+      <c r="X32">
+        <v>0.9</v>
+      </c>
+      <c r="Y32">
+        <v>0.9</v>
+      </c>
+      <c r="Z32">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AA32">
         <v>0.9000000000000001</v>
       </c>
-      <c r="T32">
-        <v>0.9</v>
-      </c>
-      <c r="U32">
-        <v>0.9</v>
-      </c>
-      <c r="V32">
+      <c r="AB32">
+        <v>0.9</v>
+      </c>
+      <c r="AC32">
+        <v>0.9</v>
+      </c>
+      <c r="AD32">
+        <v>0.9</v>
+      </c>
+      <c r="AE32">
         <v>0.9000000000000001</v>
       </c>
-      <c r="W32">
-        <v>0.9</v>
-      </c>
-      <c r="X32">
+      <c r="AF32">
+        <v>0.9</v>
+      </c>
+      <c r="AG32">
+        <v>0.9</v>
+      </c>
+      <c r="AH32">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AI32">
         <v>0.8999999999999999</v>
       </c>
-      <c r="Y32">
-        <v>0.9</v>
-      </c>
-      <c r="Z32">
-        <v>0.9</v>
-      </c>
-      <c r="AA32">
-        <v>0.9</v>
-      </c>
-      <c r="AB32">
-        <v>0.9</v>
-      </c>
-      <c r="AC32">
-        <v>0.9</v>
-      </c>
-      <c r="AD32">
+      <c r="AJ32">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AE32">
+      <c r="AK32">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AF32">
-        <v>0.9</v>
-      </c>
-      <c r="AG32">
+      <c r="AL32">
+        <v>0.9</v>
+      </c>
+      <c r="AM32">
+        <v>0.9</v>
+      </c>
+      <c r="AN32">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AO32">
         <v>0.9000000000000001</v>
       </c>
-      <c r="AH32">
+      <c r="AP32">
+        <v>0.9</v>
+      </c>
+      <c r="AQ32">
+        <v>0.9</v>
+      </c>
+      <c r="AR32">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="AS32">
+        <v>0.9</v>
+      </c>
+      <c r="AT32">
+        <v>0.9</v>
+      </c>
+      <c r="AU32">
         <v>0.8999999999999999</v>
       </c>
-      <c r="AI32">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AJ32">
-        <v>0.9</v>
-      </c>
-      <c r="AK32">
-        <v>0.9</v>
-      </c>
-      <c r="AL32">
-        <v>0.9</v>
-      </c>
-      <c r="AM32">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AN32">
-        <v>0.9</v>
-      </c>
-      <c r="AO32">
-        <v>0.9</v>
-      </c>
-      <c r="AP32">
-        <v>0.9</v>
-      </c>
-      <c r="AQ32">
-        <v>0.9</v>
-      </c>
-      <c r="AR32">
-        <v>0.9</v>
-      </c>
-      <c r="AS32">
-        <v>0.9</v>
-      </c>
-      <c r="AT32">
-        <v>0.9</v>
-      </c>
-      <c r="AU32">
-        <v>0.9</v>
-      </c>
       <c r="AV32">
+        <v>0.9</v>
+      </c>
+      <c r="AW32">
+        <v>0.9</v>
+      </c>
+      <c r="AX32">
         <v>0.8999999999999999</v>
-      </c>
-      <c r="AW32">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="AX32">
-        <v>0.9</v>
       </c>
       <c r="AY32">
         <v>0.9</v>
